--- a/reporting/FY27_Revenue_Tracker_v3.xlsx
+++ b/reporting/FY27_Revenue_Tracker_v3.xlsx
@@ -9552,7 +9552,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),f0,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),f1,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),f2,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),f3,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),f4,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),f5,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,f0*f1*f2*f3*f4*f5,n,SUM(k),tot,SUM(f0),ex,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,12)*1,0)),gs,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,13)*1,0)),ic,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,14)*1,0)),"Showing "&amp;TEXT(n,"#,##0")&amp;" of "&amp;TEXT(tot,"#,##0")&amp;" records"&amp;"      Ex GST "&amp;TEXT(ex,"$#,##0.00")&amp;"      GST "&amp;TEXT(gs,"$#,##0.00")&amp;"      Inc GST "&amp;TEXT(ic,"$#,##0.00"))</f>
+        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),keep,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,keep*fTeam*fCC*fMonth*fStat*fFind,cnt,SUM(k),tot,SUM(keep),ex,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,12)*1,0)),gs,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,13)*1,0)),ic,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,14)*1,0)),"Showing "&amp;TEXT(cnt,"#,##0")&amp;" of "&amp;TEXT(tot,"#,##0")&amp;" records"&amp;"      Ex GST "&amp;TEXT(ex,"$#,##0.00")&amp;"      GST "&amp;TEXT(gs,"$#,##0.00")&amp;"      Inc GST "&amp;TEXT(ic,"$#,##0.00"))</f>
         <v/>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),f0,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),f1,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),f2,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),f3,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),f4,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),f5,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,f0*f1*f2*f3*f4*f5,_xlfn._xlws.SORT(_xlfn._xlws.FILTER(d,k=1,"No records match these filters - widen them or check the department sheets"),1,-1))</f>
+        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),keep,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,keep*fTeam*fCC*fMonth*fStat*fFind,_xlfn._xlws.SORT(_xlfn._xlws.FILTER(d,k=1,"No records match these filters - widen them or check the department sheets"),1,-1))</f>
         <v/>
       </c>
     </row>
@@ -9803,11 +9803,11 @@
         </is>
       </c>
       <c r="B8" s="24">
-        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A8)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A8)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A8)</f>
+        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A8)+SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A8)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A8)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A8)</f>
         <v/>
       </c>
       <c r="C8" s="24">
-        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A8)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A8)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A8)</f>
+        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A8)+SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A8)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A8)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A8)</f>
         <v/>
       </c>
       <c r="D8" s="25">
@@ -9839,11 +9839,11 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4)-SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4)+SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A9)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A9)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A9)</f>
+        <f>(SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO"))-(SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO"))+SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A9)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A9)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A9)</f>
         <v/>
       </c>
       <c r="C9" s="24">
-        <f>SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4)-SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4)+SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A9)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A9)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A9)</f>
+        <f>(SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO"))-(SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO"))+SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A9)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A9)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A9)</f>
         <v/>
       </c>
       <c r="D9" s="25">
@@ -9875,11 +9875,11 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4)+SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A10)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A10)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A10)</f>
+        <f>SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[Video Revenue],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO")+SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A10)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A10)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A10)</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4)+SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A10)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A10)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A10)</f>
+        <f>SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"PRODUCTION")+SUMIFS(tbl_Production[Video GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],"VIDEO")+SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A10)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A10)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A10)</f>
         <v/>
       </c>
       <c r="D10" s="25">
@@ -9911,11 +9911,11 @@
         </is>
       </c>
       <c r="B11" s="24">
-        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A11)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A11)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A11)</f>
+        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A11)+SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A11)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A11)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A11)</f>
         <v/>
       </c>
       <c r="C11" s="24">
-        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A11)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A11)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A11)</f>
+        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A11)+SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A11)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A11)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A11)</f>
         <v/>
       </c>
       <c r="D11" s="25">
@@ -9947,11 +9947,11 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A12)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A12)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A12)</f>
+        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A12)+SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A12)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A12)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A12)</f>
         <v/>
       </c>
       <c r="C12" s="24">
-        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A12)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A12)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A12)</f>
+        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A12)+SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A12)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A12)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A12)</f>
         <v/>
       </c>
       <c r="D12" s="25">
@@ -9983,11 +9983,11 @@
         </is>
       </c>
       <c r="B13" s="24">
-        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A13)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A13)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A13)</f>
+        <f>SUMIFS(tbl_Onsite[Ex GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A13)+SUMIFS(tbl_Production[Ex GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A13)+SUMIFS(tbl_Consulting[Ex GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A13)+SUMIFS(tbl_Other[Ex GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A13)</f>
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A13)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A13)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A13)</f>
+        <f>SUMIFS(tbl_Onsite[GST],tbl_Onsite[Month],$C$4,tbl_Onsite[Cost Centre],$A13)+SUMIFS(tbl_Production[GST],tbl_Production[Month],$C$4,tbl_Production[Cost Centre],$A13)+SUMIFS(tbl_Consulting[GST],tbl_Consulting[Month],$C$4,tbl_Consulting[Cost Centre],$A13)+SUMIFS(tbl_Other[GST],tbl_Other[Month],$C$4,tbl_Other[Cost Centre],$A13)</f>
         <v/>
       </c>
       <c r="D13" s="25">
@@ -19352,7 +19352,7 @@
         <v>46234</v>
       </c>
       <c r="B5" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A5="","",EOMONTH(A5,0))</f>
         <v/>
       </c>
       <c r="C5" s="50">
@@ -19375,7 +19375,7 @@
         </is>
       </c>
       <c r="G5" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F5="","",IF(COUNTIF(lst_Jobs,F5&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H5" s="51" t="inlineStr">
@@ -19402,11 +19402,11 @@
         <v>8588.450000000001</v>
       </c>
       <c r="M5" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L5="","",IF(K5="GST 10%",ROUND(L5*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L5="","",L5+M5)</f>
         <v/>
       </c>
       <c r="O5" s="51" t="inlineStr">
@@ -19448,7 +19448,7 @@
         <v>46234</v>
       </c>
       <c r="B6" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A6="","",EOMONTH(A6,0))</f>
         <v/>
       </c>
       <c r="C6" s="50">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G6" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F6="","",IF(COUNTIF(lst_Jobs,F6&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H6" s="51" t="inlineStr">
@@ -19498,11 +19498,11 @@
         <v>22120.57</v>
       </c>
       <c r="M6" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L6="","",IF(K6="GST 10%",ROUND(L6*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L6="","",L6+M6)</f>
         <v/>
       </c>
       <c r="O6" s="51" t="inlineStr">
@@ -19544,7 +19544,7 @@
         <v>46234</v>
       </c>
       <c r="B7" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A7="","",EOMONTH(A7,0))</f>
         <v/>
       </c>
       <c r="C7" s="50">
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="G7" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F7="","",IF(COUNTIF(lst_Jobs,F7&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H7" s="51" t="inlineStr">
@@ -19594,11 +19594,11 @@
         <v>10720</v>
       </c>
       <c r="M7" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L7="","",IF(K7="GST 10%",ROUND(L7*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L7="","",L7+M7)</f>
         <v/>
       </c>
       <c r="O7" s="51" t="inlineStr">
@@ -19636,7 +19636,7 @@
         <v>46234</v>
       </c>
       <c r="B8" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A8="","",EOMONTH(A8,0))</f>
         <v/>
       </c>
       <c r="C8" s="50">
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="G8" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F8="","",IF(COUNTIF(lst_Jobs,F8&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H8" s="51" t="inlineStr">
@@ -19686,11 +19686,11 @@
         <v>103625.44</v>
       </c>
       <c r="M8" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L8="","",IF(K8="GST 10%",ROUND(L8*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L8="","",L8+M8)</f>
         <v/>
       </c>
       <c r="O8" s="51" t="inlineStr">
@@ -19728,7 +19728,7 @@
         <v>46234</v>
       </c>
       <c r="B9" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A9="","",EOMONTH(A9,0))</f>
         <v/>
       </c>
       <c r="C9" s="50">
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="G9" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F9="","",IF(COUNTIF(lst_Jobs,F9&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H9" s="51" t="inlineStr">
@@ -19778,11 +19778,11 @@
         <v>19427.5</v>
       </c>
       <c r="M9" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L9="","",IF(K9="GST 10%",ROUND(L9*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L9="","",L9+M9)</f>
         <v/>
       </c>
       <c r="O9" s="51" t="inlineStr">
@@ -19820,7 +19820,7 @@
         <v>46234</v>
       </c>
       <c r="B10" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A10="","",EOMONTH(A10,0))</f>
         <v/>
       </c>
       <c r="C10" s="50">
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="G10" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F10="","",IF(COUNTIF(lst_Jobs,F10&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H10" s="51" t="inlineStr">
@@ -19870,11 +19870,11 @@
         <v>1120</v>
       </c>
       <c r="M10" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L10="","",IF(K10="GST 10%",ROUND(L10*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L10="","",L10+M10)</f>
         <v/>
       </c>
       <c r="O10" s="51" t="inlineStr">
@@ -19912,7 +19912,7 @@
         <v>46234</v>
       </c>
       <c r="B11" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A11="","",EOMONTH(A11,0))</f>
         <v/>
       </c>
       <c r="C11" s="50">
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="G11" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F11="","",IF(COUNTIF(lst_Jobs,F11&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H11" s="51" t="inlineStr">
@@ -19962,11 +19962,11 @@
         <v>7150</v>
       </c>
       <c r="M11" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L11="","",IF(K11="GST 10%",ROUND(L11*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L11="","",L11+M11)</f>
         <v/>
       </c>
       <c r="O11" s="51" t="inlineStr">
@@ -20004,7 +20004,7 @@
         <v>46234</v>
       </c>
       <c r="B12" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A12="","",EOMONTH(A12,0))</f>
         <v/>
       </c>
       <c r="C12" s="50">
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="G12" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F12="","",IF(COUNTIF(lst_Jobs,F12&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H12" s="51" t="inlineStr">
@@ -20054,11 +20054,11 @@
         <v>12388.8</v>
       </c>
       <c r="M12" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L12="","",IF(K12="GST 10%",ROUND(L12*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L12="","",L12+M12)</f>
         <v/>
       </c>
       <c r="O12" s="51" t="inlineStr">
@@ -20096,7 +20096,7 @@
         <v>46234</v>
       </c>
       <c r="B13" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A13="","",EOMONTH(A13,0))</f>
         <v/>
       </c>
       <c r="C13" s="50">
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="G13" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F13="","",IF(COUNTIF(lst_Jobs,F13&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H13" s="51" t="inlineStr">
@@ -20146,11 +20146,11 @@
         <v>11377.12</v>
       </c>
       <c r="M13" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L13="","",IF(K13="GST 10%",ROUND(L13*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L13="","",L13+M13)</f>
         <v/>
       </c>
       <c r="O13" s="51" t="inlineStr">
@@ -20192,7 +20192,7 @@
         <v>46234</v>
       </c>
       <c r="B14" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A14="","",EOMONTH(A14,0))</f>
         <v/>
       </c>
       <c r="C14" s="50">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="G14" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F14="","",IF(COUNTIF(lst_Jobs,F14&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H14" s="51" t="inlineStr">
@@ -20242,11 +20242,11 @@
         <v>11907</v>
       </c>
       <c r="M14" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L14="","",IF(K14="GST 10%",ROUND(L14*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L14="","",L14+M14)</f>
         <v/>
       </c>
       <c r="O14" s="51" t="inlineStr">
@@ -20284,7 +20284,7 @@
         <v>46234</v>
       </c>
       <c r="B15" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A15="","",EOMONTH(A15,0))</f>
         <v/>
       </c>
       <c r="C15" s="50">
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="G15" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F15="","",IF(COUNTIF(lst_Jobs,F15&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H15" s="51" t="inlineStr">
@@ -20334,11 +20334,11 @@
         <v>11860.5</v>
       </c>
       <c r="M15" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L15="","",IF(K15="GST 10%",ROUND(L15*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L15="","",L15+M15)</f>
         <v/>
       </c>
       <c r="O15" s="51" t="inlineStr">
@@ -20380,7 +20380,7 @@
         <v>46234</v>
       </c>
       <c r="B16" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A16="","",EOMONTH(A16,0))</f>
         <v/>
       </c>
       <c r="C16" s="50">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="F16" s="51" t="n"/>
       <c r="G16" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F16="","",IF(COUNTIF(lst_Jobs,F16&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H16" s="51" t="inlineStr">
@@ -20426,11 +20426,11 @@
         <v>340</v>
       </c>
       <c r="M16" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L16="","",IF(K16="GST 10%",ROUND(L16*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L16="","",L16+M16)</f>
         <v/>
       </c>
       <c r="O16" s="51" t="inlineStr">
@@ -20472,7 +20472,7 @@
         <v>46234</v>
       </c>
       <c r="B17" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A17="","",EOMONTH(A17,0))</f>
         <v/>
       </c>
       <c r="C17" s="50">
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="G17" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F17="","",IF(COUNTIF(lst_Jobs,F17&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H17" s="51" t="inlineStr">
@@ -20522,11 +20522,11 @@
         <v>680</v>
       </c>
       <c r="M17" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L17="","",IF(K17="GST 10%",ROUND(L17*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L17="","",L17+M17)</f>
         <v/>
       </c>
       <c r="O17" s="51" t="inlineStr">
@@ -20564,7 +20564,7 @@
         <v>46234</v>
       </c>
       <c r="B18" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A18="","",EOMONTH(A18,0))</f>
         <v/>
       </c>
       <c r="C18" s="50">
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="G18" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F18="","",IF(COUNTIF(lst_Jobs,F18&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H18" s="51" t="inlineStr">
@@ -20614,11 +20614,11 @@
         <v>4250</v>
       </c>
       <c r="M18" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L18="","",IF(K18="GST 10%",ROUND(L18*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L18="","",L18+M18)</f>
         <v/>
       </c>
       <c r="O18" s="51" t="inlineStr">
@@ -20660,7 +20660,7 @@
         <v>46234</v>
       </c>
       <c r="B19" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A19="","",EOMONTH(A19,0))</f>
         <v/>
       </c>
       <c r="C19" s="50">
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="G19" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F19="","",IF(COUNTIF(lst_Jobs,F19&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H19" s="51" t="inlineStr">
@@ -20710,11 +20710,11 @@
         <v>180</v>
       </c>
       <c r="M19" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L19="","",IF(K19="GST 10%",ROUND(L19*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L19="","",L19+M19)</f>
         <v/>
       </c>
       <c r="O19" s="51" t="inlineStr">
@@ -20752,7 +20752,7 @@
         <v>46234</v>
       </c>
       <c r="B20" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A20="","",EOMONTH(A20,0))</f>
         <v/>
       </c>
       <c r="C20" s="50">
@@ -20775,7 +20775,7 @@
         </is>
       </c>
       <c r="G20" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F20="","",IF(COUNTIF(lst_Jobs,F20&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H20" s="51" t="inlineStr">
@@ -20802,11 +20802,11 @@
         <v>425</v>
       </c>
       <c r="M20" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L20="","",IF(K20="GST 10%",ROUND(L20*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L20="","",L20+M20)</f>
         <v/>
       </c>
       <c r="O20" s="51" t="inlineStr">
@@ -20844,7 +20844,7 @@
         <v>46234</v>
       </c>
       <c r="B21" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A21="","",EOMONTH(A21,0))</f>
         <v/>
       </c>
       <c r="C21" s="50">
@@ -20867,7 +20867,7 @@
         </is>
       </c>
       <c r="G21" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F21="","",IF(COUNTIF(lst_Jobs,F21&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H21" s="51" t="inlineStr">
@@ -20894,11 +20894,11 @@
         <v>510</v>
       </c>
       <c r="M21" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L21="","",IF(K21="GST 10%",ROUND(L21*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L21="","",L21+M21)</f>
         <v/>
       </c>
       <c r="O21" s="51" t="inlineStr">
@@ -20936,7 +20936,7 @@
         <v>46233</v>
       </c>
       <c r="B22" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A22="","",EOMONTH(A22,0))</f>
         <v/>
       </c>
       <c r="C22" s="50">
@@ -20959,7 +20959,7 @@
         </is>
       </c>
       <c r="G22" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F22="","",IF(COUNTIF(lst_Jobs,F22&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H22" s="51" t="inlineStr">
@@ -20986,11 +20986,11 @@
         <v>340</v>
       </c>
       <c r="M22" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L22="","",IF(K22="GST 10%",ROUND(L22*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L22="","",L22+M22)</f>
         <v/>
       </c>
       <c r="O22" s="51" t="inlineStr">
@@ -21032,7 +21032,7 @@
         <v>46233</v>
       </c>
       <c r="B23" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A23="","",EOMONTH(A23,0))</f>
         <v/>
       </c>
       <c r="C23" s="50">
@@ -21055,7 +21055,7 @@
         </is>
       </c>
       <c r="G23" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F23="","",IF(COUNTIF(lst_Jobs,F23&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H23" s="51" t="inlineStr">
@@ -21082,11 +21082,11 @@
         <v>1672.5</v>
       </c>
       <c r="M23" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L23="","",IF(K23="GST 10%",ROUND(L23*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L23="","",L23+M23)</f>
         <v/>
       </c>
       <c r="O23" s="51" t="inlineStr">
@@ -21124,7 +21124,7 @@
         <v>46233</v>
       </c>
       <c r="B24" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A24="","",EOMONTH(A24,0))</f>
         <v/>
       </c>
       <c r="C24" s="50">
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="G24" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F24="","",IF(COUNTIF(lst_Jobs,F24&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H24" s="51" t="inlineStr">
@@ -21174,11 +21174,11 @@
         <v>1670</v>
       </c>
       <c r="M24" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L24="","",IF(K24="GST 10%",ROUND(L24*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L24="","",L24+M24)</f>
         <v/>
       </c>
       <c r="O24" s="51" t="inlineStr">
@@ -21220,7 +21220,7 @@
         <v>46234</v>
       </c>
       <c r="B25" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A25="","",EOMONTH(A25,0))</f>
         <v/>
       </c>
       <c r="C25" s="50">
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="G25" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F25="","",IF(COUNTIF(lst_Jobs,F25&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H25" s="51" t="inlineStr">
@@ -21270,11 +21270,11 @@
         <v>11000</v>
       </c>
       <c r="M25" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L25="","",IF(K25="GST 10%",ROUND(L25*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L25="","",L25+M25)</f>
         <v/>
       </c>
       <c r="O25" s="51" t="inlineStr">
@@ -21312,7 +21312,7 @@
         <v>46265</v>
       </c>
       <c r="B26" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A26="","",EOMONTH(A26,0))</f>
         <v/>
       </c>
       <c r="C26" s="50">
@@ -21335,7 +21335,7 @@
         </is>
       </c>
       <c r="G26" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F26="","",IF(COUNTIF(lst_Jobs,F26&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H26" s="51" t="inlineStr">
@@ -21362,11 +21362,11 @@
         <v>1275</v>
       </c>
       <c r="M26" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L26="","",IF(K26="GST 10%",ROUND(L26*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L26="","",L26+M26)</f>
         <v/>
       </c>
       <c r="O26" s="51" t="inlineStr">
@@ -21408,7 +21408,7 @@
         <v>46265</v>
       </c>
       <c r="B27" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A27="","",EOMONTH(A27,0))</f>
         <v/>
       </c>
       <c r="C27" s="50">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="G27" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F27="","",IF(COUNTIF(lst_Jobs,F27&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H27" s="51" t="inlineStr">
@@ -21458,11 +21458,11 @@
         <v>8500</v>
       </c>
       <c r="M27" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L27="","",IF(K27="GST 10%",ROUND(L27*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L27="","",L27+M27)</f>
         <v/>
       </c>
       <c r="O27" s="51" t="inlineStr">
@@ -21500,7 +21500,7 @@
         <v>46265</v>
       </c>
       <c r="B28" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A28="","",EOMONTH(A28,0))</f>
         <v/>
       </c>
       <c r="C28" s="50">
@@ -21523,7 +21523,7 @@
         </is>
       </c>
       <c r="G28" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F28="","",IF(COUNTIF(lst_Jobs,F28&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H28" s="51" t="inlineStr">
@@ -21550,11 +21550,11 @@
         <v>8022.5</v>
       </c>
       <c r="M28" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L28="","",IF(K28="GST 10%",ROUND(L28*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L28="","",L28+M28)</f>
         <v/>
       </c>
       <c r="O28" s="51" t="inlineStr">
@@ -21590,7 +21590,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="48" t="n"/>
       <c r="B29" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A29="","",EOMONTH(A29,0))</f>
         <v/>
       </c>
       <c r="C29" s="50">
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="G29" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F29="","",IF(COUNTIF(lst_Jobs,F29&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H29" s="51" t="inlineStr">
@@ -21634,11 +21634,11 @@
       </c>
       <c r="L29" s="52" t="n"/>
       <c r="M29" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L29="","",IF(K29="GST 10%",ROUND(L29*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L29="","",L29+M29)</f>
         <v/>
       </c>
       <c r="O29" s="51" t="inlineStr">
@@ -21674,7 +21674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="48" t="n"/>
       <c r="B30" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A30="","",EOMONTH(A30,0))</f>
         <v/>
       </c>
       <c r="C30" s="50">
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="G30" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F30="","",IF(COUNTIF(lst_Jobs,F30&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H30" s="51" t="inlineStr">
@@ -21718,11 +21718,11 @@
       </c>
       <c r="L30" s="52" t="n"/>
       <c r="M30" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L30="","",IF(K30="GST 10%",ROUND(L30*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L30="","",L30+M30)</f>
         <v/>
       </c>
       <c r="O30" s="51" t="inlineStr">
@@ -21760,7 +21760,7 @@
         <v>46265</v>
       </c>
       <c r="B31" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A31="","",EOMONTH(A31,0))</f>
         <v/>
       </c>
       <c r="C31" s="50">
@@ -21783,7 +21783,7 @@
         </is>
       </c>
       <c r="G31" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F31="","",IF(COUNTIF(lst_Jobs,F31&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H31" s="51" t="inlineStr">
@@ -21810,11 +21810,11 @@
         <v>103625.44</v>
       </c>
       <c r="M31" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L31="","",IF(K31="GST 10%",ROUND(L31*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L31="","",L31+M31)</f>
         <v/>
       </c>
       <c r="O31" s="51" t="inlineStr">
@@ -21852,7 +21852,7 @@
         <v>46265</v>
       </c>
       <c r="B32" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A32="","",EOMONTH(A32,0))</f>
         <v/>
       </c>
       <c r="C32" s="50">
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="G32" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F32="","",IF(COUNTIF(lst_Jobs,F32&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H32" s="51" t="inlineStr">
@@ -21902,11 +21902,11 @@
         <v>15113.75</v>
       </c>
       <c r="M32" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L32="","",IF(K32="GST 10%",ROUND(L32*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L32="","",L32+M32)</f>
         <v/>
       </c>
       <c r="O32" s="51" t="inlineStr">
@@ -21944,7 +21944,7 @@
         <v>46265</v>
       </c>
       <c r="B33" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A33="","",EOMONTH(A33,0))</f>
         <v/>
       </c>
       <c r="C33" s="50">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="G33" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F33="","",IF(COUNTIF(lst_Jobs,F33&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H33" s="51" t="inlineStr">
@@ -21994,11 +21994,11 @@
         <v>2080</v>
       </c>
       <c r="M33" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L33="","",IF(K33="GST 10%",ROUND(L33*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L33="","",L33+M33)</f>
         <v/>
       </c>
       <c r="O33" s="51" t="inlineStr">
@@ -22036,7 +22036,7 @@
         <v>46265</v>
       </c>
       <c r="B34" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A34="","",EOMONTH(A34,0))</f>
         <v/>
       </c>
       <c r="C34" s="50">
@@ -22059,7 +22059,7 @@
         </is>
       </c>
       <c r="G34" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F34="","",IF(COUNTIF(lst_Jobs,F34&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H34" s="51" t="inlineStr">
@@ -22086,11 +22086,11 @@
         <v>7150</v>
       </c>
       <c r="M34" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L34="","",IF(K34="GST 10%",ROUND(L34*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L34="","",L34+M34)</f>
         <v/>
       </c>
       <c r="O34" s="51" t="inlineStr">
@@ -22128,7 +22128,7 @@
         <v>46265</v>
       </c>
       <c r="B35" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A35="","",EOMONTH(A35,0))</f>
         <v/>
       </c>
       <c r="C35" s="50">
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="G35" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F35="","",IF(COUNTIF(lst_Jobs,F35&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H35" s="51" t="inlineStr">
@@ -22178,11 +22178,11 @@
         <v>12388.8</v>
       </c>
       <c r="M35" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L35="","",IF(K35="GST 10%",ROUND(L35*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L35="","",L35+M35)</f>
         <v/>
       </c>
       <c r="O35" s="51" t="inlineStr">
@@ -22220,7 +22220,7 @@
         <v>46265</v>
       </c>
       <c r="B36" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A36="","",EOMONTH(A36,0))</f>
         <v/>
       </c>
       <c r="C36" s="50">
@@ -22243,7 +22243,7 @@
         </is>
       </c>
       <c r="G36" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F36="","",IF(COUNTIF(lst_Jobs,F36&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H36" s="51" t="inlineStr">
@@ -22270,11 +22270,11 @@
         <v>11960</v>
       </c>
       <c r="M36" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L36="","",IF(K36="GST 10%",ROUND(L36*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L36="","",L36+M36)</f>
         <v/>
       </c>
       <c r="O36" s="51" t="inlineStr">
@@ -22312,7 +22312,7 @@
         <v>46265</v>
       </c>
       <c r="B37" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A37="","",EOMONTH(A37,0))</f>
         <v/>
       </c>
       <c r="C37" s="50">
@@ -22335,7 +22335,7 @@
         </is>
       </c>
       <c r="G37" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F37="","",IF(COUNTIF(lst_Jobs,F37&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H37" s="51" t="inlineStr">
@@ -22362,11 +22362,11 @@
         <v>11000</v>
       </c>
       <c r="M37" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L37="","",IF(K37="GST 10%",ROUND(L37*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L37="","",L37+M37)</f>
         <v/>
       </c>
       <c r="O37" s="51" t="inlineStr">
@@ -22408,7 +22408,7 @@
         <v>46265</v>
       </c>
       <c r="B38" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A38="","",EOMONTH(A38,0))</f>
         <v/>
       </c>
       <c r="C38" s="50">
@@ -22431,7 +22431,7 @@
         </is>
       </c>
       <c r="G38" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F38="","",IF(COUNTIF(lst_Jobs,F38&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H38" s="51" t="inlineStr">
@@ -22458,11 +22458,11 @@
         <v>11907</v>
       </c>
       <c r="M38" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L38="","",IF(K38="GST 10%",ROUND(L38*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L38="","",L38+M38)</f>
         <v/>
       </c>
       <c r="O38" s="51" t="inlineStr">
@@ -22498,7 +22498,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="48" t="n"/>
       <c r="B39" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A39="","",EOMONTH(A39,0))</f>
         <v/>
       </c>
       <c r="C39" s="50">
@@ -22521,7 +22521,7 @@
         </is>
       </c>
       <c r="G39" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F39="","",IF(COUNTIF(lst_Jobs,F39&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H39" s="51" t="inlineStr">
@@ -22544,11 +22544,11 @@
         <v>3740</v>
       </c>
       <c r="M39" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L39="","",IF(K39="GST 10%",ROUND(L39*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N39" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L39="","",L39+M39)</f>
         <v/>
       </c>
       <c r="O39" s="51" t="inlineStr">
@@ -22590,7 +22590,7 @@
         <v>46265</v>
       </c>
       <c r="B40" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A40="","",EOMONTH(A40,0))</f>
         <v/>
       </c>
       <c r="C40" s="50">
@@ -22613,7 +22613,7 @@
         </is>
       </c>
       <c r="G40" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F40="","",IF(COUNTIF(lst_Jobs,F40&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H40" s="51" t="inlineStr">
@@ -22640,11 +22640,11 @@
         <v>775</v>
       </c>
       <c r="M40" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L40="","",IF(K40="GST 10%",ROUND(L40*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N40" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L40="","",L40+M40)</f>
         <v/>
       </c>
       <c r="O40" s="51" t="inlineStr">
@@ -22682,7 +22682,7 @@
         <v>46265</v>
       </c>
       <c r="B41" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A41="","",EOMONTH(A41,0))</f>
         <v/>
       </c>
       <c r="C41" s="50">
@@ -22705,7 +22705,7 @@
         </is>
       </c>
       <c r="G41" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F41="","",IF(COUNTIF(lst_Jobs,F41&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H41" s="51" t="inlineStr">
@@ -22732,11 +22732,11 @@
         <v>510</v>
       </c>
       <c r="M41" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L41="","",IF(K41="GST 10%",ROUND(L41*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N41" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L41="","",L41+M41)</f>
         <v/>
       </c>
       <c r="O41" s="51" t="inlineStr">
@@ -22774,7 +22774,7 @@
         <v>46265</v>
       </c>
       <c r="B42" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A42="","",EOMONTH(A42,0))</f>
         <v/>
       </c>
       <c r="C42" s="50">
@@ -22797,7 +22797,7 @@
         </is>
       </c>
       <c r="G42" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F42="","",IF(COUNTIF(lst_Jobs,F42&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H42" s="51" t="inlineStr">
@@ -22824,11 +22824,11 @@
         <v>340</v>
       </c>
       <c r="M42" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L42="","",IF(K42="GST 10%",ROUND(L42*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N42" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L42="","",L42+M42)</f>
         <v/>
       </c>
       <c r="O42" s="51" t="inlineStr">
@@ -22866,7 +22866,7 @@
         <v>46265</v>
       </c>
       <c r="B43" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A43="","",EOMONTH(A43,0))</f>
         <v/>
       </c>
       <c r="C43" s="50">
@@ -22889,7 +22889,7 @@
         </is>
       </c>
       <c r="G43" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F43="","",IF(COUNTIF(lst_Jobs,F43&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H43" s="51" t="inlineStr">
@@ -22916,11 +22916,11 @@
         <v>510</v>
       </c>
       <c r="M43" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L43="","",IF(K43="GST 10%",ROUND(L43*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N43" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L43="","",L43+M43)</f>
         <v/>
       </c>
       <c r="O43" s="51" t="inlineStr">
@@ -22958,7 +22958,7 @@
         <v>46265</v>
       </c>
       <c r="B44" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A44="","",EOMONTH(A44,0))</f>
         <v/>
       </c>
       <c r="C44" s="50">
@@ -22981,7 +22981,7 @@
         </is>
       </c>
       <c r="G44" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F44="","",IF(COUNTIF(lst_Jobs,F44&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H44" s="51" t="inlineStr">
@@ -23008,11 +23008,11 @@
         <v>510</v>
       </c>
       <c r="M44" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L44="","",IF(K44="GST 10%",ROUND(L44*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N44" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L44="","",L44+M44)</f>
         <v/>
       </c>
       <c r="O44" s="51" t="inlineStr">
@@ -23050,7 +23050,7 @@
         <v>46265</v>
       </c>
       <c r="B45" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A45="","",EOMONTH(A45,0))</f>
         <v/>
       </c>
       <c r="C45" s="50">
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="G45" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F45="","",IF(COUNTIF(lst_Jobs,F45&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H45" s="51" t="inlineStr">
@@ -23100,11 +23100,11 @@
         <v>340</v>
       </c>
       <c r="M45" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L45="","",IF(K45="GST 10%",ROUND(L45*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N45" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L45="","",L45+M45)</f>
         <v/>
       </c>
       <c r="O45" s="51" t="inlineStr">
@@ -23142,7 +23142,7 @@
         <v>46265</v>
       </c>
       <c r="B46" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A46="","",EOMONTH(A46,0))</f>
         <v/>
       </c>
       <c r="C46" s="50">
@@ -23165,7 +23165,7 @@
         </is>
       </c>
       <c r="G46" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F46="","",IF(COUNTIF(lst_Jobs,F46&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H46" s="51" t="inlineStr">
@@ -23192,11 +23192,11 @@
         <v>425</v>
       </c>
       <c r="M46" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L46="","",IF(K46="GST 10%",ROUND(L46*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N46" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L46="","",L46+M46)</f>
         <v/>
       </c>
       <c r="O46" s="51" t="inlineStr">
@@ -23234,7 +23234,7 @@
         <v>46265</v>
       </c>
       <c r="B47" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A47="","",EOMONTH(A47,0))</f>
         <v/>
       </c>
       <c r="C47" s="50">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="G47" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F47="","",IF(COUNTIF(lst_Jobs,F47&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H47" s="51" t="inlineStr">
@@ -23284,11 +23284,11 @@
         <v>595</v>
       </c>
       <c r="M47" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L47="","",IF(K47="GST 10%",ROUND(L47*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N47" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L47="","",L47+M47)</f>
         <v/>
       </c>
       <c r="O47" s="51" t="inlineStr">
@@ -23326,7 +23326,7 @@
         <v>46265</v>
       </c>
       <c r="B48" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A48="","",EOMONTH(A48,0))</f>
         <v/>
       </c>
       <c r="C48" s="50">
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="G48" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F48="","",IF(COUNTIF(lst_Jobs,F48&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H48" s="51" t="inlineStr">
@@ -23376,11 +23376,11 @@
         <v>22680</v>
       </c>
       <c r="M48" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L48="","",IF(K48="GST 10%",ROUND(L48*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N48" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L48="","",L48+M48)</f>
         <v/>
       </c>
       <c r="O48" s="51" t="inlineStr">
@@ -23418,7 +23418,7 @@
         <v>46265</v>
       </c>
       <c r="B49" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A49="","",EOMONTH(A49,0))</f>
         <v/>
       </c>
       <c r="C49" s="50">
@@ -23441,7 +23441,7 @@
         </is>
       </c>
       <c r="G49" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F49="","",IF(COUNTIF(lst_Jobs,F49&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H49" s="51" t="inlineStr">
@@ -23468,11 +23468,11 @@
         <v>10197.88</v>
       </c>
       <c r="M49" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L49="","",IF(K49="GST 10%",ROUND(L49*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N49" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L49="","",L49+M49)</f>
         <v/>
       </c>
       <c r="O49" s="51" t="inlineStr">
@@ -23510,7 +23510,7 @@
         <v>46265</v>
       </c>
       <c r="B50" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A50="","",EOMONTH(A50,0))</f>
         <v/>
       </c>
       <c r="C50" s="50">
@@ -23533,7 +23533,7 @@
         </is>
       </c>
       <c r="G50" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F50="","",IF(COUNTIF(lst_Jobs,F50&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H50" s="51" t="inlineStr">
@@ -23560,11 +23560,11 @@
         <v>170</v>
       </c>
       <c r="M50" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L50="","",IF(K50="GST 10%",ROUND(L50*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N50" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L50="","",L50+M50)</f>
         <v/>
       </c>
       <c r="O50" s="51" t="inlineStr">
@@ -23602,7 +23602,7 @@
         <v>46265</v>
       </c>
       <c r="B51" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A51="","",EOMONTH(A51,0))</f>
         <v/>
       </c>
       <c r="C51" s="50">
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="G51" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F51="","",IF(COUNTIF(lst_Jobs,F51&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H51" s="51" t="inlineStr">
@@ -23652,11 +23652,11 @@
         <v>11860.56</v>
       </c>
       <c r="M51" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L51="","",IF(K51="GST 10%",ROUND(L51*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N51" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L51="","",L51+M51)</f>
         <v/>
       </c>
       <c r="O51" s="51" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="48" t="n"/>
       <c r="B52" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A52="","",EOMONTH(A52,0))</f>
         <v/>
       </c>
       <c r="C52" s="50">
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="G52" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F52="","",IF(COUNTIF(lst_Jobs,F52&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H52" s="51" t="inlineStr">
@@ -23736,11 +23736,11 @@
       </c>
       <c r="L52" s="52" t="n"/>
       <c r="M52" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L52="","",IF(K52="GST 10%",ROUND(L52*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N52" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L52="","",L52+M52)</f>
         <v/>
       </c>
       <c r="O52" s="51" t="inlineStr">
@@ -23782,7 +23782,7 @@
         <v>46268</v>
       </c>
       <c r="B53" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A53="","",EOMONTH(A53,0))</f>
         <v/>
       </c>
       <c r="C53" s="50">
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="G53" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F53="","",IF(COUNTIF(lst_Jobs,F53&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H53" s="51" t="inlineStr">
@@ -23832,11 +23832,11 @@
         <v>340</v>
       </c>
       <c r="M53" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L53="","",IF(K53="GST 10%",ROUND(L53*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N53" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L53="","",L53+M53)</f>
         <v/>
       </c>
       <c r="O53" s="51" t="inlineStr">
@@ -23876,7 +23876,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="48" t="n"/>
       <c r="B54" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A54="","",EOMONTH(A54,0))</f>
         <v/>
       </c>
       <c r="C54" s="50">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G54" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F54="","",IF(COUNTIF(lst_Jobs,F54&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H54" s="51" t="inlineStr">
@@ -23922,11 +23922,11 @@
         <v>8500</v>
       </c>
       <c r="M54" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L54="","",IF(K54="GST 10%",ROUND(L54*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N54" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L54="","",L54+M54)</f>
         <v/>
       </c>
       <c r="O54" s="51" t="inlineStr">
@@ -23962,7 +23962,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="48" t="n"/>
       <c r="B55" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A55="","",EOMONTH(A55,0))</f>
         <v/>
       </c>
       <c r="C55" s="50">
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="G55" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F55="","",IF(COUNTIF(lst_Jobs,F55&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H55" s="51" t="inlineStr">
@@ -24008,11 +24008,11 @@
         <v>7145</v>
       </c>
       <c r="M55" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L55="","",IF(K55="GST 10%",ROUND(L55*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N55" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L55="","",L55+M55)</f>
         <v/>
       </c>
       <c r="O55" s="51" t="inlineStr">
@@ -24048,7 +24048,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="48" t="n"/>
       <c r="B56" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A56="","",EOMONTH(A56,0))</f>
         <v/>
       </c>
       <c r="C56" s="50">
@@ -24071,7 +24071,7 @@
         </is>
       </c>
       <c r="G56" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F56="","",IF(COUNTIF(lst_Jobs,F56&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H56" s="51" t="inlineStr">
@@ -24094,11 +24094,11 @@
         <v>1275</v>
       </c>
       <c r="M56" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L56="","",IF(K56="GST 10%",ROUND(L56*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N56" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L56="","",L56+M56)</f>
         <v/>
       </c>
       <c r="O56" s="51" t="inlineStr">
@@ -24134,7 +24134,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="48" t="n"/>
       <c r="B57" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A57="","",EOMONTH(A57,0))</f>
         <v/>
       </c>
       <c r="C57" s="50">
@@ -24157,7 +24157,7 @@
         </is>
       </c>
       <c r="G57" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F57="","",IF(COUNTIF(lst_Jobs,F57&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H57" s="51" t="inlineStr">
@@ -24180,11 +24180,11 @@
         <v>7735</v>
       </c>
       <c r="M57" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L57="","",IF(K57="GST 10%",ROUND(L57*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N57" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L57="","",L57+M57)</f>
         <v/>
       </c>
       <c r="O57" s="51" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="48" t="n"/>
       <c r="B58" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A58="","",EOMONTH(A58,0))</f>
         <v/>
       </c>
       <c r="C58" s="50">
@@ -24243,7 +24243,7 @@
         </is>
       </c>
       <c r="G58" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F58="","",IF(COUNTIF(lst_Jobs,F58&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H58" s="51" t="n"/>
@@ -24260,11 +24260,11 @@
       </c>
       <c r="L58" s="52" t="n"/>
       <c r="M58" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L58="","",IF(K58="GST 10%",ROUND(L58*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N58" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L58="","",L58+M58)</f>
         <v/>
       </c>
       <c r="O58" s="51" t="inlineStr">
@@ -24615,7 +24615,7 @@
         <v>46205</v>
       </c>
       <c r="B5" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A5="","",EOMONTH(A5,0))</f>
         <v/>
       </c>
       <c r="C5" s="50">
@@ -24638,7 +24638,7 @@
         </is>
       </c>
       <c r="G5" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F5="","",IF(COUNTIF(lst_Jobs,F5&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H5" s="51" t="inlineStr">
@@ -24665,11 +24665,11 @@
         <v>380</v>
       </c>
       <c r="M5" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L5="","",IF(K5="GST 10%",ROUND(L5*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L5="","",L5+M5)</f>
         <v/>
       </c>
       <c r="O5" s="51" t="inlineStr">
@@ -24695,15 +24695,15 @@
       <c r="S5" s="51" t="n"/>
       <c r="T5" s="52" t="n"/>
       <c r="U5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L5="","",L5-N(T5))</f>
         <v/>
       </c>
       <c r="V5" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L5="","",IF(SIGN(N(T5))*SIGN(L5)=-1,"CHECK - video sign",IF(ABS(N(T5))&gt;ABS(L5),"CHECK - video exceeds invoice",IF(AND(D5="VIDEO",ROUND(N(T5),2)&lt;&gt;ROUND(L5,2)),"CHECK - VIDEO job not fully split",IF(N(T5)=0,"All production",IF(ROUND(N(T5),2)=ROUND(L5,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W5" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L5="","",IF(N(T5)=0,0,ROUND(M5*N(T5)/L5,2)))</f>
         <v/>
       </c>
       <c r="X5" s="51" t="inlineStr">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="AC5" s="52" t="n"/>
       <c r="AD5" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC5/AG5,"")</f>
         <v/>
       </c>
       <c r="AE5" s="52" t="n"/>
@@ -24741,15 +24741,15 @@
         <v>229.56</v>
       </c>
       <c r="AG5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L5="","",L5-N(AC5))</f>
         <v/>
       </c>
       <c r="AH5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L5="","",L5-N(AE5)-N(AF5))</f>
         <v/>
       </c>
       <c r="AI5" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH5/L5,"")</f>
         <v/>
       </c>
       <c r="AJ5" s="54" t="n"/>
@@ -24765,7 +24765,7 @@
         <v>46210</v>
       </c>
       <c r="B6" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A6="","",EOMONTH(A6,0))</f>
         <v/>
       </c>
       <c r="C6" s="50">
@@ -24788,7 +24788,7 @@
         </is>
       </c>
       <c r="G6" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F6="","",IF(COUNTIF(lst_Jobs,F6&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H6" s="51" t="inlineStr">
@@ -24815,11 +24815,11 @@
         <v>3071</v>
       </c>
       <c r="M6" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L6="","",IF(K6="GST 10%",ROUND(L6*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L6="","",L6+M6)</f>
         <v/>
       </c>
       <c r="O6" s="51" t="inlineStr">
@@ -24847,15 +24847,15 @@
         <v>1029</v>
       </c>
       <c r="U6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L6="","",L6-N(T6))</f>
         <v/>
       </c>
       <c r="V6" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L6="","",IF(SIGN(N(T6))*SIGN(L6)=-1,"CHECK - video sign",IF(ABS(N(T6))&gt;ABS(L6),"CHECK - video exceeds invoice",IF(AND(D6="VIDEO",ROUND(N(T6),2)&lt;&gt;ROUND(L6,2)),"CHECK - VIDEO job not fully split",IF(N(T6)=0,"All production",IF(ROUND(N(T6),2)=ROUND(L6,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W6" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L6="","",IF(N(T6)=0,0,ROUND(M6*N(T6)/L6,2)))</f>
         <v/>
       </c>
       <c r="X6" s="51" t="inlineStr">
@@ -24887,7 +24887,7 @@
         <v>334</v>
       </c>
       <c r="AD6" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC6/AG6,"")</f>
         <v/>
       </c>
       <c r="AE6" s="52" t="n"/>
@@ -24895,15 +24895,15 @@
         <v>977.23</v>
       </c>
       <c r="AG6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L6="","",L6-N(AC6))</f>
         <v/>
       </c>
       <c r="AH6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L6="","",L6-N(AE6)-N(AF6))</f>
         <v/>
       </c>
       <c r="AI6" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH6/L6,"")</f>
         <v/>
       </c>
       <c r="AJ6" s="54" t="n">
@@ -24921,7 +24921,7 @@
         <v>46210</v>
       </c>
       <c r="B7" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A7="","",EOMONTH(A7,0))</f>
         <v/>
       </c>
       <c r="C7" s="50">
@@ -24944,7 +24944,7 @@
         </is>
       </c>
       <c r="G7" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F7="","",IF(COUNTIF(lst_Jobs,F7&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H7" s="51" t="inlineStr">
@@ -24971,11 +24971,11 @@
         <v>1925</v>
       </c>
       <c r="M7" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L7="","",IF(K7="GST 10%",ROUND(L7*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L7="","",L7+M7)</f>
         <v/>
       </c>
       <c r="O7" s="51" t="inlineStr">
@@ -25003,15 +25003,15 @@
         <v>970</v>
       </c>
       <c r="U7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L7="","",L7-N(T7))</f>
         <v/>
       </c>
       <c r="V7" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L7="","",IF(SIGN(N(T7))*SIGN(L7)=-1,"CHECK - video sign",IF(ABS(N(T7))&gt;ABS(L7),"CHECK - video exceeds invoice",IF(AND(D7="VIDEO",ROUND(N(T7),2)&lt;&gt;ROUND(L7,2)),"CHECK - VIDEO job not fully split",IF(N(T7)=0,"All production",IF(ROUND(N(T7),2)=ROUND(L7,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W7" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L7="","",IF(N(T7)=0,0,ROUND(M7*N(T7)/L7,2)))</f>
         <v/>
       </c>
       <c r="X7" s="51" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AC7" s="52" t="n"/>
       <c r="AD7" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC7/AG7,"")</f>
         <v/>
       </c>
       <c r="AE7" s="52" t="n"/>
@@ -25049,15 +25049,15 @@
         <v>821.5599999999999</v>
       </c>
       <c r="AG7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L7="","",L7-N(AC7))</f>
         <v/>
       </c>
       <c r="AH7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L7="","",L7-N(AE7)-N(AF7))</f>
         <v/>
       </c>
       <c r="AI7" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH7/L7,"")</f>
         <v/>
       </c>
       <c r="AJ7" s="54" t="n">
@@ -25077,7 +25077,7 @@
         <v>46219</v>
       </c>
       <c r="B8" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A8="","",EOMONTH(A8,0))</f>
         <v/>
       </c>
       <c r="C8" s="50">
@@ -25100,7 +25100,7 @@
         </is>
       </c>
       <c r="G8" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F8="","",IF(COUNTIF(lst_Jobs,F8&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H8" s="51" t="inlineStr">
@@ -25127,11 +25127,11 @@
         <v>261.25</v>
       </c>
       <c r="M8" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L8="","",IF(K8="GST 10%",ROUND(L8*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L8="","",L8+M8)</f>
         <v/>
       </c>
       <c r="O8" s="51" t="inlineStr">
@@ -25157,15 +25157,15 @@
       <c r="S8" s="51" t="n"/>
       <c r="T8" s="52" t="n"/>
       <c r="U8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L8="","",L8-N(T8))</f>
         <v/>
       </c>
       <c r="V8" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L8="","",IF(SIGN(N(T8))*SIGN(L8)=-1,"CHECK - video sign",IF(ABS(N(T8))&gt;ABS(L8),"CHECK - video exceeds invoice",IF(AND(D8="VIDEO",ROUND(N(T8),2)&lt;&gt;ROUND(L8,2)),"CHECK - VIDEO job not fully split",IF(N(T8)=0,"All production",IF(ROUND(N(T8),2)=ROUND(L8,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W8" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L8="","",IF(N(T8)=0,0,ROUND(M8*N(T8)/L8,2)))</f>
         <v/>
       </c>
       <c r="X8" s="51" t="inlineStr">
@@ -25195,21 +25195,21 @@
       </c>
       <c r="AC8" s="52" t="n"/>
       <c r="AD8" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC8/AG8,"")</f>
         <v/>
       </c>
       <c r="AE8" s="52" t="n"/>
       <c r="AF8" s="52" t="n"/>
       <c r="AG8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L8="","",L8-N(AC8))</f>
         <v/>
       </c>
       <c r="AH8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L8="","",L8-N(AE8)-N(AF8))</f>
         <v/>
       </c>
       <c r="AI8" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH8/L8,"")</f>
         <v/>
       </c>
       <c r="AJ8" s="54" t="n"/>
@@ -25227,7 +25227,7 @@
         <v>46210</v>
       </c>
       <c r="B9" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A9="","",EOMONTH(A9,0))</f>
         <v/>
       </c>
       <c r="C9" s="50">
@@ -25250,7 +25250,7 @@
         </is>
       </c>
       <c r="G9" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F9="","",IF(COUNTIF(lst_Jobs,F9&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H9" s="51" t="inlineStr">
@@ -25277,11 +25277,11 @@
         <v>500</v>
       </c>
       <c r="M9" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L9="","",IF(K9="GST 10%",ROUND(L9*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L9="","",L9+M9)</f>
         <v/>
       </c>
       <c r="O9" s="51" t="inlineStr">
@@ -25307,15 +25307,15 @@
       <c r="S9" s="51" t="n"/>
       <c r="T9" s="52" t="n"/>
       <c r="U9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L9="","",L9-N(T9))</f>
         <v/>
       </c>
       <c r="V9" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L9="","",IF(SIGN(N(T9))*SIGN(L9)=-1,"CHECK - video sign",IF(ABS(N(T9))&gt;ABS(L9),"CHECK - video exceeds invoice",IF(AND(D9="VIDEO",ROUND(N(T9),2)&lt;&gt;ROUND(L9,2)),"CHECK - VIDEO job not fully split",IF(N(T9)=0,"All production",IF(ROUND(N(T9),2)=ROUND(L9,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W9" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L9="","",IF(N(T9)=0,0,ROUND(M9*N(T9)/L9,2)))</f>
         <v/>
       </c>
       <c r="X9" s="51" t="inlineStr">
@@ -25347,21 +25347,21 @@
         <v>465</v>
       </c>
       <c r="AD9" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC9/AG9,"")</f>
         <v/>
       </c>
       <c r="AE9" s="52" t="n"/>
       <c r="AF9" s="52" t="n"/>
       <c r="AG9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L9="","",L9-N(AC9))</f>
         <v/>
       </c>
       <c r="AH9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L9="","",L9-N(AE9)-N(AF9))</f>
         <v/>
       </c>
       <c r="AI9" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH9/L9,"")</f>
         <v/>
       </c>
       <c r="AJ9" s="54" t="n"/>
@@ -25377,7 +25377,7 @@
         <v>46216</v>
       </c>
       <c r="B10" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A10="","",EOMONTH(A10,0))</f>
         <v/>
       </c>
       <c r="C10" s="50">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="G10" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F10="","",IF(COUNTIF(lst_Jobs,F10&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H10" s="51" t="inlineStr">
@@ -25427,11 +25427,11 @@
         <v>550</v>
       </c>
       <c r="M10" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L10="","",IF(K10="GST 10%",ROUND(L10*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L10="","",L10+M10)</f>
         <v/>
       </c>
       <c r="O10" s="51" t="inlineStr">
@@ -25459,15 +25459,15 @@
         <v>550</v>
       </c>
       <c r="U10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L10="","",L10-N(T10))</f>
         <v/>
       </c>
       <c r="V10" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L10="","",IF(SIGN(N(T10))*SIGN(L10)=-1,"CHECK - video sign",IF(ABS(N(T10))&gt;ABS(L10),"CHECK - video exceeds invoice",IF(AND(D10="VIDEO",ROUND(N(T10),2)&lt;&gt;ROUND(L10,2)),"CHECK - VIDEO job not fully split",IF(N(T10)=0,"All production",IF(ROUND(N(T10),2)=ROUND(L10,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W10" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L10="","",IF(N(T10)=0,0,ROUND(M10*N(T10)/L10,2)))</f>
         <v/>
       </c>
       <c r="X10" s="51" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="AC10" s="52" t="n"/>
       <c r="AD10" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC10/AG10,"")</f>
         <v/>
       </c>
       <c r="AE10" s="52" t="n"/>
@@ -25503,15 +25503,15 @@
         <v>312.18</v>
       </c>
       <c r="AG10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L10="","",L10-N(AC10))</f>
         <v/>
       </c>
       <c r="AH10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L10="","",L10-N(AE10)-N(AF10))</f>
         <v/>
       </c>
       <c r="AI10" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH10/L10,"")</f>
         <v/>
       </c>
       <c r="AJ10" s="54" t="n">
@@ -25527,7 +25527,7 @@
         <v>46234</v>
       </c>
       <c r="B11" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A11="","",EOMONTH(A11,0))</f>
         <v/>
       </c>
       <c r="C11" s="50">
@@ -25550,7 +25550,7 @@
         </is>
       </c>
       <c r="G11" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F11="","",IF(COUNTIF(lst_Jobs,F11&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H11" s="51" t="inlineStr">
@@ -25577,11 +25577,11 @@
         <v>12587</v>
       </c>
       <c r="M11" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L11="","",IF(K11="GST 10%",ROUND(L11*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L11="","",L11+M11)</f>
         <v/>
       </c>
       <c r="O11" s="51" t="inlineStr">
@@ -25609,15 +25609,15 @@
         <v>1702</v>
       </c>
       <c r="U11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L11="","",L11-N(T11))</f>
         <v/>
       </c>
       <c r="V11" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L11="","",IF(SIGN(N(T11))*SIGN(L11)=-1,"CHECK - video sign",IF(ABS(N(T11))&gt;ABS(L11),"CHECK - video exceeds invoice",IF(AND(D11="VIDEO",ROUND(N(T11),2)&lt;&gt;ROUND(L11,2)),"CHECK - VIDEO job not fully split",IF(N(T11)=0,"All production",IF(ROUND(N(T11),2)=ROUND(L11,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W11" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L11="","",IF(N(T11)=0,0,ROUND(M11*N(T11)/L11,2)))</f>
         <v/>
       </c>
       <c r="X11" s="51" t="inlineStr">
@@ -25647,7 +25647,7 @@
         <v>580</v>
       </c>
       <c r="AD11" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC11/AG11,"")</f>
         <v/>
       </c>
       <c r="AE11" s="52" t="n">
@@ -25657,15 +25657,15 @@
         <v>3148.7</v>
       </c>
       <c r="AG11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L11="","",L11-N(AC11))</f>
         <v/>
       </c>
       <c r="AH11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L11="","",L11-N(AE11)-N(AF11))</f>
         <v/>
       </c>
       <c r="AI11" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH11/L11,"")</f>
         <v/>
       </c>
       <c r="AJ11" s="54" t="n">
@@ -25683,7 +25683,7 @@
         <v>46232</v>
       </c>
       <c r="B12" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A12="","",EOMONTH(A12,0))</f>
         <v/>
       </c>
       <c r="C12" s="50">
@@ -25706,7 +25706,7 @@
         </is>
       </c>
       <c r="G12" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F12="","",IF(COUNTIF(lst_Jobs,F12&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H12" s="51" t="inlineStr">
@@ -25733,11 +25733,11 @@
         <v>745</v>
       </c>
       <c r="M12" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L12="","",IF(K12="GST 10%",ROUND(L12*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L12="","",L12+M12)</f>
         <v/>
       </c>
       <c r="O12" s="51" t="inlineStr">
@@ -25763,15 +25763,15 @@
       <c r="S12" s="51" t="n"/>
       <c r="T12" s="52" t="n"/>
       <c r="U12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L12="","",L12-N(T12))</f>
         <v/>
       </c>
       <c r="V12" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L12="","",IF(SIGN(N(T12))*SIGN(L12)=-1,"CHECK - video sign",IF(ABS(N(T12))&gt;ABS(L12),"CHECK - video exceeds invoice",IF(AND(D12="VIDEO",ROUND(N(T12),2)&lt;&gt;ROUND(L12,2)),"CHECK - VIDEO job not fully split",IF(N(T12)=0,"All production",IF(ROUND(N(T12),2)=ROUND(L12,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W12" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L12="","",IF(N(T12)=0,0,ROUND(M12*N(T12)/L12,2)))</f>
         <v/>
       </c>
       <c r="X12" s="51" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="AC12" s="52" t="n"/>
       <c r="AD12" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC12/AG12,"")</f>
         <v/>
       </c>
       <c r="AE12" s="52" t="n"/>
@@ -25807,15 +25807,15 @@
         <v>153.84</v>
       </c>
       <c r="AG12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L12="","",L12-N(AC12))</f>
         <v/>
       </c>
       <c r="AH12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L12="","",L12-N(AE12)-N(AF12))</f>
         <v/>
       </c>
       <c r="AI12" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH12/L12,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="54" t="n"/>
@@ -25831,7 +25831,7 @@
         <v>46234</v>
       </c>
       <c r="B13" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A13="","",EOMONTH(A13,0))</f>
         <v/>
       </c>
       <c r="C13" s="50">
@@ -25854,7 +25854,7 @@
         </is>
       </c>
       <c r="G13" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F13="","",IF(COUNTIF(lst_Jobs,F13&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H13" s="51" t="inlineStr">
@@ -25881,11 +25881,11 @@
         <v>5636</v>
       </c>
       <c r="M13" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L13="","",IF(K13="GST 10%",ROUND(L13*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L13="","",L13+M13)</f>
         <v/>
       </c>
       <c r="O13" s="51" t="inlineStr">
@@ -25913,15 +25913,15 @@
         <v>176</v>
       </c>
       <c r="U13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L13="","",L13-N(T13))</f>
         <v/>
       </c>
       <c r="V13" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L13="","",IF(SIGN(N(T13))*SIGN(L13)=-1,"CHECK - video sign",IF(ABS(N(T13))&gt;ABS(L13),"CHECK - video exceeds invoice",IF(AND(D13="VIDEO",ROUND(N(T13),2)&lt;&gt;ROUND(L13,2)),"CHECK - VIDEO job not fully split",IF(N(T13)=0,"All production",IF(ROUND(N(T13),2)=ROUND(L13,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W13" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L13="","",IF(N(T13)=0,0,ROUND(M13*N(T13)/L13,2)))</f>
         <v/>
       </c>
       <c r="X13" s="51" t="inlineStr">
@@ -25951,7 +25951,7 @@
         <v>839</v>
       </c>
       <c r="AD13" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC13/AG13,"")</f>
         <v/>
       </c>
       <c r="AE13" s="52" t="n"/>
@@ -25959,15 +25959,15 @@
         <v>1375.96</v>
       </c>
       <c r="AG13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L13="","",L13-N(AC13))</f>
         <v/>
       </c>
       <c r="AH13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L13="","",L13-N(AE13)-N(AF13))</f>
         <v/>
       </c>
       <c r="AI13" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH13/L13,"")</f>
         <v/>
       </c>
       <c r="AJ13" s="54" t="n"/>
@@ -25983,7 +25983,7 @@
         <v>46234</v>
       </c>
       <c r="B14" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A14="","",EOMONTH(A14,0))</f>
         <v/>
       </c>
       <c r="C14" s="50">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="G14" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F14="","",IF(COUNTIF(lst_Jobs,F14&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H14" s="51" t="inlineStr">
@@ -26033,11 +26033,11 @@
         <v>2575</v>
       </c>
       <c r="M14" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L14="","",IF(K14="GST 10%",ROUND(L14*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L14="","",L14+M14)</f>
         <v/>
       </c>
       <c r="O14" s="51" t="inlineStr">
@@ -26063,15 +26063,15 @@
       <c r="S14" s="51" t="n"/>
       <c r="T14" s="52" t="n"/>
       <c r="U14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L14="","",L14-N(T14))</f>
         <v/>
       </c>
       <c r="V14" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L14="","",IF(SIGN(N(T14))*SIGN(L14)=-1,"CHECK - video sign",IF(ABS(N(T14))&gt;ABS(L14),"CHECK - video exceeds invoice",IF(AND(D14="VIDEO",ROUND(N(T14),2)&lt;&gt;ROUND(L14,2)),"CHECK - VIDEO job not fully split",IF(N(T14)=0,"All production",IF(ROUND(N(T14),2)=ROUND(L14,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W14" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L14="","",IF(N(T14)=0,0,ROUND(M14*N(T14)/L14,2)))</f>
         <v/>
       </c>
       <c r="X14" s="51" t="inlineStr">
@@ -26101,7 +26101,7 @@
         <v>95</v>
       </c>
       <c r="AD14" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC14/AG14,"")</f>
         <v/>
       </c>
       <c r="AE14" s="52" t="n"/>
@@ -26109,15 +26109,15 @@
         <v>453.31</v>
       </c>
       <c r="AG14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L14="","",L14-N(AC14))</f>
         <v/>
       </c>
       <c r="AH14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L14="","",L14-N(AE14)-N(AF14))</f>
         <v/>
       </c>
       <c r="AI14" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH14/L14,"")</f>
         <v/>
       </c>
       <c r="AJ14" s="54" t="n"/>
@@ -26133,7 +26133,7 @@
         <v>46223</v>
       </c>
       <c r="B15" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A15="","",EOMONTH(A15,0))</f>
         <v/>
       </c>
       <c r="C15" s="50">
@@ -26156,7 +26156,7 @@
         </is>
       </c>
       <c r="G15" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F15="","",IF(COUNTIF(lst_Jobs,F15&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H15" s="51" t="inlineStr">
@@ -26183,11 +26183,11 @@
         <v>975</v>
       </c>
       <c r="M15" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L15="","",IF(K15="GST 10%",ROUND(L15*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L15="","",L15+M15)</f>
         <v/>
       </c>
       <c r="O15" s="51" t="inlineStr">
@@ -26213,15 +26213,15 @@
       <c r="S15" s="51" t="n"/>
       <c r="T15" s="52" t="n"/>
       <c r="U15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L15="","",L15-N(T15))</f>
         <v/>
       </c>
       <c r="V15" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L15="","",IF(SIGN(N(T15))*SIGN(L15)=-1,"CHECK - video sign",IF(ABS(N(T15))&gt;ABS(L15),"CHECK - video exceeds invoice",IF(AND(D15="VIDEO",ROUND(N(T15),2)&lt;&gt;ROUND(L15,2)),"CHECK - VIDEO job not fully split",IF(N(T15)=0,"All production",IF(ROUND(N(T15),2)=ROUND(L15,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W15" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L15="","",IF(N(T15)=0,0,ROUND(M15*N(T15)/L15,2)))</f>
         <v/>
       </c>
       <c r="X15" s="51" t="inlineStr">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="AC15" s="52" t="n"/>
       <c r="AD15" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC15/AG15,"")</f>
         <v/>
       </c>
       <c r="AE15" s="52" t="n">
@@ -26257,15 +26257,15 @@
       </c>
       <c r="AF15" s="52" t="n"/>
       <c r="AG15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L15="","",L15-N(AC15))</f>
         <v/>
       </c>
       <c r="AH15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L15="","",L15-N(AE15)-N(AF15))</f>
         <v/>
       </c>
       <c r="AI15" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH15/L15,"")</f>
         <v/>
       </c>
       <c r="AJ15" s="54" t="n"/>
@@ -26281,7 +26281,7 @@
         <v>46234</v>
       </c>
       <c r="B16" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A16="","",EOMONTH(A16,0))</f>
         <v/>
       </c>
       <c r="C16" s="50">
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G16" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F16="","",IF(COUNTIF(lst_Jobs,F16&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H16" s="51" t="inlineStr">
@@ -26331,11 +26331,11 @@
         <v>52749.78</v>
       </c>
       <c r="M16" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L16="","",IF(K16="GST 10%",ROUND(L16*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L16="","",L16+M16)</f>
         <v/>
       </c>
       <c r="O16" s="51" t="inlineStr">
@@ -26361,15 +26361,15 @@
       <c r="S16" s="51" t="n"/>
       <c r="T16" s="52" t="n"/>
       <c r="U16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L16="","",L16-N(T16))</f>
         <v/>
       </c>
       <c r="V16" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L16="","",IF(SIGN(N(T16))*SIGN(L16)=-1,"CHECK - video sign",IF(ABS(N(T16))&gt;ABS(L16),"CHECK - video exceeds invoice",IF(AND(D16="VIDEO",ROUND(N(T16),2)&lt;&gt;ROUND(L16,2)),"CHECK - VIDEO job not fully split",IF(N(T16)=0,"All production",IF(ROUND(N(T16),2)=ROUND(L16,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W16" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L16="","",IF(N(T16)=0,0,ROUND(M16*N(T16)/L16,2)))</f>
         <v/>
       </c>
       <c r="X16" s="51" t="inlineStr">
@@ -26399,7 +26399,7 @@
         <v>4452.72</v>
       </c>
       <c r="AD16" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC16/AG16,"")</f>
         <v/>
       </c>
       <c r="AE16" s="52" t="n">
@@ -26409,15 +26409,15 @@
         <v>462.23</v>
       </c>
       <c r="AG16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L16="","",L16-N(AC16))</f>
         <v/>
       </c>
       <c r="AH16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L16="","",L16-N(AE16)-N(AF16))</f>
         <v/>
       </c>
       <c r="AI16" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH16/L16,"")</f>
         <v/>
       </c>
       <c r="AJ16" s="54" t="n"/>
@@ -26435,7 +26435,7 @@
         <v>46234</v>
       </c>
       <c r="B17" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A17="","",EOMONTH(A17,0))</f>
         <v/>
       </c>
       <c r="C17" s="50">
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="G17" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F17="","",IF(COUNTIF(lst_Jobs,F17&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H17" s="51" t="inlineStr">
@@ -26485,11 +26485,11 @@
         <v>1925</v>
       </c>
       <c r="M17" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L17="","",IF(K17="GST 10%",ROUND(L17*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L17="","",L17+M17)</f>
         <v/>
       </c>
       <c r="O17" s="51" t="inlineStr">
@@ -26515,15 +26515,15 @@
       <c r="S17" s="51" t="n"/>
       <c r="T17" s="52" t="n"/>
       <c r="U17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L17="","",L17-N(T17))</f>
         <v/>
       </c>
       <c r="V17" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L17="","",IF(SIGN(N(T17))*SIGN(L17)=-1,"CHECK - video sign",IF(ABS(N(T17))&gt;ABS(L17),"CHECK - video exceeds invoice",IF(AND(D17="VIDEO",ROUND(N(T17),2)&lt;&gt;ROUND(L17,2)),"CHECK - VIDEO job not fully split",IF(N(T17)=0,"All production",IF(ROUND(N(T17),2)=ROUND(L17,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W17" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L17="","",IF(N(T17)=0,0,ROUND(M17*N(T17)/L17,2)))</f>
         <v/>
       </c>
       <c r="X17" s="51" t="inlineStr">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="AC17" s="52" t="n"/>
       <c r="AD17" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC17/AG17,"")</f>
         <v/>
       </c>
       <c r="AE17" s="52" t="n"/>
@@ -26559,15 +26559,15 @@
         <v>812.09</v>
       </c>
       <c r="AG17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L17="","",L17-N(AC17))</f>
         <v/>
       </c>
       <c r="AH17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L17="","",L17-N(AE17)-N(AF17))</f>
         <v/>
       </c>
       <c r="AI17" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH17/L17,"")</f>
         <v/>
       </c>
       <c r="AJ17" s="54" t="n">
@@ -26587,7 +26587,7 @@
         <v>46234</v>
       </c>
       <c r="B18" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A18="","",EOMONTH(A18,0))</f>
         <v/>
       </c>
       <c r="C18" s="50">
@@ -26610,7 +26610,7 @@
         </is>
       </c>
       <c r="G18" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F18="","",IF(COUNTIF(lst_Jobs,F18&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H18" s="51" t="inlineStr">
@@ -26637,11 +26637,11 @@
         <v>11570</v>
       </c>
       <c r="M18" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L18="","",IF(K18="GST 10%",ROUND(L18*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L18="","",L18+M18)</f>
         <v/>
       </c>
       <c r="O18" s="51" t="inlineStr">
@@ -26667,15 +26667,15 @@
       <c r="S18" s="51" t="n"/>
       <c r="T18" s="52" t="n"/>
       <c r="U18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L18="","",L18-N(T18))</f>
         <v/>
       </c>
       <c r="V18" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L18="","",IF(SIGN(N(T18))*SIGN(L18)=-1,"CHECK - video sign",IF(ABS(N(T18))&gt;ABS(L18),"CHECK - video exceeds invoice",IF(AND(D18="VIDEO",ROUND(N(T18),2)&lt;&gt;ROUND(L18,2)),"CHECK - VIDEO job not fully split",IF(N(T18)=0,"All production",IF(ROUND(N(T18),2)=ROUND(L18,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W18" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L18="","",IF(N(T18)=0,0,ROUND(M18*N(T18)/L18,2)))</f>
         <v/>
       </c>
       <c r="X18" s="51" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="AC18" s="52" t="n"/>
       <c r="AD18" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC18/AG18,"")</f>
         <v/>
       </c>
       <c r="AE18" s="52" t="n">
@@ -26713,15 +26713,15 @@
         <v>283.18</v>
       </c>
       <c r="AG18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L18="","",L18-N(AC18))</f>
         <v/>
       </c>
       <c r="AH18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L18="","",L18-N(AE18)-N(AF18))</f>
         <v/>
       </c>
       <c r="AI18" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH18/L18,"")</f>
         <v/>
       </c>
       <c r="AJ18" s="54" t="n"/>
@@ -26737,7 +26737,7 @@
         <v>46234</v>
       </c>
       <c r="B19" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A19="","",EOMONTH(A19,0))</f>
         <v/>
       </c>
       <c r="C19" s="50">
@@ -26760,7 +26760,7 @@
         </is>
       </c>
       <c r="G19" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F19="","",IF(COUNTIF(lst_Jobs,F19&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H19" s="51" t="inlineStr">
@@ -26787,11 +26787,11 @@
         <v>1120</v>
       </c>
       <c r="M19" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L19="","",IF(K19="GST 10%",ROUND(L19*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L19="","",L19+M19)</f>
         <v/>
       </c>
       <c r="O19" s="51" t="inlineStr">
@@ -26817,15 +26817,15 @@
       <c r="S19" s="51" t="n"/>
       <c r="T19" s="52" t="n"/>
       <c r="U19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L19="","",L19-N(T19))</f>
         <v/>
       </c>
       <c r="V19" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L19="","",IF(SIGN(N(T19))*SIGN(L19)=-1,"CHECK - video sign",IF(ABS(N(T19))&gt;ABS(L19),"CHECK - video exceeds invoice",IF(AND(D19="VIDEO",ROUND(N(T19),2)&lt;&gt;ROUND(L19,2)),"CHECK - VIDEO job not fully split",IF(N(T19)=0,"All production",IF(ROUND(N(T19),2)=ROUND(L19,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W19" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L19="","",IF(N(T19)=0,0,ROUND(M19*N(T19)/L19,2)))</f>
         <v/>
       </c>
       <c r="X19" s="51" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="AC19" s="52" t="n"/>
       <c r="AD19" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC19/AG19,"")</f>
         <v/>
       </c>
       <c r="AE19" s="52" t="n"/>
@@ -26861,15 +26861,15 @@
         <v>626.92</v>
       </c>
       <c r="AG19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L19="","",L19-N(AC19))</f>
         <v/>
       </c>
       <c r="AH19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L19="","",L19-N(AE19)-N(AF19))</f>
         <v/>
       </c>
       <c r="AI19" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH19/L19,"")</f>
         <v/>
       </c>
       <c r="AJ19" s="54" t="n"/>
@@ -26885,7 +26885,7 @@
         <v>46234</v>
       </c>
       <c r="B20" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A20="","",EOMONTH(A20,0))</f>
         <v/>
       </c>
       <c r="C20" s="50">
@@ -26908,7 +26908,7 @@
         </is>
       </c>
       <c r="G20" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F20="","",IF(COUNTIF(lst_Jobs,F20&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H20" s="51" t="inlineStr">
@@ -26935,11 +26935,11 @@
         <v>8550</v>
       </c>
       <c r="M20" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L20="","",IF(K20="GST 10%",ROUND(L20*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L20="","",L20+M20)</f>
         <v/>
       </c>
       <c r="O20" s="51" t="inlineStr">
@@ -26965,15 +26965,15 @@
       <c r="S20" s="51" t="n"/>
       <c r="T20" s="52" t="n"/>
       <c r="U20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L20="","",L20-N(T20))</f>
         <v/>
       </c>
       <c r="V20" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L20="","",IF(SIGN(N(T20))*SIGN(L20)=-1,"CHECK - video sign",IF(ABS(N(T20))&gt;ABS(L20),"CHECK - video exceeds invoice",IF(AND(D20="VIDEO",ROUND(N(T20),2)&lt;&gt;ROUND(L20,2)),"CHECK - VIDEO job not fully split",IF(N(T20)=0,"All production",IF(ROUND(N(T20),2)=ROUND(L20,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W20" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L20="","",IF(N(T20)=0,0,ROUND(M20*N(T20)/L20,2)))</f>
         <v/>
       </c>
       <c r="X20" s="51" t="inlineStr">
@@ -27001,21 +27001,21 @@
       </c>
       <c r="AC20" s="52" t="n"/>
       <c r="AD20" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC20/AG20,"")</f>
         <v/>
       </c>
       <c r="AE20" s="52" t="n"/>
       <c r="AF20" s="52" t="n"/>
       <c r="AG20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L20="","",L20-N(AC20))</f>
         <v/>
       </c>
       <c r="AH20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L20="","",L20-N(AE20)-N(AF20))</f>
         <v/>
       </c>
       <c r="AI20" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH20/L20,"")</f>
         <v/>
       </c>
       <c r="AJ20" s="54" t="n"/>
@@ -27029,7 +27029,7 @@
         <v>46247</v>
       </c>
       <c r="B21" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A21="","",EOMONTH(A21,0))</f>
         <v/>
       </c>
       <c r="C21" s="50">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="G21" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F21="","",IF(COUNTIF(lst_Jobs,F21&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H21" s="51" t="inlineStr">
@@ -27079,11 +27079,11 @@
         <v>-332.5</v>
       </c>
       <c r="M21" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L21="","",IF(K21="GST 10%",ROUND(L21*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L21="","",L21+M21)</f>
         <v/>
       </c>
       <c r="O21" s="51" t="inlineStr">
@@ -27109,15 +27109,15 @@
       <c r="S21" s="51" t="n"/>
       <c r="T21" s="52" t="n"/>
       <c r="U21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L21="","",L21-N(T21))</f>
         <v/>
       </c>
       <c r="V21" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L21="","",IF(SIGN(N(T21))*SIGN(L21)=-1,"CHECK - video sign",IF(ABS(N(T21))&gt;ABS(L21),"CHECK - video exceeds invoice",IF(AND(D21="VIDEO",ROUND(N(T21),2)&lt;&gt;ROUND(L21,2)),"CHECK - VIDEO job not fully split",IF(N(T21)=0,"All production",IF(ROUND(N(T21),2)=ROUND(L21,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W21" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L21="","",IF(N(T21)=0,0,ROUND(M21*N(T21)/L21,2)))</f>
         <v/>
       </c>
       <c r="X21" s="51" t="inlineStr">
@@ -27145,21 +27145,21 @@
       </c>
       <c r="AC21" s="52" t="n"/>
       <c r="AD21" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC21/AG21,"")</f>
         <v/>
       </c>
       <c r="AE21" s="52" t="n"/>
       <c r="AF21" s="52" t="n"/>
       <c r="AG21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L21="","",L21-N(AC21))</f>
         <v/>
       </c>
       <c r="AH21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L21="","",L21-N(AE21)-N(AF21))</f>
         <v/>
       </c>
       <c r="AI21" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH21/L21,"")</f>
         <v/>
       </c>
       <c r="AJ21" s="54" t="n"/>
@@ -27173,7 +27173,7 @@
         <v>46247</v>
       </c>
       <c r="B22" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A22="","",EOMONTH(A22,0))</f>
         <v/>
       </c>
       <c r="C22" s="50">
@@ -27196,7 +27196,7 @@
         </is>
       </c>
       <c r="G22" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F22="","",IF(COUNTIF(lst_Jobs,F22&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H22" s="51" t="inlineStr">
@@ -27223,11 +27223,11 @@
         <v>3261</v>
       </c>
       <c r="M22" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L22="","",IF(K22="GST 10%",ROUND(L22*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L22="","",L22+M22)</f>
         <v/>
       </c>
       <c r="O22" s="51" t="inlineStr">
@@ -27255,15 +27255,15 @@
         <v>1029</v>
       </c>
       <c r="U22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L22="","",L22-N(T22))</f>
         <v/>
       </c>
       <c r="V22" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L22="","",IF(SIGN(N(T22))*SIGN(L22)=-1,"CHECK - video sign",IF(ABS(N(T22))&gt;ABS(L22),"CHECK - video exceeds invoice",IF(AND(D22="VIDEO",ROUND(N(T22),2)&lt;&gt;ROUND(L22,2)),"CHECK - VIDEO job not fully split",IF(N(T22)=0,"All production",IF(ROUND(N(T22),2)=ROUND(L22,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W22" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L22="","",IF(N(T22)=0,0,ROUND(M22*N(T22)/L22,2)))</f>
         <v/>
       </c>
       <c r="X22" s="51" t="inlineStr">
@@ -27293,21 +27293,21 @@
         <v>334</v>
       </c>
       <c r="AD22" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC22/AG22,"")</f>
         <v/>
       </c>
       <c r="AE22" s="52" t="n"/>
       <c r="AF22" s="52" t="n"/>
       <c r="AG22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L22="","",L22-N(AC22))</f>
         <v/>
       </c>
       <c r="AH22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L22="","",L22-N(AE22)-N(AF22))</f>
         <v/>
       </c>
       <c r="AI22" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH22/L22,"")</f>
         <v/>
       </c>
       <c r="AJ22" s="54" t="n">
@@ -27325,7 +27325,7 @@
         <v>46247</v>
       </c>
       <c r="B23" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A23="","",EOMONTH(A23,0))</f>
         <v/>
       </c>
       <c r="C23" s="50">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G23" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F23="","",IF(COUNTIF(lst_Jobs,F23&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H23" s="51" t="inlineStr">
@@ -27375,11 +27375,11 @@
         <v>2152.5</v>
       </c>
       <c r="M23" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L23="","",IF(K23="GST 10%",ROUND(L23*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L23="","",L23+M23)</f>
         <v/>
       </c>
       <c r="O23" s="51" t="inlineStr">
@@ -27405,15 +27405,15 @@
       <c r="S23" s="51" t="n"/>
       <c r="T23" s="52" t="n"/>
       <c r="U23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L23="","",L23-N(T23))</f>
         <v/>
       </c>
       <c r="V23" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L23="","",IF(SIGN(N(T23))*SIGN(L23)=-1,"CHECK - video sign",IF(ABS(N(T23))&gt;ABS(L23),"CHECK - video exceeds invoice",IF(AND(D23="VIDEO",ROUND(N(T23),2)&lt;&gt;ROUND(L23,2)),"CHECK - VIDEO job not fully split",IF(N(T23)=0,"All production",IF(ROUND(N(T23),2)=ROUND(L23,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W23" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L23="","",IF(N(T23)=0,0,ROUND(M23*N(T23)/L23,2)))</f>
         <v/>
       </c>
       <c r="X23" s="51" t="inlineStr">
@@ -27443,21 +27443,21 @@
         <v>0</v>
       </c>
       <c r="AD23" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC23/AG23,"")</f>
         <v/>
       </c>
       <c r="AE23" s="52" t="n"/>
       <c r="AF23" s="52" t="n"/>
       <c r="AG23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L23="","",L23-N(AC23))</f>
         <v/>
       </c>
       <c r="AH23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L23="","",L23-N(AE23)-N(AF23))</f>
         <v/>
       </c>
       <c r="AI23" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH23/L23,"")</f>
         <v/>
       </c>
       <c r="AJ23" s="54" t="n"/>
@@ -27473,7 +27473,7 @@
         <v>46247</v>
       </c>
       <c r="B24" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A24="","",EOMONTH(A24,0))</f>
         <v/>
       </c>
       <c r="C24" s="50">
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="G24" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F24="","",IF(COUNTIF(lst_Jobs,F24&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H24" s="51" t="inlineStr">
@@ -27523,11 +27523,11 @@
         <v>1650</v>
       </c>
       <c r="M24" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L24="","",IF(K24="GST 10%",ROUND(L24*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L24="","",L24+M24)</f>
         <v/>
       </c>
       <c r="O24" s="51" t="inlineStr">
@@ -27555,15 +27555,15 @@
         <v>485</v>
       </c>
       <c r="U24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L24="","",L24-N(T24))</f>
         <v/>
       </c>
       <c r="V24" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L24="","",IF(SIGN(N(T24))*SIGN(L24)=-1,"CHECK - video sign",IF(ABS(N(T24))&gt;ABS(L24),"CHECK - video exceeds invoice",IF(AND(D24="VIDEO",ROUND(N(T24),2)&lt;&gt;ROUND(L24,2)),"CHECK - VIDEO job not fully split",IF(N(T24)=0,"All production",IF(ROUND(N(T24),2)=ROUND(L24,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W24" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L24="","",IF(N(T24)=0,0,ROUND(M24*N(T24)/L24,2)))</f>
         <v/>
       </c>
       <c r="X24" s="51" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="AC24" s="52" t="n"/>
       <c r="AD24" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC24/AG24,"")</f>
         <v/>
       </c>
       <c r="AE24" s="52" t="n">
@@ -27599,15 +27599,15 @@
       </c>
       <c r="AF24" s="52" t="n"/>
       <c r="AG24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L24="","",L24-N(AC24))</f>
         <v/>
       </c>
       <c r="AH24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L24="","",L24-N(AE24)-N(AF24))</f>
         <v/>
       </c>
       <c r="AI24" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH24/L24,"")</f>
         <v/>
       </c>
       <c r="AJ24" s="54" t="n">
@@ -27627,7 +27627,7 @@
         <v>46255</v>
       </c>
       <c r="B25" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A25="","",EOMONTH(A25,0))</f>
         <v/>
       </c>
       <c r="C25" s="50">
@@ -27650,7 +27650,7 @@
         </is>
       </c>
       <c r="G25" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F25="","",IF(COUNTIF(lst_Jobs,F25&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H25" s="51" t="inlineStr">
@@ -27677,11 +27677,11 @@
         <v>380</v>
       </c>
       <c r="M25" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L25="","",IF(K25="GST 10%",ROUND(L25*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L25="","",L25+M25)</f>
         <v/>
       </c>
       <c r="O25" s="51" t="inlineStr">
@@ -27707,15 +27707,15 @@
       <c r="S25" s="51" t="n"/>
       <c r="T25" s="52" t="n"/>
       <c r="U25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L25="","",L25-N(T25))</f>
         <v/>
       </c>
       <c r="V25" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L25="","",IF(SIGN(N(T25))*SIGN(L25)=-1,"CHECK - video sign",IF(ABS(N(T25))&gt;ABS(L25),"CHECK - video exceeds invoice",IF(AND(D25="VIDEO",ROUND(N(T25),2)&lt;&gt;ROUND(L25,2)),"CHECK - VIDEO job not fully split",IF(N(T25)=0,"All production",IF(ROUND(N(T25),2)=ROUND(L25,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W25" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L25="","",IF(N(T25)=0,0,ROUND(M25*N(T25)/L25,2)))</f>
         <v/>
       </c>
       <c r="X25" s="51" t="inlineStr">
@@ -27743,21 +27743,21 @@
       </c>
       <c r="AC25" s="52" t="n"/>
       <c r="AD25" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC25/AG25,"")</f>
         <v/>
       </c>
       <c r="AE25" s="52" t="n"/>
       <c r="AF25" s="52" t="n"/>
       <c r="AG25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L25="","",L25-N(AC25))</f>
         <v/>
       </c>
       <c r="AH25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L25="","",L25-N(AE25)-N(AF25))</f>
         <v/>
       </c>
       <c r="AI25" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH25/L25,"")</f>
         <v/>
       </c>
       <c r="AJ25" s="54" t="n"/>
@@ -27773,7 +27773,7 @@
         <v>46255</v>
       </c>
       <c r="B26" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A26="","",EOMONTH(A26,0))</f>
         <v/>
       </c>
       <c r="C26" s="50">
@@ -27796,7 +27796,7 @@
         </is>
       </c>
       <c r="G26" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F26="","",IF(COUNTIF(lst_Jobs,F26&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H26" s="51" t="inlineStr">
@@ -27823,11 +27823,11 @@
         <v>8260.35</v>
       </c>
       <c r="M26" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L26="","",IF(K26="GST 10%",ROUND(L26*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L26="","",L26+M26)</f>
         <v/>
       </c>
       <c r="O26" s="51" t="inlineStr">
@@ -27855,15 +27855,15 @@
         <v>1977.35</v>
       </c>
       <c r="U26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L26="","",L26-N(T26))</f>
         <v/>
       </c>
       <c r="V26" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L26="","",IF(SIGN(N(T26))*SIGN(L26)=-1,"CHECK - video sign",IF(ABS(N(T26))&gt;ABS(L26),"CHECK - video exceeds invoice",IF(AND(D26="VIDEO",ROUND(N(T26),2)&lt;&gt;ROUND(L26,2)),"CHECK - VIDEO job not fully split",IF(N(T26)=0,"All production",IF(ROUND(N(T26),2)=ROUND(L26,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W26" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L26="","",IF(N(T26)=0,0,ROUND(M26*N(T26)/L26,2)))</f>
         <v/>
       </c>
       <c r="X26" s="51" t="inlineStr">
@@ -27893,21 +27893,21 @@
         <v>2104.4</v>
       </c>
       <c r="AD26" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC26/AG26,"")</f>
         <v/>
       </c>
       <c r="AE26" s="52" t="n"/>
       <c r="AF26" s="52" t="n"/>
       <c r="AG26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L26="","",L26-N(AC26))</f>
         <v/>
       </c>
       <c r="AH26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L26="","",L26-N(AE26)-N(AF26))</f>
         <v/>
       </c>
       <c r="AI26" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH26/L26,"")</f>
         <v/>
       </c>
       <c r="AJ26" s="54" t="n">
@@ -27927,7 +27927,7 @@
         <v>46259</v>
       </c>
       <c r="B27" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A27="","",EOMONTH(A27,0))</f>
         <v/>
       </c>
       <c r="C27" s="50">
@@ -27950,7 +27950,7 @@
         </is>
       </c>
       <c r="G27" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F27="","",IF(COUNTIF(lst_Jobs,F27&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H27" s="51" t="inlineStr">
@@ -27977,11 +27977,11 @@
         <v>4300</v>
       </c>
       <c r="M27" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L27="","",IF(K27="GST 10%",ROUND(L27*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L27="","",L27+M27)</f>
         <v/>
       </c>
       <c r="O27" s="51" t="inlineStr">
@@ -28009,15 +28009,15 @@
         <v>1065</v>
       </c>
       <c r="U27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L27="","",L27-N(T27))</f>
         <v/>
       </c>
       <c r="V27" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L27="","",IF(SIGN(N(T27))*SIGN(L27)=-1,"CHECK - video sign",IF(ABS(N(T27))&gt;ABS(L27),"CHECK - video exceeds invoice",IF(AND(D27="VIDEO",ROUND(N(T27),2)&lt;&gt;ROUND(L27,2)),"CHECK - VIDEO job not fully split",IF(N(T27)=0,"All production",IF(ROUND(N(T27),2)=ROUND(L27,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W27" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L27="","",IF(N(T27)=0,0,ROUND(M27*N(T27)/L27,2)))</f>
         <v/>
       </c>
       <c r="X27" s="51" t="inlineStr">
@@ -28045,7 +28045,7 @@
       </c>
       <c r="AC27" s="52" t="n"/>
       <c r="AD27" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC27/AG27,"")</f>
         <v/>
       </c>
       <c r="AE27" s="52" t="n">
@@ -28053,15 +28053,15 @@
       </c>
       <c r="AF27" s="52" t="n"/>
       <c r="AG27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L27="","",L27-N(AC27))</f>
         <v/>
       </c>
       <c r="AH27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L27="","",L27-N(AE27)-N(AF27))</f>
         <v/>
       </c>
       <c r="AI27" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH27/L27,"")</f>
         <v/>
       </c>
       <c r="AJ27" s="54" t="n">
@@ -28079,7 +28079,7 @@
         <v>46259</v>
       </c>
       <c r="B28" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A28="","",EOMONTH(A28,0))</f>
         <v/>
       </c>
       <c r="C28" s="50">
@@ -28102,7 +28102,7 @@
         </is>
       </c>
       <c r="G28" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F28="","",IF(COUNTIF(lst_Jobs,F28&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H28" s="51" t="inlineStr">
@@ -28130,11 +28130,11 @@
         <v>28652.25</v>
       </c>
       <c r="M28" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L28="","",IF(K28="GST 10%",ROUND(L28*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L28="","",L28+M28)</f>
         <v/>
       </c>
       <c r="O28" s="51" t="inlineStr">
@@ -28162,15 +28162,15 @@
         <v>3017</v>
       </c>
       <c r="U28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L28="","",L28-N(T28))</f>
         <v/>
       </c>
       <c r="V28" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L28="","",IF(SIGN(N(T28))*SIGN(L28)=-1,"CHECK - video sign",IF(ABS(N(T28))&gt;ABS(L28),"CHECK - video exceeds invoice",IF(AND(D28="VIDEO",ROUND(N(T28),2)&lt;&gt;ROUND(L28,2)),"CHECK - VIDEO job not fully split",IF(N(T28)=0,"All production",IF(ROUND(N(T28),2)=ROUND(L28,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W28" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L28="","",IF(N(T28)=0,0,ROUND(M28*N(T28)/L28,2)))</f>
         <v/>
       </c>
       <c r="X28" s="51" t="inlineStr">
@@ -28200,7 +28200,7 @@
         <v>5271.5</v>
       </c>
       <c r="AD28" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC28/AG28,"")</f>
         <v/>
       </c>
       <c r="AE28" s="52" t="n">
@@ -28208,15 +28208,15 @@
       </c>
       <c r="AF28" s="52" t="n"/>
       <c r="AG28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L28="","",L28-N(AC28))</f>
         <v/>
       </c>
       <c r="AH28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L28="","",L28-N(AE28)-N(AF28))</f>
         <v/>
       </c>
       <c r="AI28" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH28/L28,"")</f>
         <v/>
       </c>
       <c r="AJ28" s="54" t="n">
@@ -28236,7 +28236,7 @@
         <v>46247</v>
       </c>
       <c r="B29" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A29="","",EOMONTH(A29,0))</f>
         <v/>
       </c>
       <c r="C29" s="50">
@@ -28259,7 +28259,7 @@
         </is>
       </c>
       <c r="G29" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F29="","",IF(COUNTIF(lst_Jobs,F29&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H29" s="51" t="inlineStr">
@@ -28286,11 +28286,11 @@
         <v>12170</v>
       </c>
       <c r="M29" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L29="","",IF(K29="GST 10%",ROUND(L29*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L29="","",L29+M29)</f>
         <v/>
       </c>
       <c r="O29" s="51" t="inlineStr">
@@ -28318,15 +28318,15 @@
         <v>850</v>
       </c>
       <c r="U29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L29="","",L29-N(T29))</f>
         <v/>
       </c>
       <c r="V29" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L29="","",IF(SIGN(N(T29))*SIGN(L29)=-1,"CHECK - video sign",IF(ABS(N(T29))&gt;ABS(L29),"CHECK - video exceeds invoice",IF(AND(D29="VIDEO",ROUND(N(T29),2)&lt;&gt;ROUND(L29,2)),"CHECK - VIDEO job not fully split",IF(N(T29)=0,"All production",IF(ROUND(N(T29),2)=ROUND(L29,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W29" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L29="","",IF(N(T29)=0,0,ROUND(M29*N(T29)/L29,2)))</f>
         <v/>
       </c>
       <c r="X29" s="51" t="inlineStr">
@@ -28356,7 +28356,7 @@
         <v>1680</v>
       </c>
       <c r="AD29" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC29/AG29,"")</f>
         <v/>
       </c>
       <c r="AE29" s="52" t="n">
@@ -28364,15 +28364,15 @@
       </c>
       <c r="AF29" s="52" t="n"/>
       <c r="AG29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L29="","",L29-N(AC29))</f>
         <v/>
       </c>
       <c r="AH29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L29="","",L29-N(AE29)-N(AF29))</f>
         <v/>
       </c>
       <c r="AI29" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH29/L29,"")</f>
         <v/>
       </c>
       <c r="AJ29" s="54" t="n"/>
@@ -28388,7 +28388,7 @@
         <v>46255</v>
       </c>
       <c r="B30" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A30="","",EOMONTH(A30,0))</f>
         <v/>
       </c>
       <c r="C30" s="50">
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="G30" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F30="","",IF(COUNTIF(lst_Jobs,F30&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H30" s="51" t="inlineStr">
@@ -28438,11 +28438,11 @@
         <v>14271.5</v>
       </c>
       <c r="M30" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L30="","",IF(K30="GST 10%",ROUND(L30*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L30="","",L30+M30)</f>
         <v/>
       </c>
       <c r="O30" s="51" t="inlineStr">
@@ -28470,15 +28470,15 @@
         <v>1806</v>
       </c>
       <c r="U30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L30="","",L30-N(T30))</f>
         <v/>
       </c>
       <c r="V30" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L30="","",IF(SIGN(N(T30))*SIGN(L30)=-1,"CHECK - video sign",IF(ABS(N(T30))&gt;ABS(L30),"CHECK - video exceeds invoice",IF(AND(D30="VIDEO",ROUND(N(T30),2)&lt;&gt;ROUND(L30,2)),"CHECK - VIDEO job not fully split",IF(N(T30)=0,"All production",IF(ROUND(N(T30),2)=ROUND(L30,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W30" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L30="","",IF(N(T30)=0,0,ROUND(M30*N(T30)/L30,2)))</f>
         <v/>
       </c>
       <c r="X30" s="51" t="inlineStr">
@@ -28508,7 +28508,7 @@
         <v>2351.5</v>
       </c>
       <c r="AD30" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC30/AG30,"")</f>
         <v/>
       </c>
       <c r="AE30" s="52" t="n">
@@ -28516,15 +28516,15 @@
       </c>
       <c r="AF30" s="52" t="n"/>
       <c r="AG30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L30="","",L30-N(AC30))</f>
         <v/>
       </c>
       <c r="AH30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L30="","",L30-N(AE30)-N(AF30))</f>
         <v/>
       </c>
       <c r="AI30" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH30/L30,"")</f>
         <v/>
       </c>
       <c r="AJ30" s="54" t="n"/>
@@ -28542,7 +28542,7 @@
         <v>46255</v>
       </c>
       <c r="B31" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A31="","",EOMONTH(A31,0))</f>
         <v/>
       </c>
       <c r="C31" s="50">
@@ -28565,7 +28565,7 @@
         </is>
       </c>
       <c r="G31" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F31="","",IF(COUNTIF(lst_Jobs,F31&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H31" s="51" t="inlineStr">
@@ -28592,11 +28592,11 @@
         <v>7148.75</v>
       </c>
       <c r="M31" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L31="","",IF(K31="GST 10%",ROUND(L31*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L31="","",L31+M31)</f>
         <v/>
       </c>
       <c r="O31" s="51" t="inlineStr">
@@ -28622,15 +28622,15 @@
       <c r="S31" s="51" t="n"/>
       <c r="T31" s="52" t="n"/>
       <c r="U31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L31="","",L31-N(T31))</f>
         <v/>
       </c>
       <c r="V31" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L31="","",IF(SIGN(N(T31))*SIGN(L31)=-1,"CHECK - video sign",IF(ABS(N(T31))&gt;ABS(L31),"CHECK - video exceeds invoice",IF(AND(D31="VIDEO",ROUND(N(T31),2)&lt;&gt;ROUND(L31,2)),"CHECK - VIDEO job not fully split",IF(N(T31)=0,"All production",IF(ROUND(N(T31),2)=ROUND(L31,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W31" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L31="","",IF(N(T31)=0,0,ROUND(M31*N(T31)/L31,2)))</f>
         <v/>
       </c>
       <c r="X31" s="51" t="inlineStr">
@@ -28660,7 +28660,7 @@
         <v>1309.25</v>
       </c>
       <c r="AD31" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC31/AG31,"")</f>
         <v/>
       </c>
       <c r="AE31" s="52" t="n">
@@ -28668,15 +28668,15 @@
       </c>
       <c r="AF31" s="52" t="n"/>
       <c r="AG31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L31="","",L31-N(AC31))</f>
         <v/>
       </c>
       <c r="AH31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L31="","",L31-N(AE31)-N(AF31))</f>
         <v/>
       </c>
       <c r="AI31" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH31/L31,"")</f>
         <v/>
       </c>
       <c r="AJ31" s="54" t="n">
@@ -28694,7 +28694,7 @@
         <v>46255</v>
       </c>
       <c r="B32" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A32="","",EOMONTH(A32,0))</f>
         <v/>
       </c>
       <c r="C32" s="50">
@@ -28717,7 +28717,7 @@
         </is>
       </c>
       <c r="G32" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F32="","",IF(COUNTIF(lst_Jobs,F32&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H32" s="51" t="inlineStr">
@@ -28744,11 +28744,11 @@
         <v>1510</v>
       </c>
       <c r="M32" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L32="","",IF(K32="GST 10%",ROUND(L32*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L32="","",L32+M32)</f>
         <v/>
       </c>
       <c r="O32" s="51" t="inlineStr">
@@ -28776,15 +28776,15 @@
         <v>485</v>
       </c>
       <c r="U32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L32="","",L32-N(T32))</f>
         <v/>
       </c>
       <c r="V32" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L32="","",IF(SIGN(N(T32))*SIGN(L32)=-1,"CHECK - video sign",IF(ABS(N(T32))&gt;ABS(L32),"CHECK - video exceeds invoice",IF(AND(D32="VIDEO",ROUND(N(T32),2)&lt;&gt;ROUND(L32,2)),"CHECK - VIDEO job not fully split",IF(N(T32)=0,"All production",IF(ROUND(N(T32),2)=ROUND(L32,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W32" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L32="","",IF(N(T32)=0,0,ROUND(M32*N(T32)/L32,2)))</f>
         <v/>
       </c>
       <c r="X32" s="51" t="inlineStr">
@@ -28814,21 +28814,21 @@
         <v>25</v>
       </c>
       <c r="AD32" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC32/AG32,"")</f>
         <v/>
       </c>
       <c r="AE32" s="52" t="n"/>
       <c r="AF32" s="52" t="n"/>
       <c r="AG32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L32="","",L32-N(AC32))</f>
         <v/>
       </c>
       <c r="AH32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L32="","",L32-N(AE32)-N(AF32))</f>
         <v/>
       </c>
       <c r="AI32" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH32/L32,"")</f>
         <v/>
       </c>
       <c r="AJ32" s="54" t="n">
@@ -28848,7 +28848,7 @@
         <v>46255</v>
       </c>
       <c r="B33" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A33="","",EOMONTH(A33,0))</f>
         <v/>
       </c>
       <c r="C33" s="50">
@@ -28871,7 +28871,7 @@
         </is>
       </c>
       <c r="G33" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F33="","",IF(COUNTIF(lst_Jobs,F33&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H33" s="51" t="inlineStr">
@@ -28898,11 +28898,11 @@
         <v>37579</v>
       </c>
       <c r="M33" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L33="","",IF(K33="GST 10%",ROUND(L33*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L33="","",L33+M33)</f>
         <v/>
       </c>
       <c r="O33" s="51" t="inlineStr">
@@ -28930,15 +28930,15 @@
         <v>3357</v>
       </c>
       <c r="U33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L33="","",L33-N(T33))</f>
         <v/>
       </c>
       <c r="V33" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L33="","",IF(SIGN(N(T33))*SIGN(L33)=-1,"CHECK - video sign",IF(ABS(N(T33))&gt;ABS(L33),"CHECK - video exceeds invoice",IF(AND(D33="VIDEO",ROUND(N(T33),2)&lt;&gt;ROUND(L33,2)),"CHECK - VIDEO job not fully split",IF(N(T33)=0,"All production",IF(ROUND(N(T33),2)=ROUND(L33,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W33" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L33="","",IF(N(T33)=0,0,ROUND(M33*N(T33)/L33,2)))</f>
         <v/>
       </c>
       <c r="X33" s="51" t="inlineStr">
@@ -28968,7 +28968,7 @@
         <v>2181</v>
       </c>
       <c r="AD33" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC33/AG33,"")</f>
         <v/>
       </c>
       <c r="AE33" s="52" t="n">
@@ -28976,15 +28976,15 @@
       </c>
       <c r="AF33" s="52" t="n"/>
       <c r="AG33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L33="","",L33-N(AC33))</f>
         <v/>
       </c>
       <c r="AH33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L33="","",L33-N(AE33)-N(AF33))</f>
         <v/>
       </c>
       <c r="AI33" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH33/L33,"")</f>
         <v/>
       </c>
       <c r="AJ33" s="54" t="n"/>
@@ -29002,7 +29002,7 @@
         <v>46261</v>
       </c>
       <c r="B34" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A34="","",EOMONTH(A34,0))</f>
         <v/>
       </c>
       <c r="C34" s="50">
@@ -29025,7 +29025,7 @@
         </is>
       </c>
       <c r="G34" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F34="","",IF(COUNTIF(lst_Jobs,F34&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H34" s="51" t="inlineStr">
@@ -29052,11 +29052,11 @@
         <v>4601.7</v>
       </c>
       <c r="M34" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L34="","",IF(K34="GST 10%",ROUND(L34*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L34="","",L34+M34)</f>
         <v/>
       </c>
       <c r="O34" s="51" t="inlineStr">
@@ -29084,15 +29084,15 @@
         <v>4221.7</v>
       </c>
       <c r="U34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L34="","",L34-N(T34))</f>
         <v/>
       </c>
       <c r="V34" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L34="","",IF(SIGN(N(T34))*SIGN(L34)=-1,"CHECK - video sign",IF(ABS(N(T34))&gt;ABS(L34),"CHECK - video exceeds invoice",IF(AND(D34="VIDEO",ROUND(N(T34),2)&lt;&gt;ROUND(L34,2)),"CHECK - VIDEO job not fully split",IF(N(T34)=0,"All production",IF(ROUND(N(T34),2)=ROUND(L34,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W34" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L34="","",IF(N(T34)=0,0,ROUND(M34*N(T34)/L34,2)))</f>
         <v/>
       </c>
       <c r="X34" s="51" t="inlineStr">
@@ -29122,21 +29122,21 @@
         <v>148.8</v>
       </c>
       <c r="AD34" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC34/AG34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="52" t="n"/>
       <c r="AF34" s="52" t="n"/>
       <c r="AG34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L34="","",L34-N(AC34))</f>
         <v/>
       </c>
       <c r="AH34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L34="","",L34-N(AE34)-N(AF34))</f>
         <v/>
       </c>
       <c r="AI34" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH34/L34,"")</f>
         <v/>
       </c>
       <c r="AJ34" s="54" t="n">
@@ -29156,7 +29156,7 @@
         <v>46265</v>
       </c>
       <c r="B35" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A35="","",EOMONTH(A35,0))</f>
         <v/>
       </c>
       <c r="C35" s="50">
@@ -29179,7 +29179,7 @@
         </is>
       </c>
       <c r="G35" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F35="","",IF(COUNTIF(lst_Jobs,F35&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H35" s="51" t="inlineStr">
@@ -29206,11 +29206,11 @@
         <v>10540.5</v>
       </c>
       <c r="M35" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L35="","",IF(K35="GST 10%",ROUND(L35*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L35="","",L35+M35)</f>
         <v/>
       </c>
       <c r="O35" s="51" t="inlineStr">
@@ -29236,15 +29236,15 @@
       <c r="S35" s="51" t="n"/>
       <c r="T35" s="52" t="n"/>
       <c r="U35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L35="","",L35-N(T35))</f>
         <v/>
       </c>
       <c r="V35" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L35="","",IF(SIGN(N(T35))*SIGN(L35)=-1,"CHECK - video sign",IF(ABS(N(T35))&gt;ABS(L35),"CHECK - video exceeds invoice",IF(AND(D35="VIDEO",ROUND(N(T35),2)&lt;&gt;ROUND(L35,2)),"CHECK - VIDEO job not fully split",IF(N(T35)=0,"All production",IF(ROUND(N(T35),2)=ROUND(L35,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W35" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L35="","",IF(N(T35)=0,0,ROUND(M35*N(T35)/L35,2)))</f>
         <v/>
       </c>
       <c r="X35" s="51" t="inlineStr">
@@ -29274,7 +29274,7 @@
         <v>2984.5</v>
       </c>
       <c r="AD35" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC35/AG35,"")</f>
         <v/>
       </c>
       <c r="AE35" s="52" t="n">
@@ -29282,15 +29282,15 @@
       </c>
       <c r="AF35" s="52" t="n"/>
       <c r="AG35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L35="","",L35-N(AC35))</f>
         <v/>
       </c>
       <c r="AH35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L35="","",L35-N(AE35)-N(AF35))</f>
         <v/>
       </c>
       <c r="AI35" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH35/L35,"")</f>
         <v/>
       </c>
       <c r="AJ35" s="54" t="n">
@@ -29308,7 +29308,7 @@
         <v>46260</v>
       </c>
       <c r="B36" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A36="","",EOMONTH(A36,0))</f>
         <v/>
       </c>
       <c r="C36" s="50">
@@ -29331,7 +29331,7 @@
         </is>
       </c>
       <c r="G36" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F36="","",IF(COUNTIF(lst_Jobs,F36&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H36" s="51" t="inlineStr">
@@ -29358,11 +29358,11 @@
         <v>2732.5</v>
       </c>
       <c r="M36" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L36="","",IF(K36="GST 10%",ROUND(L36*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L36="","",L36+M36)</f>
         <v/>
       </c>
       <c r="O36" s="51" t="inlineStr">
@@ -29388,15 +29388,15 @@
       <c r="S36" s="51" t="n"/>
       <c r="T36" s="52" t="n"/>
       <c r="U36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L36="","",L36-N(T36))</f>
         <v/>
       </c>
       <c r="V36" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L36="","",IF(SIGN(N(T36))*SIGN(L36)=-1,"CHECK - video sign",IF(ABS(N(T36))&gt;ABS(L36),"CHECK - video exceeds invoice",IF(AND(D36="VIDEO",ROUND(N(T36),2)&lt;&gt;ROUND(L36,2)),"CHECK - VIDEO job not fully split",IF(N(T36)=0,"All production",IF(ROUND(N(T36),2)=ROUND(L36,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W36" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L36="","",IF(N(T36)=0,0,ROUND(M36*N(T36)/L36,2)))</f>
         <v/>
       </c>
       <c r="X36" s="51" t="inlineStr">
@@ -29426,21 +29426,21 @@
         <v>95</v>
       </c>
       <c r="AD36" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC36/AG36,"")</f>
         <v/>
       </c>
       <c r="AE36" s="52" t="n"/>
       <c r="AF36" s="52" t="n"/>
       <c r="AG36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L36="","",L36-N(AC36))</f>
         <v/>
       </c>
       <c r="AH36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L36="","",L36-N(AE36)-N(AF36))</f>
         <v/>
       </c>
       <c r="AI36" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH36/L36,"")</f>
         <v/>
       </c>
       <c r="AJ36" s="54" t="n"/>
@@ -29456,7 +29456,7 @@
         <v>46260</v>
       </c>
       <c r="B37" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A37="","",EOMONTH(A37,0))</f>
         <v/>
       </c>
       <c r="C37" s="50">
@@ -29479,7 +29479,7 @@
         </is>
       </c>
       <c r="G37" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F37="","",IF(COUNTIF(lst_Jobs,F37&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H37" s="51" t="inlineStr">
@@ -29506,11 +29506,11 @@
         <v>460</v>
       </c>
       <c r="M37" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L37="","",IF(K37="GST 10%",ROUND(L37*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L37="","",L37+M37)</f>
         <v/>
       </c>
       <c r="O37" s="51" t="inlineStr">
@@ -29536,15 +29536,15 @@
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="52" t="n"/>
       <c r="U37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L37="","",L37-N(T37))</f>
         <v/>
       </c>
       <c r="V37" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L37="","",IF(SIGN(N(T37))*SIGN(L37)=-1,"CHECK - video sign",IF(ABS(N(T37))&gt;ABS(L37),"CHECK - video exceeds invoice",IF(AND(D37="VIDEO",ROUND(N(T37),2)&lt;&gt;ROUND(L37,2)),"CHECK - VIDEO job not fully split",IF(N(T37)=0,"All production",IF(ROUND(N(T37),2)=ROUND(L37,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W37" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L37="","",IF(N(T37)=0,0,ROUND(M37*N(T37)/L37,2)))</f>
         <v/>
       </c>
       <c r="X37" s="51" t="inlineStr">
@@ -29572,21 +29572,21 @@
       </c>
       <c r="AC37" s="52" t="n"/>
       <c r="AD37" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC37/AG37,"")</f>
         <v/>
       </c>
       <c r="AE37" s="52" t="n"/>
       <c r="AF37" s="52" t="n"/>
       <c r="AG37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L37="","",L37-N(AC37))</f>
         <v/>
       </c>
       <c r="AH37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L37="","",L37-N(AE37)-N(AF37))</f>
         <v/>
       </c>
       <c r="AI37" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH37/L37,"")</f>
         <v/>
       </c>
       <c r="AJ37" s="54" t="n"/>
@@ -29602,7 +29602,7 @@
         <v>46259</v>
       </c>
       <c r="B38" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A38="","",EOMONTH(A38,0))</f>
         <v/>
       </c>
       <c r="C38" s="50">
@@ -29625,7 +29625,7 @@
         </is>
       </c>
       <c r="G38" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F38="","",IF(COUNTIF(lst_Jobs,F38&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H38" s="51" t="inlineStr">
@@ -29652,11 +29652,11 @@
         <v>13661</v>
       </c>
       <c r="M38" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L38="","",IF(K38="GST 10%",ROUND(L38*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L38="","",L38+M38)</f>
         <v/>
       </c>
       <c r="O38" s="51" t="inlineStr">
@@ -29684,15 +29684,15 @@
         <v>674</v>
       </c>
       <c r="U38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L38="","",L38-N(T38))</f>
         <v/>
       </c>
       <c r="V38" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L38="","",IF(SIGN(N(T38))*SIGN(L38)=-1,"CHECK - video sign",IF(ABS(N(T38))&gt;ABS(L38),"CHECK - video exceeds invoice",IF(AND(D38="VIDEO",ROUND(N(T38),2)&lt;&gt;ROUND(L38,2)),"CHECK - VIDEO job not fully split",IF(N(T38)=0,"All production",IF(ROUND(N(T38),2)=ROUND(L38,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W38" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L38="","",IF(N(T38)=0,0,ROUND(M38*N(T38)/L38,2)))</f>
         <v/>
       </c>
       <c r="X38" s="51" t="inlineStr">
@@ -29722,7 +29722,7 @@
         <v>611.5</v>
       </c>
       <c r="AD38" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC38/AG38,"")</f>
         <v/>
       </c>
       <c r="AE38" s="52" t="n">
@@ -29730,15 +29730,15 @@
       </c>
       <c r="AF38" s="52" t="n"/>
       <c r="AG38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L38="","",L38-N(AC38))</f>
         <v/>
       </c>
       <c r="AH38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L38="","",L38-N(AE38)-N(AF38))</f>
         <v/>
       </c>
       <c r="AI38" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH38/L38,"")</f>
         <v/>
       </c>
       <c r="AJ38" s="54" t="n"/>
@@ -29758,7 +29758,7 @@
         <v>46259</v>
       </c>
       <c r="B39" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A39="","",EOMONTH(A39,0))</f>
         <v/>
       </c>
       <c r="C39" s="50">
@@ -29781,7 +29781,7 @@
         </is>
       </c>
       <c r="G39" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F39="","",IF(COUNTIF(lst_Jobs,F39&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H39" s="51" t="inlineStr">
@@ -29808,11 +29808,11 @@
         <v>11644.25</v>
       </c>
       <c r="M39" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L39="","",IF(K39="GST 10%",ROUND(L39*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N39" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L39="","",L39+M39)</f>
         <v/>
       </c>
       <c r="O39" s="51" t="inlineStr">
@@ -29840,15 +29840,15 @@
         <v>263.5</v>
       </c>
       <c r="U39" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L39="","",L39-N(T39))</f>
         <v/>
       </c>
       <c r="V39" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L39="","",IF(SIGN(N(T39))*SIGN(L39)=-1,"CHECK - video sign",IF(ABS(N(T39))&gt;ABS(L39),"CHECK - video exceeds invoice",IF(AND(D39="VIDEO",ROUND(N(T39),2)&lt;&gt;ROUND(L39,2)),"CHECK - VIDEO job not fully split",IF(N(T39)=0,"All production",IF(ROUND(N(T39),2)=ROUND(L39,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W39" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L39="","",IF(N(T39)=0,0,ROUND(M39*N(T39)/L39,2)))</f>
         <v/>
       </c>
       <c r="X39" s="51" t="inlineStr">
@@ -29878,7 +29878,7 @@
         <v>885.75</v>
       </c>
       <c r="AD39" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC39/AG39,"")</f>
         <v/>
       </c>
       <c r="AE39" s="52" t="n">
@@ -29886,15 +29886,15 @@
       </c>
       <c r="AF39" s="52" t="n"/>
       <c r="AG39" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L39="","",L39-N(AC39))</f>
         <v/>
       </c>
       <c r="AH39" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L39="","",L39-N(AE39)-N(AF39))</f>
         <v/>
       </c>
       <c r="AI39" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH39/L39,"")</f>
         <v/>
       </c>
       <c r="AJ39" s="54" t="n"/>
@@ -29912,7 +29912,7 @@
         <v>46260</v>
       </c>
       <c r="B40" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A40="","",EOMONTH(A40,0))</f>
         <v/>
       </c>
       <c r="C40" s="50">
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="G40" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F40="","",IF(COUNTIF(lst_Jobs,F40&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H40" s="51" t="inlineStr">
@@ -29962,11 +29962,11 @@
         <v>1055</v>
       </c>
       <c r="M40" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L40="","",IF(K40="GST 10%",ROUND(L40*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N40" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L40="","",L40+M40)</f>
         <v/>
       </c>
       <c r="O40" s="51" t="inlineStr">
@@ -29992,15 +29992,15 @@
       <c r="S40" s="51" t="n"/>
       <c r="T40" s="52" t="n"/>
       <c r="U40" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L40="","",L40-N(T40))</f>
         <v/>
       </c>
       <c r="V40" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L40="","",IF(SIGN(N(T40))*SIGN(L40)=-1,"CHECK - video sign",IF(ABS(N(T40))&gt;ABS(L40),"CHECK - video exceeds invoice",IF(AND(D40="VIDEO",ROUND(N(T40),2)&lt;&gt;ROUND(L40,2)),"CHECK - VIDEO job not fully split",IF(N(T40)=0,"All production",IF(ROUND(N(T40),2)=ROUND(L40,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W40" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L40="","",IF(N(T40)=0,0,ROUND(M40*N(T40)/L40,2)))</f>
         <v/>
       </c>
       <c r="X40" s="51" t="inlineStr">
@@ -30028,21 +30028,21 @@
       </c>
       <c r="AC40" s="52" t="n"/>
       <c r="AD40" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC40/AG40,"")</f>
         <v/>
       </c>
       <c r="AE40" s="52" t="n"/>
       <c r="AF40" s="52" t="n"/>
       <c r="AG40" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L40="","",L40-N(AC40))</f>
         <v/>
       </c>
       <c r="AH40" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L40="","",L40-N(AE40)-N(AF40))</f>
         <v/>
       </c>
       <c r="AI40" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH40/L40,"")</f>
         <v/>
       </c>
       <c r="AJ40" s="54" t="n"/>
@@ -30058,7 +30058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="48" t="n"/>
       <c r="B41" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A41="","",EOMONTH(A41,0))</f>
         <v/>
       </c>
       <c r="C41" s="50">
@@ -30081,7 +30081,7 @@
         </is>
       </c>
       <c r="G41" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F41="","",IF(COUNTIF(lst_Jobs,F41&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H41" s="51" t="inlineStr">
@@ -30108,11 +30108,11 @@
         <v>8472.5</v>
       </c>
       <c r="M41" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L41="","",IF(K41="GST 10%",ROUND(L41*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N41" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L41="","",L41+M41)</f>
         <v/>
       </c>
       <c r="O41" s="51" t="inlineStr">
@@ -30138,15 +30138,15 @@
       <c r="S41" s="51" t="n"/>
       <c r="T41" s="52" t="n"/>
       <c r="U41" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L41="","",L41-N(T41))</f>
         <v/>
       </c>
       <c r="V41" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L41="","",IF(SIGN(N(T41))*SIGN(L41)=-1,"CHECK - video sign",IF(ABS(N(T41))&gt;ABS(L41),"CHECK - video exceeds invoice",IF(AND(D41="VIDEO",ROUND(N(T41),2)&lt;&gt;ROUND(L41,2)),"CHECK - VIDEO job not fully split",IF(N(T41)=0,"All production",IF(ROUND(N(T41),2)=ROUND(L41,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W41" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L41="","",IF(N(T41)=0,0,ROUND(M41*N(T41)/L41,2)))</f>
         <v/>
       </c>
       <c r="X41" s="51" t="inlineStr">
@@ -30176,7 +30176,7 @@
         <v>3652.5</v>
       </c>
       <c r="AD41" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC41/AG41,"")</f>
         <v/>
       </c>
       <c r="AE41" s="52" t="n">
@@ -30184,15 +30184,15 @@
       </c>
       <c r="AF41" s="52" t="n"/>
       <c r="AG41" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L41="","",L41-N(AC41))</f>
         <v/>
       </c>
       <c r="AH41" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L41="","",L41-N(AE41)-N(AF41))</f>
         <v/>
       </c>
       <c r="AI41" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH41/L41,"")</f>
         <v/>
       </c>
       <c r="AJ41" s="54" t="n"/>
@@ -30208,7 +30208,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="48" t="n"/>
       <c r="B42" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A42="","",EOMONTH(A42,0))</f>
         <v/>
       </c>
       <c r="C42" s="50">
@@ -30231,7 +30231,7 @@
         </is>
       </c>
       <c r="G42" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F42="","",IF(COUNTIF(lst_Jobs,F42&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H42" s="51" t="inlineStr">
@@ -30258,11 +30258,11 @@
         <v>12600.6</v>
       </c>
       <c r="M42" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L42="","",IF(K42="GST 10%",ROUND(L42*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N42" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L42="","",L42+M42)</f>
         <v/>
       </c>
       <c r="O42" s="51" t="inlineStr">
@@ -30290,15 +30290,15 @@
         <v>1261.6</v>
       </c>
       <c r="U42" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L42="","",L42-N(T42))</f>
         <v/>
       </c>
       <c r="V42" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L42="","",IF(SIGN(N(T42))*SIGN(L42)=-1,"CHECK - video sign",IF(ABS(N(T42))&gt;ABS(L42),"CHECK - video exceeds invoice",IF(AND(D42="VIDEO",ROUND(N(T42),2)&lt;&gt;ROUND(L42,2)),"CHECK - VIDEO job not fully split",IF(N(T42)=0,"All production",IF(ROUND(N(T42),2)=ROUND(L42,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W42" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L42="","",IF(N(T42)=0,0,ROUND(M42*N(T42)/L42,2)))</f>
         <v/>
       </c>
       <c r="X42" s="51" t="inlineStr">
@@ -30328,21 +30328,21 @@
         <v>1651.4</v>
       </c>
       <c r="AD42" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC42/AG42,"")</f>
         <v/>
       </c>
       <c r="AE42" s="52" t="n"/>
       <c r="AF42" s="52" t="n"/>
       <c r="AG42" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L42="","",L42-N(AC42))</f>
         <v/>
       </c>
       <c r="AH42" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L42="","",L42-N(AE42)-N(AF42))</f>
         <v/>
       </c>
       <c r="AI42" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH42/L42,"")</f>
         <v/>
       </c>
       <c r="AJ42" s="54" t="n">
@@ -30362,7 +30362,7 @@
         <v>46265</v>
       </c>
       <c r="B43" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A43="","",EOMONTH(A43,0))</f>
         <v/>
       </c>
       <c r="C43" s="50">
@@ -30385,7 +30385,7 @@
         </is>
       </c>
       <c r="G43" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F43="","",IF(COUNTIF(lst_Jobs,F43&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H43" s="51" t="inlineStr">
@@ -30412,11 +30412,11 @@
         <v>13401.5</v>
       </c>
       <c r="M43" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L43="","",IF(K43="GST 10%",ROUND(L43*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N43" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L43="","",L43+M43)</f>
         <v/>
       </c>
       <c r="O43" s="51" t="inlineStr">
@@ -30444,15 +30444,15 @@
         <v>1771</v>
       </c>
       <c r="U43" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L43="","",L43-N(T43))</f>
         <v/>
       </c>
       <c r="V43" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L43="","",IF(SIGN(N(T43))*SIGN(L43)=-1,"CHECK - video sign",IF(ABS(N(T43))&gt;ABS(L43),"CHECK - video exceeds invoice",IF(AND(D43="VIDEO",ROUND(N(T43),2)&lt;&gt;ROUND(L43,2)),"CHECK - VIDEO job not fully split",IF(N(T43)=0,"All production",IF(ROUND(N(T43),2)=ROUND(L43,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W43" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L43="","",IF(N(T43)=0,0,ROUND(M43*N(T43)/L43,2)))</f>
         <v/>
       </c>
       <c r="X43" s="51" t="inlineStr">
@@ -30482,7 +30482,7 @@
         <v>524.5</v>
       </c>
       <c r="AD43" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC43/AG43,"")</f>
         <v/>
       </c>
       <c r="AE43" s="52" t="n">
@@ -30490,15 +30490,15 @@
       </c>
       <c r="AF43" s="52" t="n"/>
       <c r="AG43" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L43="","",L43-N(AC43))</f>
         <v/>
       </c>
       <c r="AH43" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L43="","",L43-N(AE43)-N(AF43))</f>
         <v/>
       </c>
       <c r="AI43" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH43/L43,"")</f>
         <v/>
       </c>
       <c r="AJ43" s="54" t="n">
@@ -30516,7 +30516,7 @@
         <v>46265</v>
       </c>
       <c r="B44" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A44="","",EOMONTH(A44,0))</f>
         <v/>
       </c>
       <c r="C44" s="50">
@@ -30539,7 +30539,7 @@
         </is>
       </c>
       <c r="G44" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F44="","",IF(COUNTIF(lst_Jobs,F44&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H44" s="51" t="inlineStr">
@@ -30566,11 +30566,11 @@
         <v>10835.49</v>
       </c>
       <c r="M44" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L44="","",IF(K44="GST 10%",ROUND(L44*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N44" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L44="","",L44+M44)</f>
         <v/>
       </c>
       <c r="O44" s="51" t="inlineStr">
@@ -30596,15 +30596,15 @@
       <c r="S44" s="51" t="n"/>
       <c r="T44" s="52" t="n"/>
       <c r="U44" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L44="","",L44-N(T44))</f>
         <v/>
       </c>
       <c r="V44" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L44="","",IF(SIGN(N(T44))*SIGN(L44)=-1,"CHECK - video sign",IF(ABS(N(T44))&gt;ABS(L44),"CHECK - video exceeds invoice",IF(AND(D44="VIDEO",ROUND(N(T44),2)&lt;&gt;ROUND(L44,2)),"CHECK - VIDEO job not fully split",IF(N(T44)=0,"All production",IF(ROUND(N(T44),2)=ROUND(L44,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W44" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L44="","",IF(N(T44)=0,0,ROUND(M44*N(T44)/L44,2)))</f>
         <v/>
       </c>
       <c r="X44" s="51" t="inlineStr">
@@ -30634,7 +30634,7 @@
         <v>495</v>
       </c>
       <c r="AD44" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC44/AG44,"")</f>
         <v/>
       </c>
       <c r="AE44" s="52" t="n">
@@ -30642,15 +30642,15 @@
       </c>
       <c r="AF44" s="52" t="n"/>
       <c r="AG44" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L44="","",L44-N(AC44))</f>
         <v/>
       </c>
       <c r="AH44" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L44="","",L44-N(AE44)-N(AF44))</f>
         <v/>
       </c>
       <c r="AI44" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH44/L44,"")</f>
         <v/>
       </c>
       <c r="AJ44" s="54" t="n"/>
@@ -30666,7 +30666,7 @@
         <v>46265</v>
       </c>
       <c r="B45" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A45="","",EOMONTH(A45,0))</f>
         <v/>
       </c>
       <c r="C45" s="50">
@@ -30689,7 +30689,7 @@
         </is>
       </c>
       <c r="G45" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F45="","",IF(COUNTIF(lst_Jobs,F45&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H45" s="51" t="inlineStr">
@@ -30716,11 +30716,11 @@
         <v>24413.75</v>
       </c>
       <c r="M45" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L45="","",IF(K45="GST 10%",ROUND(L45*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N45" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L45="","",L45+M45)</f>
         <v/>
       </c>
       <c r="O45" s="51" t="inlineStr">
@@ -30748,15 +30748,15 @@
         <v>1785</v>
       </c>
       <c r="U45" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L45="","",L45-N(T45))</f>
         <v/>
       </c>
       <c r="V45" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L45="","",IF(SIGN(N(T45))*SIGN(L45)=-1,"CHECK - video sign",IF(ABS(N(T45))&gt;ABS(L45),"CHECK - video exceeds invoice",IF(AND(D45="VIDEO",ROUND(N(T45),2)&lt;&gt;ROUND(L45,2)),"CHECK - VIDEO job not fully split",IF(N(T45)=0,"All production",IF(ROUND(N(T45),2)=ROUND(L45,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W45" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L45="","",IF(N(T45)=0,0,ROUND(M45*N(T45)/L45,2)))</f>
         <v/>
       </c>
       <c r="X45" s="51" t="inlineStr">
@@ -30786,7 +30786,7 @@
         <v>2281.25</v>
       </c>
       <c r="AD45" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC45/AG45,"")</f>
         <v/>
       </c>
       <c r="AE45" s="52" t="n">
@@ -30794,15 +30794,15 @@
       </c>
       <c r="AF45" s="52" t="n"/>
       <c r="AG45" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L45="","",L45-N(AC45))</f>
         <v/>
       </c>
       <c r="AH45" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L45="","",L45-N(AE45)-N(AF45))</f>
         <v/>
       </c>
       <c r="AI45" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH45/L45,"")</f>
         <v/>
       </c>
       <c r="AJ45" s="54" t="n">
@@ -30822,7 +30822,7 @@
         <v>46253</v>
       </c>
       <c r="B46" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A46="","",EOMONTH(A46,0))</f>
         <v/>
       </c>
       <c r="C46" s="50">
@@ -30845,7 +30845,7 @@
         </is>
       </c>
       <c r="G46" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F46="","",IF(COUNTIF(lst_Jobs,F46&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H46" s="51" t="inlineStr">
@@ -30872,11 +30872,11 @@
         <v>13347</v>
       </c>
       <c r="M46" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L46="","",IF(K46="GST 10%",ROUND(L46*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N46" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L46="","",L46+M46)</f>
         <v/>
       </c>
       <c r="O46" s="51" t="inlineStr">
@@ -30904,15 +30904,15 @@
         <v>86.5</v>
       </c>
       <c r="U46" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L46="","",L46-N(T46))</f>
         <v/>
       </c>
       <c r="V46" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L46="","",IF(SIGN(N(T46))*SIGN(L46)=-1,"CHECK - video sign",IF(ABS(N(T46))&gt;ABS(L46),"CHECK - video exceeds invoice",IF(AND(D46="VIDEO",ROUND(N(T46),2)&lt;&gt;ROUND(L46,2)),"CHECK - VIDEO job not fully split",IF(N(T46)=0,"All production",IF(ROUND(N(T46),2)=ROUND(L46,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W46" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L46="","",IF(N(T46)=0,0,ROUND(M46*N(T46)/L46,2)))</f>
         <v/>
       </c>
       <c r="X46" s="51" t="inlineStr">
@@ -30942,7 +30942,7 @@
         <v>3563</v>
       </c>
       <c r="AD46" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC46/AG46,"")</f>
         <v/>
       </c>
       <c r="AE46" s="52" t="n">
@@ -30950,15 +30950,15 @@
       </c>
       <c r="AF46" s="52" t="n"/>
       <c r="AG46" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L46="","",L46-N(AC46))</f>
         <v/>
       </c>
       <c r="AH46" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L46="","",L46-N(AE46)-N(AF46))</f>
         <v/>
       </c>
       <c r="AI46" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH46/L46,"")</f>
         <v/>
       </c>
       <c r="AJ46" s="54" t="n"/>
@@ -30976,7 +30976,7 @@
         <v>46261</v>
       </c>
       <c r="B47" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A47="","",EOMONTH(A47,0))</f>
         <v/>
       </c>
       <c r="C47" s="50">
@@ -30999,7 +30999,7 @@
         </is>
       </c>
       <c r="G47" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F47="","",IF(COUNTIF(lst_Jobs,F47&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H47" s="51" t="inlineStr">
@@ -31026,11 +31026,11 @@
         <v>770</v>
       </c>
       <c r="M47" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L47="","",IF(K47="GST 10%",ROUND(L47*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N47" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L47="","",L47+M47)</f>
         <v/>
       </c>
       <c r="O47" s="51" t="inlineStr">
@@ -31056,15 +31056,15 @@
       <c r="S47" s="51" t="n"/>
       <c r="T47" s="52" t="n"/>
       <c r="U47" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L47="","",L47-N(T47))</f>
         <v/>
       </c>
       <c r="V47" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L47="","",IF(SIGN(N(T47))*SIGN(L47)=-1,"CHECK - video sign",IF(ABS(N(T47))&gt;ABS(L47),"CHECK - video exceeds invoice",IF(AND(D47="VIDEO",ROUND(N(T47),2)&lt;&gt;ROUND(L47,2)),"CHECK - VIDEO job not fully split",IF(N(T47)=0,"All production",IF(ROUND(N(T47),2)=ROUND(L47,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W47" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L47="","",IF(N(T47)=0,0,ROUND(M47*N(T47)/L47,2)))</f>
         <v/>
       </c>
       <c r="X47" s="51" t="inlineStr">
@@ -31094,21 +31094,21 @@
         <v>90</v>
       </c>
       <c r="AD47" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC47/AG47,"")</f>
         <v/>
       </c>
       <c r="AE47" s="52" t="n"/>
       <c r="AF47" s="52" t="n"/>
       <c r="AG47" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L47="","",L47-N(AC47))</f>
         <v/>
       </c>
       <c r="AH47" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L47="","",L47-N(AE47)-N(AF47))</f>
         <v/>
       </c>
       <c r="AI47" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH47/L47,"")</f>
         <v/>
       </c>
       <c r="AJ47" s="54" t="n"/>
@@ -31126,7 +31126,7 @@
         <v>46260</v>
       </c>
       <c r="B48" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A48="","",EOMONTH(A48,0))</f>
         <v/>
       </c>
       <c r="C48" s="50">
@@ -31149,7 +31149,7 @@
         </is>
       </c>
       <c r="G48" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F48="","",IF(COUNTIF(lst_Jobs,F48&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H48" s="51" t="inlineStr">
@@ -31176,11 +31176,11 @@
         <v>380</v>
       </c>
       <c r="M48" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L48="","",IF(K48="GST 10%",ROUND(L48*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N48" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L48="","",L48+M48)</f>
         <v/>
       </c>
       <c r="O48" s="51" t="inlineStr">
@@ -31206,15 +31206,15 @@
       <c r="S48" s="51" t="n"/>
       <c r="T48" s="52" t="n"/>
       <c r="U48" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L48="","",L48-N(T48))</f>
         <v/>
       </c>
       <c r="V48" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L48="","",IF(SIGN(N(T48))*SIGN(L48)=-1,"CHECK - video sign",IF(ABS(N(T48))&gt;ABS(L48),"CHECK - video exceeds invoice",IF(AND(D48="VIDEO",ROUND(N(T48),2)&lt;&gt;ROUND(L48,2)),"CHECK - VIDEO job not fully split",IF(N(T48)=0,"All production",IF(ROUND(N(T48),2)=ROUND(L48,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W48" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L48="","",IF(N(T48)=0,0,ROUND(M48*N(T48)/L48,2)))</f>
         <v/>
       </c>
       <c r="X48" s="51" t="inlineStr">
@@ -31242,21 +31242,21 @@
       </c>
       <c r="AC48" s="52" t="n"/>
       <c r="AD48" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC48/AG48,"")</f>
         <v/>
       </c>
       <c r="AE48" s="52" t="n"/>
       <c r="AF48" s="52" t="n"/>
       <c r="AG48" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L48="","",L48-N(AC48))</f>
         <v/>
       </c>
       <c r="AH48" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L48="","",L48-N(AE48)-N(AF48))</f>
         <v/>
       </c>
       <c r="AI48" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH48/L48,"")</f>
         <v/>
       </c>
       <c r="AJ48" s="54" t="n"/>
@@ -31272,7 +31272,7 @@
         <v>46265</v>
       </c>
       <c r="B49" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A49="","",EOMONTH(A49,0))</f>
         <v/>
       </c>
       <c r="C49" s="50">
@@ -31295,7 +31295,7 @@
         </is>
       </c>
       <c r="G49" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F49="","",IF(COUNTIF(lst_Jobs,F49&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H49" s="51" t="inlineStr">
@@ -31322,11 +31322,11 @@
         <v>830</v>
       </c>
       <c r="M49" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L49="","",IF(K49="GST 10%",ROUND(L49*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N49" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L49="","",L49+M49)</f>
         <v/>
       </c>
       <c r="O49" s="51" t="inlineStr">
@@ -31352,15 +31352,15 @@
       <c r="S49" s="51" t="n"/>
       <c r="T49" s="52" t="n"/>
       <c r="U49" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L49="","",L49-N(T49))</f>
         <v/>
       </c>
       <c r="V49" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L49="","",IF(SIGN(N(T49))*SIGN(L49)=-1,"CHECK - video sign",IF(ABS(N(T49))&gt;ABS(L49),"CHECK - video exceeds invoice",IF(AND(D49="VIDEO",ROUND(N(T49),2)&lt;&gt;ROUND(L49,2)),"CHECK - VIDEO job not fully split",IF(N(T49)=0,"All production",IF(ROUND(N(T49),2)=ROUND(L49,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W49" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L49="","",IF(N(T49)=0,0,ROUND(M49*N(T49)/L49,2)))</f>
         <v/>
       </c>
       <c r="X49" s="51" t="inlineStr">
@@ -31388,7 +31388,7 @@
       </c>
       <c r="AC49" s="52" t="n"/>
       <c r="AD49" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC49/AG49,"")</f>
         <v/>
       </c>
       <c r="AE49" s="52" t="n">
@@ -31396,15 +31396,15 @@
       </c>
       <c r="AF49" s="52" t="n"/>
       <c r="AG49" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L49="","",L49-N(AC49))</f>
         <v/>
       </c>
       <c r="AH49" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L49="","",L49-N(AE49)-N(AF49))</f>
         <v/>
       </c>
       <c r="AI49" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH49/L49,"")</f>
         <v/>
       </c>
       <c r="AJ49" s="54" t="n"/>
@@ -31418,7 +31418,7 @@
         <v>46265</v>
       </c>
       <c r="B50" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A50="","",EOMONTH(A50,0))</f>
         <v/>
       </c>
       <c r="C50" s="50">
@@ -31441,7 +31441,7 @@
         </is>
       </c>
       <c r="G50" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F50="","",IF(COUNTIF(lst_Jobs,F50&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H50" s="51" t="inlineStr">
@@ -31468,11 +31468,11 @@
         <v>13389.5</v>
       </c>
       <c r="M50" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L50="","",IF(K50="GST 10%",ROUND(L50*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N50" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L50="","",L50+M50)</f>
         <v/>
       </c>
       <c r="O50" s="51" t="inlineStr">
@@ -31498,15 +31498,15 @@
       <c r="S50" s="51" t="n"/>
       <c r="T50" s="52" t="n"/>
       <c r="U50" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L50="","",L50-N(T50))</f>
         <v/>
       </c>
       <c r="V50" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L50="","",IF(SIGN(N(T50))*SIGN(L50)=-1,"CHECK - video sign",IF(ABS(N(T50))&gt;ABS(L50),"CHECK - video exceeds invoice",IF(AND(D50="VIDEO",ROUND(N(T50),2)&lt;&gt;ROUND(L50,2)),"CHECK - VIDEO job not fully split",IF(N(T50)=0,"All production",IF(ROUND(N(T50),2)=ROUND(L50,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W50" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L50="","",IF(N(T50)=0,0,ROUND(M50*N(T50)/L50,2)))</f>
         <v/>
       </c>
       <c r="X50" s="51" t="inlineStr">
@@ -31536,7 +31536,7 @@
         <v>3530.5</v>
       </c>
       <c r="AD50" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC50/AG50,"")</f>
         <v/>
       </c>
       <c r="AE50" s="52" t="n">
@@ -31544,15 +31544,15 @@
       </c>
       <c r="AF50" s="52" t="n"/>
       <c r="AG50" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L50="","",L50-N(AC50))</f>
         <v/>
       </c>
       <c r="AH50" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L50="","",L50-N(AE50)-N(AF50))</f>
         <v/>
       </c>
       <c r="AI50" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH50/L50,"")</f>
         <v/>
       </c>
       <c r="AJ50" s="54" t="n"/>
@@ -31570,7 +31570,7 @@
         <v>46265</v>
       </c>
       <c r="B51" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A51="","",EOMONTH(A51,0))</f>
         <v/>
       </c>
       <c r="C51" s="50">
@@ -31593,7 +31593,7 @@
         </is>
       </c>
       <c r="G51" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F51="","",IF(COUNTIF(lst_Jobs,F51&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H51" s="51" t="inlineStr">
@@ -31620,11 +31620,11 @@
         <v>3990</v>
       </c>
       <c r="M51" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L51="","",IF(K51="GST 10%",ROUND(L51*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N51" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L51="","",L51+M51)</f>
         <v/>
       </c>
       <c r="O51" s="51" t="inlineStr">
@@ -31650,15 +31650,15 @@
       <c r="S51" s="51" t="n"/>
       <c r="T51" s="52" t="n"/>
       <c r="U51" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L51="","",L51-N(T51))</f>
         <v/>
       </c>
       <c r="V51" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L51="","",IF(SIGN(N(T51))*SIGN(L51)=-1,"CHECK - video sign",IF(ABS(N(T51))&gt;ABS(L51),"CHECK - video exceeds invoice",IF(AND(D51="VIDEO",ROUND(N(T51),2)&lt;&gt;ROUND(L51,2)),"CHECK - VIDEO job not fully split",IF(N(T51)=0,"All production",IF(ROUND(N(T51),2)=ROUND(L51,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W51" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L51="","",IF(N(T51)=0,0,ROUND(M51*N(T51)/L51,2)))</f>
         <v/>
       </c>
       <c r="X51" s="51" t="inlineStr">
@@ -31686,21 +31686,21 @@
       </c>
       <c r="AC51" s="52" t="n"/>
       <c r="AD51" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC51/AG51,"")</f>
         <v/>
       </c>
       <c r="AE51" s="52" t="n"/>
       <c r="AF51" s="52" t="n"/>
       <c r="AG51" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L51="","",L51-N(AC51))</f>
         <v/>
       </c>
       <c r="AH51" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L51="","",L51-N(AE51)-N(AF51))</f>
         <v/>
       </c>
       <c r="AI51" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH51/L51,"")</f>
         <v/>
       </c>
       <c r="AJ51" s="54" t="n"/>
@@ -31716,7 +31716,7 @@
         <v>46218</v>
       </c>
       <c r="B52" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A52="","",EOMONTH(A52,0))</f>
         <v/>
       </c>
       <c r="C52" s="50">
@@ -31739,7 +31739,7 @@
         </is>
       </c>
       <c r="G52" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F52="","",IF(COUNTIF(lst_Jobs,F52&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H52" s="51" t="inlineStr">
@@ -31766,11 +31766,11 @@
         <v>54051.4</v>
       </c>
       <c r="M52" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L52="","",IF(K52="GST 10%",ROUND(L52*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N52" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L52="","",L52+M52)</f>
         <v/>
       </c>
       <c r="O52" s="51" t="inlineStr">
@@ -31798,15 +31798,15 @@
         <v>4308</v>
       </c>
       <c r="U52" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L52="","",L52-N(T52))</f>
         <v/>
       </c>
       <c r="V52" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L52="","",IF(SIGN(N(T52))*SIGN(L52)=-1,"CHECK - video sign",IF(ABS(N(T52))&gt;ABS(L52),"CHECK - video exceeds invoice",IF(AND(D52="VIDEO",ROUND(N(T52),2)&lt;&gt;ROUND(L52,2)),"CHECK - VIDEO job not fully split",IF(N(T52)=0,"All production",IF(ROUND(N(T52),2)=ROUND(L52,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W52" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L52="","",IF(N(T52)=0,0,ROUND(M52*N(T52)/L52,2)))</f>
         <v/>
       </c>
       <c r="X52" s="51" t="n"/>
@@ -31832,21 +31832,21 @@
       </c>
       <c r="AC52" s="52" t="n"/>
       <c r="AD52" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC52/AG52,"")</f>
         <v/>
       </c>
       <c r="AE52" s="52" t="n"/>
       <c r="AF52" s="52" t="n"/>
       <c r="AG52" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L52="","",L52-N(AC52))</f>
         <v/>
       </c>
       <c r="AH52" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L52="","",L52-N(AE52)-N(AF52))</f>
         <v/>
       </c>
       <c r="AI52" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH52/L52,"")</f>
         <v/>
       </c>
       <c r="AJ52" s="54" t="n"/>
@@ -31860,7 +31860,7 @@
         <v>46216</v>
       </c>
       <c r="B53" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A53="","",EOMONTH(A53,0))</f>
         <v/>
       </c>
       <c r="C53" s="50">
@@ -31883,7 +31883,7 @@
         </is>
       </c>
       <c r="G53" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F53="","",IF(COUNTIF(lst_Jobs,F53&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H53" s="51" t="inlineStr">
@@ -31908,11 +31908,11 @@
       </c>
       <c r="L53" s="52" t="n"/>
       <c r="M53" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L53="","",IF(K53="GST 10%",ROUND(L53*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N53" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L53="","",L53+M53)</f>
         <v/>
       </c>
       <c r="O53" s="51" t="inlineStr">
@@ -31938,15 +31938,15 @@
       <c r="S53" s="51" t="n"/>
       <c r="T53" s="52" t="n"/>
       <c r="U53" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L53="","",L53-N(T53))</f>
         <v/>
       </c>
       <c r="V53" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L53="","",IF(SIGN(N(T53))*SIGN(L53)=-1,"CHECK - video sign",IF(ABS(N(T53))&gt;ABS(L53),"CHECK - video exceeds invoice",IF(AND(D53="VIDEO",ROUND(N(T53),2)&lt;&gt;ROUND(L53,2)),"CHECK - VIDEO job not fully split",IF(N(T53)=0,"All production",IF(ROUND(N(T53),2)=ROUND(L53,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W53" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L53="","",IF(N(T53)=0,0,ROUND(M53*N(T53)/L53,2)))</f>
         <v/>
       </c>
       <c r="X53" s="51" t="inlineStr">
@@ -31972,21 +31972,21 @@
       </c>
       <c r="AC53" s="52" t="n"/>
       <c r="AD53" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC53/AG53,"")</f>
         <v/>
       </c>
       <c r="AE53" s="52" t="n"/>
       <c r="AF53" s="52" t="n"/>
       <c r="AG53" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L53="","",L53-N(AC53))</f>
         <v/>
       </c>
       <c r="AH53" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L53="","",L53-N(AE53)-N(AF53))</f>
         <v/>
       </c>
       <c r="AI53" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH53/L53,"")</f>
         <v/>
       </c>
       <c r="AJ53" s="54" t="n"/>
@@ -32000,7 +32000,7 @@
         <v>46265</v>
       </c>
       <c r="B54" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A54="","",EOMONTH(A54,0))</f>
         <v/>
       </c>
       <c r="C54" s="50">
@@ -32023,7 +32023,7 @@
         </is>
       </c>
       <c r="G54" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F54="","",IF(COUNTIF(lst_Jobs,F54&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H54" s="51" t="inlineStr">
@@ -32048,11 +32048,11 @@
       </c>
       <c r="L54" s="52" t="n"/>
       <c r="M54" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L54="","",IF(K54="GST 10%",ROUND(L54*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N54" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L54="","",L54+M54)</f>
         <v/>
       </c>
       <c r="O54" s="51" t="inlineStr">
@@ -32078,15 +32078,15 @@
       <c r="S54" s="51" t="n"/>
       <c r="T54" s="52" t="n"/>
       <c r="U54" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L54="","",L54-N(T54))</f>
         <v/>
       </c>
       <c r="V54" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L54="","",IF(SIGN(N(T54))*SIGN(L54)=-1,"CHECK - video sign",IF(ABS(N(T54))&gt;ABS(L54),"CHECK - video exceeds invoice",IF(AND(D54="VIDEO",ROUND(N(T54),2)&lt;&gt;ROUND(L54,2)),"CHECK - VIDEO job not fully split",IF(N(T54)=0,"All production",IF(ROUND(N(T54),2)=ROUND(L54,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W54" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L54="","",IF(N(T54)=0,0,ROUND(M54*N(T54)/L54,2)))</f>
         <v/>
       </c>
       <c r="X54" s="51" t="inlineStr">
@@ -32112,21 +32112,21 @@
       </c>
       <c r="AC54" s="52" t="n"/>
       <c r="AD54" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC54/AG54,"")</f>
         <v/>
       </c>
       <c r="AE54" s="52" t="n"/>
       <c r="AF54" s="52" t="n"/>
       <c r="AG54" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L54="","",L54-N(AC54))</f>
         <v/>
       </c>
       <c r="AH54" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L54="","",L54-N(AE54)-N(AF54))</f>
         <v/>
       </c>
       <c r="AI54" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH54/L54,"")</f>
         <v/>
       </c>
       <c r="AJ54" s="54" t="n"/>
@@ -32138,7 +32138,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="48" t="n"/>
       <c r="B55" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A55="","",EOMONTH(A55,0))</f>
         <v/>
       </c>
       <c r="C55" s="50">
@@ -32161,7 +32161,7 @@
         </is>
       </c>
       <c r="G55" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F55="","",IF(COUNTIF(lst_Jobs,F55&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H55" s="51" t="inlineStr">
@@ -32184,11 +32184,11 @@
         <v>4174</v>
       </c>
       <c r="M55" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L55="","",IF(K55="GST 10%",ROUND(L55*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N55" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L55="","",L55+M55)</f>
         <v/>
       </c>
       <c r="O55" s="51" t="inlineStr">
@@ -32216,15 +32216,15 @@
         <v>1500</v>
       </c>
       <c r="U55" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L55="","",L55-N(T55))</f>
         <v/>
       </c>
       <c r="V55" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L55="","",IF(SIGN(N(T55))*SIGN(L55)=-1,"CHECK - video sign",IF(ABS(N(T55))&gt;ABS(L55),"CHECK - video exceeds invoice",IF(AND(D55="VIDEO",ROUND(N(T55),2)&lt;&gt;ROUND(L55,2)),"CHECK - VIDEO job not fully split",IF(N(T55)=0,"All production",IF(ROUND(N(T55),2)=ROUND(L55,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W55" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L55="","",IF(N(T55)=0,0,ROUND(M55*N(T55)/L55,2)))</f>
         <v/>
       </c>
       <c r="X55" s="51" t="inlineStr">
@@ -32254,21 +32254,21 @@
         <v>261</v>
       </c>
       <c r="AD55" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC55/AG55,"")</f>
         <v/>
       </c>
       <c r="AE55" s="52" t="n"/>
       <c r="AF55" s="52" t="n"/>
       <c r="AG55" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L55="","",L55-N(AC55))</f>
         <v/>
       </c>
       <c r="AH55" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L55="","",L55-N(AE55)-N(AF55))</f>
         <v/>
       </c>
       <c r="AI55" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH55/L55,"")</f>
         <v/>
       </c>
       <c r="AJ55" s="54" t="n"/>
@@ -32284,7 +32284,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="48" t="n"/>
       <c r="B56" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A56="","",EOMONTH(A56,0))</f>
         <v/>
       </c>
       <c r="C56" s="50">
@@ -32307,7 +32307,7 @@
         </is>
       </c>
       <c r="G56" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F56="","",IF(COUNTIF(lst_Jobs,F56&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H56" s="51" t="inlineStr">
@@ -32330,11 +32330,11 @@
         <v>7768</v>
       </c>
       <c r="M56" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L56="","",IF(K56="GST 10%",ROUND(L56*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N56" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L56="","",L56+M56)</f>
         <v/>
       </c>
       <c r="O56" s="51" t="inlineStr">
@@ -32362,15 +32362,15 @@
         <v>1508</v>
       </c>
       <c r="U56" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L56="","",L56-N(T56))</f>
         <v/>
       </c>
       <c r="V56" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L56="","",IF(SIGN(N(T56))*SIGN(L56)=-1,"CHECK - video sign",IF(ABS(N(T56))&gt;ABS(L56),"CHECK - video exceeds invoice",IF(AND(D56="VIDEO",ROUND(N(T56),2)&lt;&gt;ROUND(L56,2)),"CHECK - VIDEO job not fully split",IF(N(T56)=0,"All production",IF(ROUND(N(T56),2)=ROUND(L56,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W56" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L56="","",IF(N(T56)=0,0,ROUND(M56*N(T56)/L56,2)))</f>
         <v/>
       </c>
       <c r="X56" s="51" t="inlineStr">
@@ -32400,21 +32400,21 @@
         <v>180</v>
       </c>
       <c r="AD56" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC56/AG56,"")</f>
         <v/>
       </c>
       <c r="AE56" s="52" t="n"/>
       <c r="AF56" s="52" t="n"/>
       <c r="AG56" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L56="","",L56-N(AC56))</f>
         <v/>
       </c>
       <c r="AH56" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L56="","",L56-N(AE56)-N(AF56))</f>
         <v/>
       </c>
       <c r="AI56" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH56/L56,"")</f>
         <v/>
       </c>
       <c r="AJ56" s="54" t="n">
@@ -32430,7 +32430,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="48" t="n"/>
       <c r="B57" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A57="","",EOMONTH(A57,0))</f>
         <v/>
       </c>
       <c r="C57" s="50">
@@ -32453,7 +32453,7 @@
         </is>
       </c>
       <c r="G57" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F57="","",IF(COUNTIF(lst_Jobs,F57&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H57" s="51" t="inlineStr">
@@ -32476,11 +32476,11 @@
         <v>495</v>
       </c>
       <c r="M57" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L57="","",IF(K57="GST 10%",ROUND(L57*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N57" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L57="","",L57+M57)</f>
         <v/>
       </c>
       <c r="O57" s="51" t="inlineStr">
@@ -32506,15 +32506,15 @@
       <c r="S57" s="51" t="n"/>
       <c r="T57" s="52" t="n"/>
       <c r="U57" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L57="","",L57-N(T57))</f>
         <v/>
       </c>
       <c r="V57" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L57="","",IF(SIGN(N(T57))*SIGN(L57)=-1,"CHECK - video sign",IF(ABS(N(T57))&gt;ABS(L57),"CHECK - video exceeds invoice",IF(AND(D57="VIDEO",ROUND(N(T57),2)&lt;&gt;ROUND(L57,2)),"CHECK - VIDEO job not fully split",IF(N(T57)=0,"All production",IF(ROUND(N(T57),2)=ROUND(L57,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W57" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L57="","",IF(N(T57)=0,0,ROUND(M57*N(T57)/L57,2)))</f>
         <v/>
       </c>
       <c r="X57" s="51" t="inlineStr">
@@ -32542,21 +32542,21 @@
       </c>
       <c r="AC57" s="52" t="n"/>
       <c r="AD57" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC57/AG57,"")</f>
         <v/>
       </c>
       <c r="AE57" s="52" t="n"/>
       <c r="AF57" s="52" t="n"/>
       <c r="AG57" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L57="","",L57-N(AC57))</f>
         <v/>
       </c>
       <c r="AH57" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L57="","",L57-N(AE57)-N(AF57))</f>
         <v/>
       </c>
       <c r="AI57" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH57/L57,"")</f>
         <v/>
       </c>
       <c r="AJ57" s="54" t="n"/>
@@ -32574,7 +32574,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="48" t="n"/>
       <c r="B58" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A58="","",EOMONTH(A58,0))</f>
         <v/>
       </c>
       <c r="C58" s="50">
@@ -32597,7 +32597,7 @@
         </is>
       </c>
       <c r="G58" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F58="","",IF(COUNTIF(lst_Jobs,F58&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H58" s="51" t="inlineStr">
@@ -32620,11 +32620,11 @@
         <v>865</v>
       </c>
       <c r="M58" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L58="","",IF(K58="GST 10%",ROUND(L58*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N58" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L58="","",L58+M58)</f>
         <v/>
       </c>
       <c r="O58" s="51" t="inlineStr">
@@ -32650,15 +32650,15 @@
       <c r="S58" s="51" t="n"/>
       <c r="T58" s="52" t="n"/>
       <c r="U58" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L58="","",L58-N(T58))</f>
         <v/>
       </c>
       <c r="V58" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L58="","",IF(SIGN(N(T58))*SIGN(L58)=-1,"CHECK - video sign",IF(ABS(N(T58))&gt;ABS(L58),"CHECK - video exceeds invoice",IF(AND(D58="VIDEO",ROUND(N(T58),2)&lt;&gt;ROUND(L58,2)),"CHECK - VIDEO job not fully split",IF(N(T58)=0,"All production",IF(ROUND(N(T58),2)=ROUND(L58,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W58" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L58="","",IF(N(T58)=0,0,ROUND(M58*N(T58)/L58,2)))</f>
         <v/>
       </c>
       <c r="X58" s="51" t="inlineStr">
@@ -32688,21 +32688,21 @@
         <v>90</v>
       </c>
       <c r="AD58" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC58/AG58,"")</f>
         <v/>
       </c>
       <c r="AE58" s="52" t="n"/>
       <c r="AF58" s="52" t="n"/>
       <c r="AG58" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L58="","",L58-N(AC58))</f>
         <v/>
       </c>
       <c r="AH58" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L58="","",L58-N(AE58)-N(AF58))</f>
         <v/>
       </c>
       <c r="AI58" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH58/L58,"")</f>
         <v/>
       </c>
       <c r="AJ58" s="54" t="n"/>
@@ -32720,7 +32720,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="48" t="n"/>
       <c r="B59" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A59="","",EOMONTH(A59,0))</f>
         <v/>
       </c>
       <c r="C59" s="50">
@@ -32743,7 +32743,7 @@
         </is>
       </c>
       <c r="G59" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F59="","",IF(COUNTIF(lst_Jobs,F59&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H59" s="51" t="inlineStr">
@@ -32766,11 +32766,11 @@
         <v>3261</v>
       </c>
       <c r="M59" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L59="","",IF(K59="GST 10%",ROUND(L59*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N59" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L59="","",L59+M59)</f>
         <v/>
       </c>
       <c r="O59" s="51" t="inlineStr">
@@ -32798,15 +32798,15 @@
         <v>1029</v>
       </c>
       <c r="U59" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L59="","",L59-N(T59))</f>
         <v/>
       </c>
       <c r="V59" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L59="","",IF(SIGN(N(T59))*SIGN(L59)=-1,"CHECK - video sign",IF(ABS(N(T59))&gt;ABS(L59),"CHECK - video exceeds invoice",IF(AND(D59="VIDEO",ROUND(N(T59),2)&lt;&gt;ROUND(L59,2)),"CHECK - VIDEO job not fully split",IF(N(T59)=0,"All production",IF(ROUND(N(T59),2)=ROUND(L59,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W59" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L59="","",IF(N(T59)=0,0,ROUND(M59*N(T59)/L59,2)))</f>
         <v/>
       </c>
       <c r="X59" s="51" t="inlineStr">
@@ -32836,21 +32836,21 @@
         <v>334</v>
       </c>
       <c r="AD59" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC59/AG59,"")</f>
         <v/>
       </c>
       <c r="AE59" s="52" t="n"/>
       <c r="AF59" s="52" t="n"/>
       <c r="AG59" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L59="","",L59-N(AC59))</f>
         <v/>
       </c>
       <c r="AH59" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L59="","",L59-N(AE59)-N(AF59))</f>
         <v/>
       </c>
       <c r="AI59" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH59/L59,"")</f>
         <v/>
       </c>
       <c r="AJ59" s="54" t="n">
@@ -32866,7 +32866,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="48" t="n"/>
       <c r="B60" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A60="","",EOMONTH(A60,0))</f>
         <v/>
       </c>
       <c r="C60" s="50">
@@ -32889,7 +32889,7 @@
         </is>
       </c>
       <c r="G60" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F60="","",IF(COUNTIF(lst_Jobs,F60&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H60" s="51" t="inlineStr">
@@ -32912,11 +32912,11 @@
         <v>10015.89</v>
       </c>
       <c r="M60" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L60="","",IF(K60="GST 10%",ROUND(L60*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N60" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L60="","",L60+M60)</f>
         <v/>
       </c>
       <c r="O60" s="51" t="inlineStr">
@@ -32944,15 +32944,15 @@
         <v>1578.1</v>
       </c>
       <c r="U60" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L60="","",L60-N(T60))</f>
         <v/>
       </c>
       <c r="V60" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L60="","",IF(SIGN(N(T60))*SIGN(L60)=-1,"CHECK - video sign",IF(ABS(N(T60))&gt;ABS(L60),"CHECK - video exceeds invoice",IF(AND(D60="VIDEO",ROUND(N(T60),2)&lt;&gt;ROUND(L60,2)),"CHECK - VIDEO job not fully split",IF(N(T60)=0,"All production",IF(ROUND(N(T60),2)=ROUND(L60,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W60" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L60="","",IF(N(T60)=0,0,ROUND(M60*N(T60)/L60,2)))</f>
         <v/>
       </c>
       <c r="X60" s="51" t="inlineStr">
@@ -32982,21 +32982,21 @@
         <v>2005.65</v>
       </c>
       <c r="AD60" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC60/AG60,"")</f>
         <v/>
       </c>
       <c r="AE60" s="52" t="n"/>
       <c r="AF60" s="52" t="n"/>
       <c r="AG60" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L60="","",L60-N(AC60))</f>
         <v/>
       </c>
       <c r="AH60" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L60="","",L60-N(AE60)-N(AF60))</f>
         <v/>
       </c>
       <c r="AI60" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH60/L60,"")</f>
         <v/>
       </c>
       <c r="AJ60" s="54" t="n">
@@ -33012,7 +33012,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="48" t="n"/>
       <c r="B61" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A61="","",EOMONTH(A61,0))</f>
         <v/>
       </c>
       <c r="C61" s="50">
@@ -33035,7 +33035,7 @@
         </is>
       </c>
       <c r="G61" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F61="","",IF(COUNTIF(lst_Jobs,F61&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H61" s="51" t="inlineStr">
@@ -33058,11 +33058,11 @@
         <v>570</v>
       </c>
       <c r="M61" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L61="","",IF(K61="GST 10%",ROUND(L61*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N61" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L61="","",L61+M61)</f>
         <v/>
       </c>
       <c r="O61" s="51" t="inlineStr">
@@ -33088,15 +33088,15 @@
       <c r="S61" s="51" t="n"/>
       <c r="T61" s="52" t="n"/>
       <c r="U61" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L61="","",L61-N(T61))</f>
         <v/>
       </c>
       <c r="V61" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L61="","",IF(SIGN(N(T61))*SIGN(L61)=-1,"CHECK - video sign",IF(ABS(N(T61))&gt;ABS(L61),"CHECK - video exceeds invoice",IF(AND(D61="VIDEO",ROUND(N(T61),2)&lt;&gt;ROUND(L61,2)),"CHECK - VIDEO job not fully split",IF(N(T61)=0,"All production",IF(ROUND(N(T61),2)=ROUND(L61,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W61" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L61="","",IF(N(T61)=0,0,ROUND(M61*N(T61)/L61,2)))</f>
         <v/>
       </c>
       <c r="X61" s="51" t="inlineStr">
@@ -33124,21 +33124,21 @@
       </c>
       <c r="AC61" s="52" t="n"/>
       <c r="AD61" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC61/AG61,"")</f>
         <v/>
       </c>
       <c r="AE61" s="52" t="n"/>
       <c r="AF61" s="52" t="n"/>
       <c r="AG61" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L61="","",L61-N(AC61))</f>
         <v/>
       </c>
       <c r="AH61" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L61="","",L61-N(AE61)-N(AF61))</f>
         <v/>
       </c>
       <c r="AI61" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH61/L61,"")</f>
         <v/>
       </c>
       <c r="AJ61" s="54" t="n"/>
@@ -33152,7 +33152,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="48" t="n"/>
       <c r="B62" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A62="","",EOMONTH(A62,0))</f>
         <v/>
       </c>
       <c r="C62" s="50">
@@ -33175,7 +33175,7 @@
         </is>
       </c>
       <c r="G62" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F62="","",IF(COUNTIF(lst_Jobs,F62&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H62" s="51" t="inlineStr">
@@ -33198,11 +33198,11 @@
         <v>380</v>
       </c>
       <c r="M62" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L62="","",IF(K62="GST 10%",ROUND(L62*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N62" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L62="","",L62+M62)</f>
         <v/>
       </c>
       <c r="O62" s="51" t="inlineStr">
@@ -33228,15 +33228,15 @@
       <c r="S62" s="51" t="n"/>
       <c r="T62" s="52" t="n"/>
       <c r="U62" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L62="","",L62-N(T62))</f>
         <v/>
       </c>
       <c r="V62" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L62="","",IF(SIGN(N(T62))*SIGN(L62)=-1,"CHECK - video sign",IF(ABS(N(T62))&gt;ABS(L62),"CHECK - video exceeds invoice",IF(AND(D62="VIDEO",ROUND(N(T62),2)&lt;&gt;ROUND(L62,2)),"CHECK - VIDEO job not fully split",IF(N(T62)=0,"All production",IF(ROUND(N(T62),2)=ROUND(L62,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W62" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L62="","",IF(N(T62)=0,0,ROUND(M62*N(T62)/L62,2)))</f>
         <v/>
       </c>
       <c r="X62" s="51" t="inlineStr">
@@ -33264,21 +33264,21 @@
       </c>
       <c r="AC62" s="52" t="n"/>
       <c r="AD62" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC62/AG62,"")</f>
         <v/>
       </c>
       <c r="AE62" s="52" t="n"/>
       <c r="AF62" s="52" t="n"/>
       <c r="AG62" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L62="","",L62-N(AC62))</f>
         <v/>
       </c>
       <c r="AH62" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L62="","",L62-N(AE62)-N(AF62))</f>
         <v/>
       </c>
       <c r="AI62" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH62/L62,"")</f>
         <v/>
       </c>
       <c r="AJ62" s="54" t="n"/>
@@ -33292,7 +33292,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="48" t="n"/>
       <c r="B63" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A63="","",EOMONTH(A63,0))</f>
         <v/>
       </c>
       <c r="C63" s="50">
@@ -33315,7 +33315,7 @@
         </is>
       </c>
       <c r="G63" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F63="","",IF(COUNTIF(lst_Jobs,F63&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H63" s="51" t="inlineStr">
@@ -33338,11 +33338,11 @@
         <v>380</v>
       </c>
       <c r="M63" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L63="","",IF(K63="GST 10%",ROUND(L63*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N63" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L63="","",L63+M63)</f>
         <v/>
       </c>
       <c r="O63" s="51" t="inlineStr">
@@ -33368,15 +33368,15 @@
       <c r="S63" s="51" t="n"/>
       <c r="T63" s="52" t="n"/>
       <c r="U63" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L63="","",L63-N(T63))</f>
         <v/>
       </c>
       <c r="V63" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L63="","",IF(SIGN(N(T63))*SIGN(L63)=-1,"CHECK - video sign",IF(ABS(N(T63))&gt;ABS(L63),"CHECK - video exceeds invoice",IF(AND(D63="VIDEO",ROUND(N(T63),2)&lt;&gt;ROUND(L63,2)),"CHECK - VIDEO job not fully split",IF(N(T63)=0,"All production",IF(ROUND(N(T63),2)=ROUND(L63,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W63" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L63="","",IF(N(T63)=0,0,ROUND(M63*N(T63)/L63,2)))</f>
         <v/>
       </c>
       <c r="X63" s="51" t="inlineStr">
@@ -33404,21 +33404,21 @@
       </c>
       <c r="AC63" s="52" t="n"/>
       <c r="AD63" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC63/AG63,"")</f>
         <v/>
       </c>
       <c r="AE63" s="52" t="n"/>
       <c r="AF63" s="52" t="n"/>
       <c r="AG63" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L63="","",L63-N(AC63))</f>
         <v/>
       </c>
       <c r="AH63" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L63="","",L63-N(AE63)-N(AF63))</f>
         <v/>
       </c>
       <c r="AI63" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH63/L63,"")</f>
         <v/>
       </c>
       <c r="AJ63" s="54" t="n"/>
@@ -33432,7 +33432,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="48" t="n"/>
       <c r="B64" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A64="","",EOMONTH(A64,0))</f>
         <v/>
       </c>
       <c r="C64" s="50">
@@ -33455,7 +33455,7 @@
         </is>
       </c>
       <c r="G64" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F64="","",IF(COUNTIF(lst_Jobs,F64&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H64" s="51" t="inlineStr">
@@ -33478,11 +33478,11 @@
         <v>4729</v>
       </c>
       <c r="M64" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L64="","",IF(K64="GST 10%",ROUND(L64*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N64" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L64="","",L64+M64)</f>
         <v/>
       </c>
       <c r="O64" s="51" t="inlineStr">
@@ -33508,15 +33508,15 @@
       <c r="S64" s="51" t="n"/>
       <c r="T64" s="52" t="n"/>
       <c r="U64" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L64="","",L64-N(T64))</f>
         <v/>
       </c>
       <c r="V64" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L64="","",IF(SIGN(N(T64))*SIGN(L64)=-1,"CHECK - video sign",IF(ABS(N(T64))&gt;ABS(L64),"CHECK - video exceeds invoice",IF(AND(D64="VIDEO",ROUND(N(T64),2)&lt;&gt;ROUND(L64,2)),"CHECK - VIDEO job not fully split",IF(N(T64)=0,"All production",IF(ROUND(N(T64),2)=ROUND(L64,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W64" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L64="","",IF(N(T64)=0,0,ROUND(M64*N(T64)/L64,2)))</f>
         <v/>
       </c>
       <c r="X64" s="51" t="inlineStr">
@@ -33544,21 +33544,21 @@
       </c>
       <c r="AC64" s="52" t="n"/>
       <c r="AD64" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC64/AG64,"")</f>
         <v/>
       </c>
       <c r="AE64" s="52" t="n"/>
       <c r="AF64" s="52" t="n"/>
       <c r="AG64" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L64="","",L64-N(AC64))</f>
         <v/>
       </c>
       <c r="AH64" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L64="","",L64-N(AE64)-N(AF64))</f>
         <v/>
       </c>
       <c r="AI64" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH64/L64,"")</f>
         <v/>
       </c>
       <c r="AJ64" s="54" t="n"/>
@@ -33572,7 +33572,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="48" t="n"/>
       <c r="B65" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A65="","",EOMONTH(A65,0))</f>
         <v/>
       </c>
       <c r="C65" s="50">
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="G65" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F65="","",IF(COUNTIF(lst_Jobs,F65&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H65" s="51" t="inlineStr">
@@ -33618,11 +33618,11 @@
         <v>946</v>
       </c>
       <c r="M65" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L65="","",IF(K65="GST 10%",ROUND(L65*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N65" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L65="","",L65+M65)</f>
         <v/>
       </c>
       <c r="O65" s="51" t="inlineStr">
@@ -33648,15 +33648,15 @@
       <c r="S65" s="51" t="n"/>
       <c r="T65" s="52" t="n"/>
       <c r="U65" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Video Revenue]]))</f>
+        <f>IF(L65="","",L65-N(T65))</f>
         <v/>
       </c>
       <c r="V65" s="50">
-        <f>IF([@[Ex GST]]="","",IF(SIGN(N([@[Video Revenue]]))*SIGN([@[Ex GST]])=-1,"CHECK - video sign",IF(ABS(N([@[Video Revenue]]))&gt;ABS([@[Ex GST]]),"CHECK - video exceeds invoice",IF(AND([@[Cost Centre]]="VIDEO",ROUND(N([@[Video Revenue]]),2)&lt;&gt;ROUND([@[Ex GST]],2)),"CHECK - VIDEO job not fully split",IF(N([@[Video Revenue]])=0,"All production",IF(ROUND(N([@[Video Revenue]]),2)=ROUND([@[Ex GST]],2),"All video","Split"))))))</f>
+        <f>IF(L65="","",IF(SIGN(N(T65))*SIGN(L65)=-1,"CHECK - video sign",IF(ABS(N(T65))&gt;ABS(L65),"CHECK - video exceeds invoice",IF(AND(D65="VIDEO",ROUND(N(T65),2)&lt;&gt;ROUND(L65,2)),"CHECK - VIDEO job not fully split",IF(N(T65)=0,"All production",IF(ROUND(N(T65),2)=ROUND(L65,2),"All video","Split"))))))</f>
         <v/>
       </c>
       <c r="W65" s="53">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Video Revenue]])=0,0,ROUND([@GST]*N([@[Video Revenue]])/[@[Ex GST]],2)))</f>
+        <f>IF(L65="","",IF(N(T65)=0,0,ROUND(M65*N(T65)/L65,2)))</f>
         <v/>
       </c>
       <c r="X65" s="51" t="inlineStr">
@@ -33684,21 +33684,21 @@
       </c>
       <c r="AC65" s="52" t="n"/>
       <c r="AD65" s="55">
-        <f>IFERROR([@[Discounts Included]]/[@[Net Total]],"")</f>
+        <f>IFERROR(AC65/AG65,"")</f>
         <v/>
       </c>
       <c r="AE65" s="52" t="n"/>
       <c r="AF65" s="52" t="n"/>
       <c r="AG65" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Discounts Included]]))</f>
+        <f>IF(L65="","",L65-N(AC65))</f>
         <v/>
       </c>
       <c r="AH65" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-N([@[Cross Hire Expense]])-N([@[Labour Expense (Internal)]]))</f>
+        <f>IF(L65="","",L65-N(AE65)-N(AF65))</f>
         <v/>
       </c>
       <c r="AI65" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AH65/L65,"")</f>
         <v/>
       </c>
       <c r="AJ65" s="54" t="n"/>
@@ -33981,7 +33981,7 @@
         <v>45805</v>
       </c>
       <c r="B5" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A5="","",EOMONTH(A5,0))</f>
         <v/>
       </c>
       <c r="C5" s="50">
@@ -34004,7 +34004,7 @@
         </is>
       </c>
       <c r="G5" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F5="","",IF(COUNTIF(lst_Jobs,F5&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H5" s="51" t="inlineStr">
@@ -34031,11 +34031,11 @@
         <v>9875</v>
       </c>
       <c r="M5" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L5="","",IF(K5="GST 10%",ROUND(L5*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L5="","",L5+M5)</f>
         <v/>
       </c>
       <c r="O5" s="51" t="inlineStr">
@@ -34078,19 +34078,19 @@
       <c r="Z5" s="52" t="n"/>
       <c r="AA5" s="52" t="n"/>
       <c r="AB5" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L5="","",N(Y5)+N(Z5)+N(AA5))</f>
         <v/>
       </c>
       <c r="AC5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L5="","",L5-AB5)</f>
         <v/>
       </c>
       <c r="AD5" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC5/L5,"")</f>
         <v/>
       </c>
       <c r="AE5" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L5="","",IF(N(V5)+N(W5)+N(X5)=0,"Not split",IF(ROUND(N(V5)+N(W5)+N(X5),2)=ROUND(L5,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34099,7 +34099,7 @@
         <v>46101</v>
       </c>
       <c r="B6" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A6="","",EOMONTH(A6,0))</f>
         <v/>
       </c>
       <c r="C6" s="50">
@@ -34122,7 +34122,7 @@
         </is>
       </c>
       <c r="G6" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F6="","",IF(COUNTIF(lst_Jobs,F6&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H6" s="51" t="inlineStr">
@@ -34149,11 +34149,11 @@
         <v>23050</v>
       </c>
       <c r="M6" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L6="","",IF(K6="GST 10%",ROUND(L6*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L6="","",L6+M6)</f>
         <v/>
       </c>
       <c r="O6" s="51" t="inlineStr">
@@ -34196,19 +34196,19 @@
       <c r="Z6" s="52" t="n"/>
       <c r="AA6" s="52" t="n"/>
       <c r="AB6" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L6="","",N(Y6)+N(Z6)+N(AA6))</f>
         <v/>
       </c>
       <c r="AC6" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L6="","",L6-AB6)</f>
         <v/>
       </c>
       <c r="AD6" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC6/L6,"")</f>
         <v/>
       </c>
       <c r="AE6" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L6="","",IF(N(V6)+N(W6)+N(X6)=0,"Not split",IF(ROUND(N(V6)+N(W6)+N(X6),2)=ROUND(L6,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
         <v>46104</v>
       </c>
       <c r="B7" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A7="","",EOMONTH(A7,0))</f>
         <v/>
       </c>
       <c r="C7" s="50">
@@ -34240,7 +34240,7 @@
         </is>
       </c>
       <c r="G7" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F7="","",IF(COUNTIF(lst_Jobs,F7&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H7" s="51" t="inlineStr">
@@ -34267,11 +34267,11 @@
         <v>13250</v>
       </c>
       <c r="M7" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L7="","",IF(K7="GST 10%",ROUND(L7*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L7="","",L7+M7)</f>
         <v/>
       </c>
       <c r="O7" s="51" t="inlineStr">
@@ -34314,19 +34314,19 @@
       <c r="Z7" s="52" t="n"/>
       <c r="AA7" s="52" t="n"/>
       <c r="AB7" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L7="","",N(Y7)+N(Z7)+N(AA7))</f>
         <v/>
       </c>
       <c r="AC7" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L7="","",L7-AB7)</f>
         <v/>
       </c>
       <c r="AD7" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC7/L7,"")</f>
         <v/>
       </c>
       <c r="AE7" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L7="","",IF(N(V7)+N(W7)+N(X7)=0,"Not split",IF(ROUND(N(V7)+N(W7)+N(X7),2)=ROUND(L7,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34335,7 +34335,7 @@
         <v>46128</v>
       </c>
       <c r="B8" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A8="","",EOMONTH(A8,0))</f>
         <v/>
       </c>
       <c r="C8" s="50">
@@ -34358,7 +34358,7 @@
         </is>
       </c>
       <c r="G8" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F8="","",IF(COUNTIF(lst_Jobs,F8&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H8" s="51" t="inlineStr">
@@ -34385,11 +34385,11 @@
         <v>24410</v>
       </c>
       <c r="M8" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L8="","",IF(K8="GST 10%",ROUND(L8*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L8="","",L8+M8)</f>
         <v/>
       </c>
       <c r="O8" s="51" t="inlineStr">
@@ -34432,19 +34432,19 @@
       <c r="Z8" s="52" t="n"/>
       <c r="AA8" s="52" t="n"/>
       <c r="AB8" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L8="","",N(Y8)+N(Z8)+N(AA8))</f>
         <v/>
       </c>
       <c r="AC8" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L8="","",L8-AB8)</f>
         <v/>
       </c>
       <c r="AD8" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC8/L8,"")</f>
         <v/>
       </c>
       <c r="AE8" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L8="","",IF(N(V8)+N(W8)+N(X8)=0,"Not split",IF(ROUND(N(V8)+N(W8)+N(X8),2)=ROUND(L8,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34453,7 +34453,7 @@
         <v>46162</v>
       </c>
       <c r="B9" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A9="","",EOMONTH(A9,0))</f>
         <v/>
       </c>
       <c r="C9" s="50">
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G9" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F9="","",IF(COUNTIF(lst_Jobs,F9&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H9" s="51" t="inlineStr">
@@ -34503,11 +34503,11 @@
         <v>57706</v>
       </c>
       <c r="M9" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L9="","",IF(K9="GST 10%",ROUND(L9*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L9="","",L9+M9)</f>
         <v/>
       </c>
       <c r="O9" s="51" t="inlineStr">
@@ -34552,19 +34552,19 @@
       </c>
       <c r="AA9" s="52" t="n"/>
       <c r="AB9" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L9="","",N(Y9)+N(Z9)+N(AA9))</f>
         <v/>
       </c>
       <c r="AC9" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L9="","",L9-AB9)</f>
         <v/>
       </c>
       <c r="AD9" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC9/L9,"")</f>
         <v/>
       </c>
       <c r="AE9" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L9="","",IF(N(V9)+N(W9)+N(X9)=0,"Not split",IF(ROUND(N(V9)+N(W9)+N(X9),2)=ROUND(L9,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34573,7 +34573,7 @@
         <v>46163</v>
       </c>
       <c r="B10" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A10="","",EOMONTH(A10,0))</f>
         <v/>
       </c>
       <c r="C10" s="50">
@@ -34596,7 +34596,7 @@
         </is>
       </c>
       <c r="G10" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F10="","",IF(COUNTIF(lst_Jobs,F10&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H10" s="51" t="inlineStr">
@@ -34623,11 +34623,11 @@
         <v>26234</v>
       </c>
       <c r="M10" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L10="","",IF(K10="GST 10%",ROUND(L10*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L10="","",L10+M10)</f>
         <v/>
       </c>
       <c r="O10" s="51" t="inlineStr">
@@ -34672,19 +34672,19 @@
       </c>
       <c r="AA10" s="52" t="n"/>
       <c r="AB10" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L10="","",N(Y10)+N(Z10)+N(AA10))</f>
         <v/>
       </c>
       <c r="AC10" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L10="","",L10-AB10)</f>
         <v/>
       </c>
       <c r="AD10" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC10/L10,"")</f>
         <v/>
       </c>
       <c r="AE10" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L10="","",IF(N(V10)+N(W10)+N(X10)=0,"Not split",IF(ROUND(N(V10)+N(W10)+N(X10),2)=ROUND(L10,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34693,7 +34693,7 @@
         <v>46171</v>
       </c>
       <c r="B11" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A11="","",EOMONTH(A11,0))</f>
         <v/>
       </c>
       <c r="C11" s="50">
@@ -34716,7 +34716,7 @@
         </is>
       </c>
       <c r="G11" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F11="","",IF(COUNTIF(lst_Jobs,F11&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H11" s="51" t="inlineStr">
@@ -34743,11 +34743,11 @@
         <v>7563</v>
       </c>
       <c r="M11" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L11="","",IF(K11="GST 10%",ROUND(L11*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L11="","",L11+M11)</f>
         <v/>
       </c>
       <c r="O11" s="51" t="inlineStr">
@@ -34792,19 +34792,19 @@
       </c>
       <c r="AA11" s="52" t="n"/>
       <c r="AB11" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L11="","",N(Y11)+N(Z11)+N(AA11))</f>
         <v/>
       </c>
       <c r="AC11" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L11="","",L11-AB11)</f>
         <v/>
       </c>
       <c r="AD11" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC11/L11,"")</f>
         <v/>
       </c>
       <c r="AE11" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L11="","",IF(N(V11)+N(W11)+N(X11)=0,"Not split",IF(ROUND(N(V11)+N(W11)+N(X11),2)=ROUND(L11,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34813,7 +34813,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A12="","",EOMONTH(A12,0))</f>
         <v/>
       </c>
       <c r="C12" s="50">
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G12" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F12="","",IF(COUNTIF(lst_Jobs,F12&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H12" s="51" t="inlineStr">
@@ -34863,11 +34863,11 @@
         <v>12039</v>
       </c>
       <c r="M12" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L12="","",IF(K12="GST 10%",ROUND(L12*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L12="","",L12+M12)</f>
         <v/>
       </c>
       <c r="O12" s="51" t="inlineStr">
@@ -34912,19 +34912,19 @@
       </c>
       <c r="AA12" s="52" t="n"/>
       <c r="AB12" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L12="","",N(Y12)+N(Z12)+N(AA12))</f>
         <v/>
       </c>
       <c r="AC12" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L12="","",L12-AB12)</f>
         <v/>
       </c>
       <c r="AD12" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC12/L12,"")</f>
         <v/>
       </c>
       <c r="AE12" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L12="","",IF(N(V12)+N(W12)+N(X12)=0,"Not split",IF(ROUND(N(V12)+N(W12)+N(X12),2)=ROUND(L12,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -34933,7 +34933,7 @@
         <v>46190</v>
       </c>
       <c r="B13" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A13="","",EOMONTH(A13,0))</f>
         <v/>
       </c>
       <c r="C13" s="50">
@@ -34956,7 +34956,7 @@
         </is>
       </c>
       <c r="G13" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F13="","",IF(COUNTIF(lst_Jobs,F13&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H13" s="51" t="inlineStr">
@@ -34983,11 +34983,11 @@
         <v>96068</v>
       </c>
       <c r="M13" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L13="","",IF(K13="GST 10%",ROUND(L13*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L13="","",L13+M13)</f>
         <v/>
       </c>
       <c r="O13" s="51" t="inlineStr">
@@ -35032,19 +35032,19 @@
       </c>
       <c r="AA13" s="52" t="n"/>
       <c r="AB13" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L13="","",N(Y13)+N(Z13)+N(AA13))</f>
         <v/>
       </c>
       <c r="AC13" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L13="","",L13-AB13)</f>
         <v/>
       </c>
       <c r="AD13" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC13/L13,"")</f>
         <v/>
       </c>
       <c r="AE13" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L13="","",IF(N(V13)+N(W13)+N(X13)=0,"Not split",IF(ROUND(N(V13)+N(W13)+N(X13),2)=ROUND(L13,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35053,7 +35053,7 @@
         <v>46198</v>
       </c>
       <c r="B14" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A14="","",EOMONTH(A14,0))</f>
         <v/>
       </c>
       <c r="C14" s="50">
@@ -35076,7 +35076,7 @@
         </is>
       </c>
       <c r="G14" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F14="","",IF(COUNTIF(lst_Jobs,F14&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H14" s="51" t="inlineStr">
@@ -35103,11 +35103,11 @@
         <v>561</v>
       </c>
       <c r="M14" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L14="","",IF(K14="GST 10%",ROUND(L14*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L14="","",L14+M14)</f>
         <v/>
       </c>
       <c r="O14" s="51" t="inlineStr">
@@ -35152,19 +35152,19 @@
       </c>
       <c r="AA14" s="52" t="n"/>
       <c r="AB14" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L14="","",N(Y14)+N(Z14)+N(AA14))</f>
         <v/>
       </c>
       <c r="AC14" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L14="","",L14-AB14)</f>
         <v/>
       </c>
       <c r="AD14" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC14/L14,"")</f>
         <v/>
       </c>
       <c r="AE14" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L14="","",IF(N(V14)+N(W14)+N(X14)=0,"Not split",IF(ROUND(N(V14)+N(W14)+N(X14),2)=ROUND(L14,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35173,7 +35173,7 @@
         <v>46198</v>
       </c>
       <c r="B15" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A15="","",EOMONTH(A15,0))</f>
         <v/>
       </c>
       <c r="C15" s="50">
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G15" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F15="","",IF(COUNTIF(lst_Jobs,F15&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H15" s="51" t="inlineStr">
@@ -35223,11 +35223,11 @@
         <v>2247.5</v>
       </c>
       <c r="M15" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L15="","",IF(K15="GST 10%",ROUND(L15*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L15="","",L15+M15)</f>
         <v/>
       </c>
       <c r="O15" s="51" t="inlineStr">
@@ -35274,19 +35274,19 @@
       </c>
       <c r="AA15" s="52" t="n"/>
       <c r="AB15" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L15="","",N(Y15)+N(Z15)+N(AA15))</f>
         <v/>
       </c>
       <c r="AC15" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L15="","",L15-AB15)</f>
         <v/>
       </c>
       <c r="AD15" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC15/L15,"")</f>
         <v/>
       </c>
       <c r="AE15" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L15="","",IF(N(V15)+N(W15)+N(X15)=0,"Not split",IF(ROUND(N(V15)+N(W15)+N(X15),2)=ROUND(L15,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35295,7 +35295,7 @@
         <v>46203</v>
       </c>
       <c r="B16" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A16="","",EOMONTH(A16,0))</f>
         <v/>
       </c>
       <c r="C16" s="50">
@@ -35318,7 +35318,7 @@
         </is>
       </c>
       <c r="G16" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F16="","",IF(COUNTIF(lst_Jobs,F16&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H16" s="51" t="inlineStr">
@@ -35345,11 +35345,11 @@
         <v>159150</v>
       </c>
       <c r="M16" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L16="","",IF(K16="GST 10%",ROUND(L16*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L16="","",L16+M16)</f>
         <v/>
       </c>
       <c r="O16" s="51" t="inlineStr">
@@ -35390,19 +35390,19 @@
       </c>
       <c r="AA16" s="52" t="n"/>
       <c r="AB16" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L16="","",N(Y16)+N(Z16)+N(AA16))</f>
         <v/>
       </c>
       <c r="AC16" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L16="","",L16-AB16)</f>
         <v/>
       </c>
       <c r="AD16" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC16/L16,"")</f>
         <v/>
       </c>
       <c r="AE16" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L16="","",IF(N(V16)+N(W16)+N(X16)=0,"Not split",IF(ROUND(N(V16)+N(W16)+N(X16),2)=ROUND(L16,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
         <v>46203</v>
       </c>
       <c r="B17" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A17="","",EOMONTH(A17,0))</f>
         <v/>
       </c>
       <c r="C17" s="50">
@@ -35434,7 +35434,7 @@
         </is>
       </c>
       <c r="G17" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F17="","",IF(COUNTIF(lst_Jobs,F17&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H17" s="51" t="inlineStr">
@@ -35461,11 +35461,11 @@
         <v>27408</v>
       </c>
       <c r="M17" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L17="","",IF(K17="GST 10%",ROUND(L17*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L17="","",L17+M17)</f>
         <v/>
       </c>
       <c r="O17" s="51" t="inlineStr">
@@ -35514,19 +35514,19 @@
       </c>
       <c r="AA17" s="52" t="n"/>
       <c r="AB17" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L17="","",N(Y17)+N(Z17)+N(AA17))</f>
         <v/>
       </c>
       <c r="AC17" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L17="","",L17-AB17)</f>
         <v/>
       </c>
       <c r="AD17" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC17/L17,"")</f>
         <v/>
       </c>
       <c r="AE17" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L17="","",IF(N(V17)+N(W17)+N(X17)=0,"Not split",IF(ROUND(N(V17)+N(W17)+N(X17),2)=ROUND(L17,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
         <v>46203</v>
       </c>
       <c r="B18" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A18="","",EOMONTH(A18,0))</f>
         <v/>
       </c>
       <c r="C18" s="50">
@@ -35558,7 +35558,7 @@
         </is>
       </c>
       <c r="G18" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F18="","",IF(COUNTIF(lst_Jobs,F18&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H18" s="51" t="inlineStr">
@@ -35585,11 +35585,11 @@
         <v>20128</v>
       </c>
       <c r="M18" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L18="","",IF(K18="GST 10%",ROUND(L18*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L18="","",L18+M18)</f>
         <v/>
       </c>
       <c r="O18" s="51" t="inlineStr">
@@ -35634,19 +35634,19 @@
       </c>
       <c r="AA18" s="52" t="n"/>
       <c r="AB18" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L18="","",N(Y18)+N(Z18)+N(AA18))</f>
         <v/>
       </c>
       <c r="AC18" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L18="","",L18-AB18)</f>
         <v/>
       </c>
       <c r="AD18" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC18/L18,"")</f>
         <v/>
       </c>
       <c r="AE18" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L18="","",IF(N(V18)+N(W18)+N(X18)=0,"Not split",IF(ROUND(N(V18)+N(W18)+N(X18),2)=ROUND(L18,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35655,7 +35655,7 @@
         <v>46203</v>
       </c>
       <c r="B19" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A19="","",EOMONTH(A19,0))</f>
         <v/>
       </c>
       <c r="C19" s="50">
@@ -35678,7 +35678,7 @@
         </is>
       </c>
       <c r="G19" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F19="","",IF(COUNTIF(lst_Jobs,F19&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H19" s="51" t="inlineStr">
@@ -35705,11 +35705,11 @@
         <v>5065</v>
       </c>
       <c r="M19" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L19="","",IF(K19="GST 10%",ROUND(L19*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L19="","",L19+M19)</f>
         <v/>
       </c>
       <c r="O19" s="51" t="inlineStr">
@@ -35754,19 +35754,19 @@
       </c>
       <c r="AA19" s="52" t="n"/>
       <c r="AB19" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L19="","",N(Y19)+N(Z19)+N(AA19))</f>
         <v/>
       </c>
       <c r="AC19" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L19="","",L19-AB19)</f>
         <v/>
       </c>
       <c r="AD19" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC19/L19,"")</f>
         <v/>
       </c>
       <c r="AE19" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L19="","",IF(N(V19)+N(W19)+N(X19)=0,"Not split",IF(ROUND(N(V19)+N(W19)+N(X19),2)=ROUND(L19,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35775,7 +35775,7 @@
         <v>46203</v>
       </c>
       <c r="B20" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A20="","",EOMONTH(A20,0))</f>
         <v/>
       </c>
       <c r="C20" s="50">
@@ -35798,7 +35798,7 @@
         </is>
       </c>
       <c r="G20" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F20="","",IF(COUNTIF(lst_Jobs,F20&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H20" s="51" t="inlineStr">
@@ -35825,11 +35825,11 @@
         <v>354</v>
       </c>
       <c r="M20" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L20="","",IF(K20="GST 10%",ROUND(L20*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L20="","",L20+M20)</f>
         <v/>
       </c>
       <c r="O20" s="51" t="inlineStr">
@@ -35870,19 +35870,19 @@
       </c>
       <c r="AA20" s="52" t="n"/>
       <c r="AB20" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L20="","",N(Y20)+N(Z20)+N(AA20))</f>
         <v/>
       </c>
       <c r="AC20" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L20="","",L20-AB20)</f>
         <v/>
       </c>
       <c r="AD20" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC20/L20,"")</f>
         <v/>
       </c>
       <c r="AE20" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L20="","",IF(N(V20)+N(W20)+N(X20)=0,"Not split",IF(ROUND(N(V20)+N(W20)+N(X20),2)=ROUND(L20,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -35891,7 +35891,7 @@
         <v>46209</v>
       </c>
       <c r="B21" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A21="","",EOMONTH(A21,0))</f>
         <v/>
       </c>
       <c r="C21" s="50">
@@ -35914,7 +35914,7 @@
         </is>
       </c>
       <c r="G21" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F21="","",IF(COUNTIF(lst_Jobs,F21&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H21" s="51" t="inlineStr">
@@ -35941,11 +35941,11 @@
         <v>1161</v>
       </c>
       <c r="M21" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L21="","",IF(K21="GST 10%",ROUND(L21*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L21="","",L21+M21)</f>
         <v/>
       </c>
       <c r="O21" s="51" t="inlineStr">
@@ -35990,19 +35990,19 @@
       </c>
       <c r="AA21" s="52" t="n"/>
       <c r="AB21" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L21="","",N(Y21)+N(Z21)+N(AA21))</f>
         <v/>
       </c>
       <c r="AC21" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L21="","",L21-AB21)</f>
         <v/>
       </c>
       <c r="AD21" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC21/L21,"")</f>
         <v/>
       </c>
       <c r="AE21" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L21="","",IF(N(V21)+N(W21)+N(X21)=0,"Not split",IF(ROUND(N(V21)+N(W21)+N(X21),2)=ROUND(L21,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
         <v>46233</v>
       </c>
       <c r="B22" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A22="","",EOMONTH(A22,0))</f>
         <v/>
       </c>
       <c r="C22" s="50">
@@ -36034,7 +36034,7 @@
         </is>
       </c>
       <c r="G22" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F22="","",IF(COUNTIF(lst_Jobs,F22&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H22" s="51" t="inlineStr">
@@ -36061,11 +36061,11 @@
         <v>3890</v>
       </c>
       <c r="M22" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L22="","",IF(K22="GST 10%",ROUND(L22*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L22="","",L22+M22)</f>
         <v/>
       </c>
       <c r="O22" s="51" t="inlineStr">
@@ -36110,19 +36110,19 @@
       </c>
       <c r="AA22" s="52" t="n"/>
       <c r="AB22" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L22="","",N(Y22)+N(Z22)+N(AA22))</f>
         <v/>
       </c>
       <c r="AC22" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L22="","",L22-AB22)</f>
         <v/>
       </c>
       <c r="AD22" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC22/L22,"")</f>
         <v/>
       </c>
       <c r="AE22" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L22="","",IF(N(V22)+N(W22)+N(X22)=0,"Not split",IF(ROUND(N(V22)+N(W22)+N(X22),2)=ROUND(L22,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36131,7 +36131,7 @@
         <v>46233</v>
       </c>
       <c r="B23" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A23="","",EOMONTH(A23,0))</f>
         <v/>
       </c>
       <c r="C23" s="50">
@@ -36154,7 +36154,7 @@
         </is>
       </c>
       <c r="G23" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F23="","",IF(COUNTIF(lst_Jobs,F23&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H23" s="51" t="inlineStr">
@@ -36181,11 +36181,11 @@
         <v>60348</v>
       </c>
       <c r="M23" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L23="","",IF(K23="GST 10%",ROUND(L23*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L23="","",L23+M23)</f>
         <v/>
       </c>
       <c r="O23" s="51" t="inlineStr">
@@ -36230,19 +36230,19 @@
       </c>
       <c r="AA23" s="52" t="n"/>
       <c r="AB23" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L23="","",N(Y23)+N(Z23)+N(AA23))</f>
         <v/>
       </c>
       <c r="AC23" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L23="","",L23-AB23)</f>
         <v/>
       </c>
       <c r="AD23" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC23/L23,"")</f>
         <v/>
       </c>
       <c r="AE23" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L23="","",IF(N(V23)+N(W23)+N(X23)=0,"Not split",IF(ROUND(N(V23)+N(W23)+N(X23),2)=ROUND(L23,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36251,7 +36251,7 @@
         <v>46233</v>
       </c>
       <c r="B24" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A24="","",EOMONTH(A24,0))</f>
         <v/>
       </c>
       <c r="C24" s="50">
@@ -36274,7 +36274,7 @@
         </is>
       </c>
       <c r="G24" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F24="","",IF(COUNTIF(lst_Jobs,F24&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H24" s="51" t="inlineStr">
@@ -36301,11 +36301,11 @@
         <v>7705</v>
       </c>
       <c r="M24" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L24="","",IF(K24="GST 10%",ROUND(L24*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L24="","",L24+M24)</f>
         <v/>
       </c>
       <c r="O24" s="51" t="inlineStr">
@@ -36354,19 +36354,19 @@
       </c>
       <c r="AA24" s="52" t="n"/>
       <c r="AB24" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L24="","",N(Y24)+N(Z24)+N(AA24))</f>
         <v/>
       </c>
       <c r="AC24" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L24="","",L24-AB24)</f>
         <v/>
       </c>
       <c r="AD24" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC24/L24,"")</f>
         <v/>
       </c>
       <c r="AE24" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L24="","",IF(N(V24)+N(W24)+N(X24)=0,"Not split",IF(ROUND(N(V24)+N(W24)+N(X24),2)=ROUND(L24,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36375,7 +36375,7 @@
         <v>46234</v>
       </c>
       <c r="B25" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A25="","",EOMONTH(A25,0))</f>
         <v/>
       </c>
       <c r="C25" s="50">
@@ -36398,7 +36398,7 @@
         </is>
       </c>
       <c r="G25" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F25="","",IF(COUNTIF(lst_Jobs,F25&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H25" s="51" t="inlineStr">
@@ -36425,11 +36425,11 @@
         <v>6137</v>
       </c>
       <c r="M25" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L25="","",IF(K25="GST 10%",ROUND(L25*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L25="","",L25+M25)</f>
         <v/>
       </c>
       <c r="O25" s="51" t="inlineStr">
@@ -36474,19 +36474,19 @@
       </c>
       <c r="AA25" s="52" t="n"/>
       <c r="AB25" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L25="","",N(Y25)+N(Z25)+N(AA25))</f>
         <v/>
       </c>
       <c r="AC25" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L25="","",L25-AB25)</f>
         <v/>
       </c>
       <c r="AD25" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC25/L25,"")</f>
         <v/>
       </c>
       <c r="AE25" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L25="","",IF(N(V25)+N(W25)+N(X25)=0,"Not split",IF(ROUND(N(V25)+N(W25)+N(X25),2)=ROUND(L25,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36495,7 +36495,7 @@
         <v>46234</v>
       </c>
       <c r="B26" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A26="","",EOMONTH(A26,0))</f>
         <v/>
       </c>
       <c r="C26" s="50">
@@ -36518,7 +36518,7 @@
         </is>
       </c>
       <c r="G26" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F26="","",IF(COUNTIF(lst_Jobs,F26&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H26" s="51" t="inlineStr">
@@ -36545,11 +36545,11 @@
         <v>4205</v>
       </c>
       <c r="M26" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L26="","",IF(K26="GST 10%",ROUND(L26*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L26="","",L26+M26)</f>
         <v/>
       </c>
       <c r="O26" s="51" t="inlineStr">
@@ -36594,19 +36594,19 @@
         <v>3364</v>
       </c>
       <c r="AB26" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L26="","",N(Y26)+N(Z26)+N(AA26))</f>
         <v/>
       </c>
       <c r="AC26" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L26="","",L26-AB26)</f>
         <v/>
       </c>
       <c r="AD26" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC26/L26,"")</f>
         <v/>
       </c>
       <c r="AE26" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L26="","",IF(N(V26)+N(W26)+N(X26)=0,"Not split",IF(ROUND(N(V26)+N(W26)+N(X26),2)=ROUND(L26,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36615,7 +36615,7 @@
         <v>46234</v>
       </c>
       <c r="B27" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A27="","",EOMONTH(A27,0))</f>
         <v/>
       </c>
       <c r="C27" s="50">
@@ -36638,7 +36638,7 @@
         </is>
       </c>
       <c r="G27" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F27="","",IF(COUNTIF(lst_Jobs,F27&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H27" s="51" t="inlineStr">
@@ -36665,11 +36665,11 @@
         <v>4702</v>
       </c>
       <c r="M27" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L27="","",IF(K27="GST 10%",ROUND(L27*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L27="","",L27+M27)</f>
         <v/>
       </c>
       <c r="O27" s="51" t="inlineStr">
@@ -36714,19 +36714,19 @@
       </c>
       <c r="AA27" s="52" t="n"/>
       <c r="AB27" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L27="","",N(Y27)+N(Z27)+N(AA27))</f>
         <v/>
       </c>
       <c r="AC27" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L27="","",L27-AB27)</f>
         <v/>
       </c>
       <c r="AD27" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC27/L27,"")</f>
         <v/>
       </c>
       <c r="AE27" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L27="","",IF(N(V27)+N(W27)+N(X27)=0,"Not split",IF(ROUND(N(V27)+N(W27)+N(X27),2)=ROUND(L27,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36735,7 +36735,7 @@
         <v>46274</v>
       </c>
       <c r="B28" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A28="","",EOMONTH(A28,0))</f>
         <v/>
       </c>
       <c r="C28" s="50">
@@ -36758,7 +36758,7 @@
         </is>
       </c>
       <c r="G28" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F28="","",IF(COUNTIF(lst_Jobs,F28&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H28" s="51" t="inlineStr">
@@ -36785,11 +36785,11 @@
         <v>202647</v>
       </c>
       <c r="M28" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L28="","",IF(K28="GST 10%",ROUND(L28*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L28="","",L28+M28)</f>
         <v/>
       </c>
       <c r="O28" s="51" t="inlineStr">
@@ -36828,19 +36828,19 @@
       </c>
       <c r="AA28" s="52" t="n"/>
       <c r="AB28" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L28="","",N(Y28)+N(Z28)+N(AA28))</f>
         <v/>
       </c>
       <c r="AC28" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L28="","",L28-AB28)</f>
         <v/>
       </c>
       <c r="AD28" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC28/L28,"")</f>
         <v/>
       </c>
       <c r="AE28" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L28="","",IF(N(V28)+N(W28)+N(X28)=0,"Not split",IF(ROUND(N(V28)+N(W28)+N(X28),2)=ROUND(L28,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36849,7 +36849,7 @@
         <v>46254</v>
       </c>
       <c r="B29" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A29="","",EOMONTH(A29,0))</f>
         <v/>
       </c>
       <c r="C29" s="50">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="G29" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F29="","",IF(COUNTIF(lst_Jobs,F29&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H29" s="51" t="inlineStr">
@@ -36899,11 +36899,11 @@
         <v>45909</v>
       </c>
       <c r="M29" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L29="","",IF(K29="GST 10%",ROUND(L29*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L29="","",L29+M29)</f>
         <v/>
       </c>
       <c r="O29" s="51" t="inlineStr">
@@ -36948,19 +36948,19 @@
       </c>
       <c r="AA29" s="52" t="n"/>
       <c r="AB29" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L29="","",N(Y29)+N(Z29)+N(AA29))</f>
         <v/>
       </c>
       <c r="AC29" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L29="","",L29-AB29)</f>
         <v/>
       </c>
       <c r="AD29" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC29/L29,"")</f>
         <v/>
       </c>
       <c r="AE29" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L29="","",IF(N(V29)+N(W29)+N(X29)=0,"Not split",IF(ROUND(N(V29)+N(W29)+N(X29),2)=ROUND(L29,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -36969,7 +36969,7 @@
         <v>46237</v>
       </c>
       <c r="B30" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A30="","",EOMONTH(A30,0))</f>
         <v/>
       </c>
       <c r="C30" s="50">
@@ -36992,7 +36992,7 @@
         </is>
       </c>
       <c r="G30" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F30="","",IF(COUNTIF(lst_Jobs,F30&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H30" s="51" t="inlineStr">
@@ -37019,11 +37019,11 @@
         <v>12271</v>
       </c>
       <c r="M30" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L30="","",IF(K30="GST 10%",ROUND(L30*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L30="","",L30+M30)</f>
         <v/>
       </c>
       <c r="O30" s="51" t="inlineStr">
@@ -37062,19 +37062,19 @@
       </c>
       <c r="AA30" s="52" t="n"/>
       <c r="AB30" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L30="","",N(Y30)+N(Z30)+N(AA30))</f>
         <v/>
       </c>
       <c r="AC30" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L30="","",L30-AB30)</f>
         <v/>
       </c>
       <c r="AD30" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC30/L30,"")</f>
         <v/>
       </c>
       <c r="AE30" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L30="","",IF(N(V30)+N(W30)+N(X30)=0,"Not split",IF(ROUND(N(V30)+N(W30)+N(X30),2)=ROUND(L30,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
         <v>46261</v>
       </c>
       <c r="B31" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A31="","",EOMONTH(A31,0))</f>
         <v/>
       </c>
       <c r="C31" s="50">
@@ -37106,7 +37106,7 @@
         </is>
       </c>
       <c r="G31" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F31="","",IF(COUNTIF(lst_Jobs,F31&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H31" s="51" t="inlineStr">
@@ -37133,11 +37133,11 @@
         <v>4462</v>
       </c>
       <c r="M31" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L31="","",IF(K31="GST 10%",ROUND(L31*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L31="","",L31+M31)</f>
         <v/>
       </c>
       <c r="O31" s="51" t="inlineStr">
@@ -37182,19 +37182,19 @@
       <c r="Z31" s="52" t="n"/>
       <c r="AA31" s="52" t="n"/>
       <c r="AB31" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L31="","",N(Y31)+N(Z31)+N(AA31))</f>
         <v/>
       </c>
       <c r="AC31" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L31="","",L31-AB31)</f>
         <v/>
       </c>
       <c r="AD31" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC31/L31,"")</f>
         <v/>
       </c>
       <c r="AE31" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L31="","",IF(N(V31)+N(W31)+N(X31)=0,"Not split",IF(ROUND(N(V31)+N(W31)+N(X31),2)=ROUND(L31,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -37203,7 +37203,7 @@
         <v>46253</v>
       </c>
       <c r="B32" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A32="","",EOMONTH(A32,0))</f>
         <v/>
       </c>
       <c r="C32" s="50">
@@ -37226,7 +37226,7 @@
         </is>
       </c>
       <c r="G32" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F32="","",IF(COUNTIF(lst_Jobs,F32&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H32" s="51" t="inlineStr">
@@ -37253,11 +37253,11 @@
         <v>3489</v>
       </c>
       <c r="M32" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L32="","",IF(K32="GST 10%",ROUND(L32*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L32="","",L32+M32)</f>
         <v/>
       </c>
       <c r="O32" s="51" t="inlineStr">
@@ -37302,26 +37302,26 @@
       </c>
       <c r="AA32" s="52" t="n"/>
       <c r="AB32" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L32="","",N(Y32)+N(Z32)+N(AA32))</f>
         <v/>
       </c>
       <c r="AC32" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L32="","",L32-AB32)</f>
         <v/>
       </c>
       <c r="AD32" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC32/L32,"")</f>
         <v/>
       </c>
       <c r="AE32" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L32="","",IF(N(V32)+N(W32)+N(X32)=0,"Not split",IF(ROUND(N(V32)+N(W32)+N(X32),2)=ROUND(L32,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="48" t="n"/>
       <c r="B33" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A33="","",EOMONTH(A33,0))</f>
         <v/>
       </c>
       <c r="C33" s="50">
@@ -37344,7 +37344,7 @@
         </is>
       </c>
       <c r="G33" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F33="","",IF(COUNTIF(lst_Jobs,F33&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H33" s="51" t="inlineStr">
@@ -37367,11 +37367,11 @@
         <v>2707</v>
       </c>
       <c r="M33" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L33="","",IF(K33="GST 10%",ROUND(L33*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L33="","",L33+M33)</f>
         <v/>
       </c>
       <c r="O33" s="51" t="inlineStr">
@@ -37418,26 +37418,26 @@
       </c>
       <c r="AA33" s="52" t="n"/>
       <c r="AB33" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L33="","",N(Y33)+N(Z33)+N(AA33))</f>
         <v/>
       </c>
       <c r="AC33" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L33="","",L33-AB33)</f>
         <v/>
       </c>
       <c r="AD33" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC33/L33,"")</f>
         <v/>
       </c>
       <c r="AE33" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L33="","",IF(N(V33)+N(W33)+N(X33)=0,"Not split",IF(ROUND(N(V33)+N(W33)+N(X33),2)=ROUND(L33,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="48" t="n"/>
       <c r="B34" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A34="","",EOMONTH(A34,0))</f>
         <v/>
       </c>
       <c r="C34" s="50">
@@ -37460,7 +37460,7 @@
         </is>
       </c>
       <c r="G34" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F34="","",IF(COUNTIF(lst_Jobs,F34&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H34" s="51" t="inlineStr">
@@ -37483,11 +37483,11 @@
         <v>4631</v>
       </c>
       <c r="M34" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L34="","",IF(K34="GST 10%",ROUND(L34*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L34="","",L34+M34)</f>
         <v/>
       </c>
       <c r="O34" s="51" t="inlineStr">
@@ -37528,19 +37528,19 @@
       <c r="Z34" s="52" t="n"/>
       <c r="AA34" s="52" t="n"/>
       <c r="AB34" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L34="","",N(Y34)+N(Z34)+N(AA34))</f>
         <v/>
       </c>
       <c r="AC34" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L34="","",L34-AB34)</f>
         <v/>
       </c>
       <c r="AD34" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC34/L34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L34="","",IF(N(V34)+N(W34)+N(X34)=0,"Not split",IF(ROUND(N(V34)+N(W34)+N(X34),2)=ROUND(L34,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -37549,7 +37549,7 @@
         <v>46254</v>
       </c>
       <c r="B35" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A35="","",EOMONTH(A35,0))</f>
         <v/>
       </c>
       <c r="C35" s="50">
@@ -37572,7 +37572,7 @@
         </is>
       </c>
       <c r="G35" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F35="","",IF(COUNTIF(lst_Jobs,F35&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H35" s="51" t="inlineStr">
@@ -37599,11 +37599,11 @@
         <v>993</v>
       </c>
       <c r="M35" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L35="","",IF(K35="GST 10%",ROUND(L35*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L35="","",L35+M35)</f>
         <v/>
       </c>
       <c r="O35" s="51" t="inlineStr">
@@ -37644,26 +37644,26 @@
       </c>
       <c r="AA35" s="52" t="n"/>
       <c r="AB35" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L35="","",N(Y35)+N(Z35)+N(AA35))</f>
         <v/>
       </c>
       <c r="AC35" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L35="","",L35-AB35)</f>
         <v/>
       </c>
       <c r="AD35" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC35/L35,"")</f>
         <v/>
       </c>
       <c r="AE35" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L35="","",IF(N(V35)+N(W35)+N(X35)=0,"Not split",IF(ROUND(N(V35)+N(W35)+N(X35),2)=ROUND(L35,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="48" t="n"/>
       <c r="B36" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A36="","",EOMONTH(A36,0))</f>
         <v/>
       </c>
       <c r="C36" s="50">
@@ -37686,7 +37686,7 @@
         </is>
       </c>
       <c r="G36" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F36="","",IF(COUNTIF(lst_Jobs,F36&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H36" s="51" t="inlineStr">
@@ -37709,11 +37709,11 @@
         <v>2957</v>
       </c>
       <c r="M36" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L36="","",IF(K36="GST 10%",ROUND(L36*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L36="","",L36+M36)</f>
         <v/>
       </c>
       <c r="O36" s="51" t="inlineStr">
@@ -37758,19 +37758,19 @@
       </c>
       <c r="AA36" s="52" t="n"/>
       <c r="AB36" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L36="","",N(Y36)+N(Z36)+N(AA36))</f>
         <v/>
       </c>
       <c r="AC36" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L36="","",L36-AB36)</f>
         <v/>
       </c>
       <c r="AD36" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC36/L36,"")</f>
         <v/>
       </c>
       <c r="AE36" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L36="","",IF(N(V36)+N(W36)+N(X36)=0,"Not split",IF(ROUND(N(V36)+N(W36)+N(X36),2)=ROUND(L36,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
         <v>46267</v>
       </c>
       <c r="B37" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A37="","",EOMONTH(A37,0))</f>
         <v/>
       </c>
       <c r="C37" s="50">
@@ -37802,7 +37802,7 @@
         </is>
       </c>
       <c r="G37" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F37="","",IF(COUNTIF(lst_Jobs,F37&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H37" s="51" t="inlineStr">
@@ -37829,11 +37829,11 @@
         <v>671</v>
       </c>
       <c r="M37" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L37="","",IF(K37="GST 10%",ROUND(L37*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L37="","",L37+M37)</f>
         <v/>
       </c>
       <c r="O37" s="51" t="inlineStr">
@@ -37872,19 +37872,19 @@
       <c r="Z37" s="52" t="n"/>
       <c r="AA37" s="52" t="n"/>
       <c r="AB37" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L37="","",N(Y37)+N(Z37)+N(AA37))</f>
         <v/>
       </c>
       <c r="AC37" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L37="","",L37-AB37)</f>
         <v/>
       </c>
       <c r="AD37" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC37/L37,"")</f>
         <v/>
       </c>
       <c r="AE37" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L37="","",IF(N(V37)+N(W37)+N(X37)=0,"Not split",IF(ROUND(N(V37)+N(W37)+N(X37),2)=ROUND(L37,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -37893,7 +37893,7 @@
         <v>46275</v>
       </c>
       <c r="B38" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A38="","",EOMONTH(A38,0))</f>
         <v/>
       </c>
       <c r="C38" s="50">
@@ -37916,7 +37916,7 @@
         </is>
       </c>
       <c r="G38" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F38="","",IF(COUNTIF(lst_Jobs,F38&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H38" s="51" t="inlineStr">
@@ -37943,11 +37943,11 @@
         <v>3956.77</v>
       </c>
       <c r="M38" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L38="","",IF(K38="GST 10%",ROUND(L38*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L38="","",L38+M38)</f>
         <v/>
       </c>
       <c r="O38" s="51" t="inlineStr">
@@ -37986,19 +37986,19 @@
       </c>
       <c r="AA38" s="52" t="n"/>
       <c r="AB38" s="53">
-        <f>IF([@[Ex GST]]="","",N([@[Labour Expense (External)]])+N([@[Equipment Expense (Internal)]])+N([@[Subscription &amp; Licences Expense]]))</f>
+        <f>IF(L38="","",N(Y38)+N(Z38)+N(AA38))</f>
         <v/>
       </c>
       <c r="AC38" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]-[@[Total Expense]])</f>
+        <f>IF(L38="","",L38-AB38)</f>
         <v/>
       </c>
       <c r="AD38" s="55">
-        <f>IFERROR([@Margin]/[@[Ex GST]],"")</f>
+        <f>IFERROR(AC38/L38,"")</f>
         <v/>
       </c>
       <c r="AE38" s="50">
-        <f>IF([@[Ex GST]]="","",IF(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]])=0,"Not split",IF(ROUND(N([@[Labour Revenue]])+N([@[Equipment Revenue]])+N([@[Subscription Revenue]]),2)=ROUND([@[Ex GST]],2),"OK","MISMATCH")))</f>
+        <f>IF(L38="","",IF(N(V38)+N(W38)+N(X38)=0,"Not split",IF(ROUND(N(V38)+N(W38)+N(X38),2)=ROUND(L38,2),"OK","MISMATCH")))</f>
         <v/>
       </c>
     </row>
@@ -38194,7 +38194,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="48" t="n"/>
       <c r="B5" s="49">
-        <f>IF([@Date]="","",EOMONTH([@Date],0))</f>
+        <f>IF(A5="","",EOMONTH(A5,0))</f>
         <v/>
       </c>
       <c r="C5" s="50">
@@ -38205,7 +38205,7 @@
       <c r="E5" s="51" t="n"/>
       <c r="F5" s="51" t="n"/>
       <c r="G5" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(F5="","",IF(COUNTIF(lst_Jobs,F5&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="H5" s="51" t="n"/>
@@ -38214,11 +38214,11 @@
       <c r="K5" s="51" t="n"/>
       <c r="L5" s="52" t="n"/>
       <c r="M5" s="53">
-        <f>IF([@[Ex GST]]="","",IF([@[Tax Code]]="GST 10%",ROUND([@[Ex GST]]*0.1,2),0))</f>
+        <f>IF(L5="","",IF(K5="GST 10%",ROUND(L5*0.1,2),0))</f>
         <v/>
       </c>
       <c r="N5" s="53">
-        <f>IF([@[Ex GST]]="","",[@[Ex GST]]+[@GST])</f>
+        <f>IF(L5="","",L5+M5)</f>
         <v/>
       </c>
       <c r="O5" s="51" t="n"/>
@@ -38385,7 +38385,7 @@
         </is>
       </c>
       <c r="C5" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B5="","",IF(COUNTIF(lst_Jobs,B5&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D5" s="51" t="inlineStr">
@@ -38439,7 +38439,7 @@
         </is>
       </c>
       <c r="C6" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B6="","",IF(COUNTIF(lst_Jobs,B6&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D6" s="51" t="inlineStr">
@@ -38493,7 +38493,7 @@
         </is>
       </c>
       <c r="C7" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B7="","",IF(COUNTIF(lst_Jobs,B7&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D7" s="51" t="inlineStr">
@@ -38547,7 +38547,7 @@
         </is>
       </c>
       <c r="C8" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B8="","",IF(COUNTIF(lst_Jobs,B8&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D8" s="51" t="inlineStr">
@@ -38601,7 +38601,7 @@
         </is>
       </c>
       <c r="C9" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B9="","",IF(COUNTIF(lst_Jobs,B9&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D9" s="51" t="inlineStr">
@@ -38655,7 +38655,7 @@
         </is>
       </c>
       <c r="C10" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B10="","",IF(COUNTIF(lst_Jobs,B10&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D10" s="51" t="inlineStr">
@@ -38709,7 +38709,7 @@
         </is>
       </c>
       <c r="C11" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B11="","",IF(COUNTIF(lst_Jobs,B11&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D11" s="51" t="inlineStr">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="C12" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B12="","",IF(COUNTIF(lst_Jobs,B12&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D12" s="51" t="inlineStr">
@@ -38817,7 +38817,7 @@
         </is>
       </c>
       <c r="C13" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B13="","",IF(COUNTIF(lst_Jobs,B13&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D13" s="51" t="inlineStr">
@@ -38871,7 +38871,7 @@
         </is>
       </c>
       <c r="C14" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B14="","",IF(COUNTIF(lst_Jobs,B14&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D14" s="51" t="inlineStr">
@@ -38925,7 +38925,7 @@
         </is>
       </c>
       <c r="C15" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B15="","",IF(COUNTIF(lst_Jobs,B15&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D15" s="51" t="inlineStr">
@@ -38979,7 +38979,7 @@
         </is>
       </c>
       <c r="C16" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B16="","",IF(COUNTIF(lst_Jobs,B16&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D16" s="51" t="inlineStr">
@@ -39033,7 +39033,7 @@
         </is>
       </c>
       <c r="C17" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B17="","",IF(COUNTIF(lst_Jobs,B17&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D17" s="51" t="inlineStr">
@@ -39087,7 +39087,7 @@
         </is>
       </c>
       <c r="C18" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B18="","",IF(COUNTIF(lst_Jobs,B18&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D18" s="51" t="inlineStr">
@@ -39141,7 +39141,7 @@
         </is>
       </c>
       <c r="C19" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B19="","",IF(COUNTIF(lst_Jobs,B19&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D19" s="51" t="inlineStr">
@@ -39195,7 +39195,7 @@
         </is>
       </c>
       <c r="C20" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B20="","",IF(COUNTIF(lst_Jobs,B20&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D20" s="51" t="inlineStr">
@@ -39249,7 +39249,7 @@
         </is>
       </c>
       <c r="C21" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B21="","",IF(COUNTIF(lst_Jobs,B21&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D21" s="51" t="inlineStr">
@@ -39303,7 +39303,7 @@
         </is>
       </c>
       <c r="C22" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B22="","",IF(COUNTIF(lst_Jobs,B22&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D22" s="51" t="inlineStr">
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="C23" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B23="","",IF(COUNTIF(lst_Jobs,B23&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D23" s="51" t="inlineStr">
@@ -39411,7 +39411,7 @@
         </is>
       </c>
       <c r="C24" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B24="","",IF(COUNTIF(lst_Jobs,B24&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D24" s="51" t="inlineStr">
@@ -39465,7 +39465,7 @@
         </is>
       </c>
       <c r="C25" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B25="","",IF(COUNTIF(lst_Jobs,B25&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D25" s="51" t="inlineStr">
@@ -39519,7 +39519,7 @@
         </is>
       </c>
       <c r="C26" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B26="","",IF(COUNTIF(lst_Jobs,B26&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D26" s="51" t="inlineStr">
@@ -39573,7 +39573,7 @@
         </is>
       </c>
       <c r="C27" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B27="","",IF(COUNTIF(lst_Jobs,B27&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D27" s="51" t="inlineStr">
@@ -39627,7 +39627,7 @@
         </is>
       </c>
       <c r="C28" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B28="","",IF(COUNTIF(lst_Jobs,B28&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D28" s="51" t="inlineStr">
@@ -39681,7 +39681,7 @@
         </is>
       </c>
       <c r="C29" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B29="","",IF(COUNTIF(lst_Jobs,B29&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D29" s="51" t="inlineStr">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="C30" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B30="","",IF(COUNTIF(lst_Jobs,B30&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D30" s="51" t="inlineStr">
@@ -39789,7 +39789,7 @@
         </is>
       </c>
       <c r="C31" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B31="","",IF(COUNTIF(lst_Jobs,B31&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D31" s="51" t="inlineStr">
@@ -39843,7 +39843,7 @@
         </is>
       </c>
       <c r="C32" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B32="","",IF(COUNTIF(lst_Jobs,B32&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
@@ -39897,7 +39897,7 @@
         </is>
       </c>
       <c r="C33" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B33="","",IF(COUNTIF(lst_Jobs,B33&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
@@ -39951,7 +39951,7 @@
         </is>
       </c>
       <c r="C34" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B34="","",IF(COUNTIF(lst_Jobs,B34&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D34" s="51" t="inlineStr">
@@ -40005,7 +40005,7 @@
         </is>
       </c>
       <c r="C35" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B35="","",IF(COUNTIF(lst_Jobs,B35&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D35" s="51" t="inlineStr">
@@ -40059,7 +40059,7 @@
         </is>
       </c>
       <c r="C36" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B36="","",IF(COUNTIF(lst_Jobs,B36&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D36" s="51" t="inlineStr">
@@ -40113,7 +40113,7 @@
         </is>
       </c>
       <c r="C37" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B37="","",IF(COUNTIF(lst_Jobs,B37&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D37" s="51" t="inlineStr">
@@ -40167,7 +40167,7 @@
         </is>
       </c>
       <c r="C38" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B38="","",IF(COUNTIF(lst_Jobs,B38&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D38" s="51" t="inlineStr">
@@ -40221,7 +40221,7 @@
         </is>
       </c>
       <c r="C39" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B39="","",IF(COUNTIF(lst_Jobs,B39&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D39" s="51" t="inlineStr">
@@ -40275,7 +40275,7 @@
         </is>
       </c>
       <c r="C40" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B40="","",IF(COUNTIF(lst_Jobs,B40&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D40" s="51" t="inlineStr">
@@ -40329,7 +40329,7 @@
         </is>
       </c>
       <c r="C41" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B41="","",IF(COUNTIF(lst_Jobs,B41&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D41" s="51" t="inlineStr">
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="C42" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B42="","",IF(COUNTIF(lst_Jobs,B42&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D42" s="51" t="inlineStr">
@@ -40437,7 +40437,7 @@
         </is>
       </c>
       <c r="C43" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B43="","",IF(COUNTIF(lst_Jobs,B43&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D43" s="51" t="inlineStr">
@@ -40491,7 +40491,7 @@
         </is>
       </c>
       <c r="C44" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B44="","",IF(COUNTIF(lst_Jobs,B44&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D44" s="51" t="inlineStr">
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="C45" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B45="","",IF(COUNTIF(lst_Jobs,B45&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D45" s="51" t="inlineStr">
@@ -40599,7 +40599,7 @@
         </is>
       </c>
       <c r="C46" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B46="","",IF(COUNTIF(lst_Jobs,B46&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D46" s="51" t="inlineStr">
@@ -40653,7 +40653,7 @@
         </is>
       </c>
       <c r="C47" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B47="","",IF(COUNTIF(lst_Jobs,B47&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D47" s="51" t="inlineStr">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="C48" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B48="","",IF(COUNTIF(lst_Jobs,B48&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D48" s="51" t="inlineStr">
@@ -40761,7 +40761,7 @@
         </is>
       </c>
       <c r="C49" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B49="","",IF(COUNTIF(lst_Jobs,B49&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D49" s="51" t="inlineStr">
@@ -40815,7 +40815,7 @@
         </is>
       </c>
       <c r="C50" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B50="","",IF(COUNTIF(lst_Jobs,B50&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D50" s="51" t="inlineStr">
@@ -40869,7 +40869,7 @@
         </is>
       </c>
       <c r="C51" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B51="","",IF(COUNTIF(lst_Jobs,B51&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D51" s="51" t="inlineStr">
@@ -40923,7 +40923,7 @@
         </is>
       </c>
       <c r="C52" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B52="","",IF(COUNTIF(lst_Jobs,B52&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D52" s="51" t="inlineStr">
@@ -40977,7 +40977,7 @@
         </is>
       </c>
       <c r="C53" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B53="","",IF(COUNTIF(lst_Jobs,B53&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D53" s="51" t="inlineStr">
@@ -41031,7 +41031,7 @@
         </is>
       </c>
       <c r="C54" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B54="","",IF(COUNTIF(lst_Jobs,B54&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D54" s="51" t="inlineStr">
@@ -41085,7 +41085,7 @@
         </is>
       </c>
       <c r="C55" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B55="","",IF(COUNTIF(lst_Jobs,B55&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D55" s="51" t="inlineStr">
@@ -41139,7 +41139,7 @@
         </is>
       </c>
       <c r="C56" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B56="","",IF(COUNTIF(lst_Jobs,B56&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D56" s="51" t="inlineStr">
@@ -41193,7 +41193,7 @@
         </is>
       </c>
       <c r="C57" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B57="","",IF(COUNTIF(lst_Jobs,B57&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D57" s="51" t="inlineStr">
@@ -41247,7 +41247,7 @@
         </is>
       </c>
       <c r="C58" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B58="","",IF(COUNTIF(lst_Jobs,B58&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D58" s="51" t="inlineStr">
@@ -41301,7 +41301,7 @@
         </is>
       </c>
       <c r="C59" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B59="","",IF(COUNTIF(lst_Jobs,B59&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D59" s="51" t="inlineStr">
@@ -41355,7 +41355,7 @@
         </is>
       </c>
       <c r="C60" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B60="","",IF(COUNTIF(lst_Jobs,B60&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D60" s="51" t="inlineStr">
@@ -41409,7 +41409,7 @@
         </is>
       </c>
       <c r="C61" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B61="","",IF(COUNTIF(lst_Jobs,B61&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D61" s="51" t="inlineStr">
@@ -41463,7 +41463,7 @@
         </is>
       </c>
       <c r="C62" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B62="","",IF(COUNTIF(lst_Jobs,B62&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D62" s="51" t="inlineStr">
@@ -41517,7 +41517,7 @@
         </is>
       </c>
       <c r="C63" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B63="","",IF(COUNTIF(lst_Jobs,B63&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D63" s="51" t="inlineStr">
@@ -41571,7 +41571,7 @@
         </is>
       </c>
       <c r="C64" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B64="","",IF(COUNTIF(lst_Jobs,B64&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D64" s="51" t="inlineStr">
@@ -41625,7 +41625,7 @@
         </is>
       </c>
       <c r="C65" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B65="","",IF(COUNTIF(lst_Jobs,B65&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D65" s="51" t="inlineStr">
@@ -41679,7 +41679,7 @@
         </is>
       </c>
       <c r="C66" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B66="","",IF(COUNTIF(lst_Jobs,B66&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D66" s="51" t="inlineStr">
@@ -41733,7 +41733,7 @@
         </is>
       </c>
       <c r="C67" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B67="","",IF(COUNTIF(lst_Jobs,B67&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D67" s="51" t="inlineStr">
@@ -41787,7 +41787,7 @@
         </is>
       </c>
       <c r="C68" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B68="","",IF(COUNTIF(lst_Jobs,B68&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D68" s="51" t="inlineStr">
@@ -41841,7 +41841,7 @@
         </is>
       </c>
       <c r="C69" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B69="","",IF(COUNTIF(lst_Jobs,B69&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D69" s="51" t="inlineStr">
@@ -41895,7 +41895,7 @@
         </is>
       </c>
       <c r="C70" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B70="","",IF(COUNTIF(lst_Jobs,B70&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D70" s="51" t="inlineStr">
@@ -41945,7 +41945,7 @@
         </is>
       </c>
       <c r="C71" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B71="","",IF(COUNTIF(lst_Jobs,B71&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D71" s="51" t="inlineStr">
@@ -41993,7 +41993,7 @@
         </is>
       </c>
       <c r="C72" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B72="","",IF(COUNTIF(lst_Jobs,B72&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D72" s="51" t="inlineStr">
@@ -42041,7 +42041,7 @@
         </is>
       </c>
       <c r="C73" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B73="","",IF(COUNTIF(lst_Jobs,B73&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D73" s="51" t="inlineStr">
@@ -42091,7 +42091,7 @@
         </is>
       </c>
       <c r="C74" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B74="","",IF(COUNTIF(lst_Jobs,B74&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D74" s="51" t="inlineStr">
@@ -42141,7 +42141,7 @@
         </is>
       </c>
       <c r="C75" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B75="","",IF(COUNTIF(lst_Jobs,B75&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D75" s="51" t="inlineStr">
@@ -42191,7 +42191,7 @@
         </is>
       </c>
       <c r="C76" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B76="","",IF(COUNTIF(lst_Jobs,B76&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D76" s="51" t="inlineStr">
@@ -42241,7 +42241,7 @@
         </is>
       </c>
       <c r="C77" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B77="","",IF(COUNTIF(lst_Jobs,B77&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D77" s="51" t="inlineStr">
@@ -42291,7 +42291,7 @@
         </is>
       </c>
       <c r="C78" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B78="","",IF(COUNTIF(lst_Jobs,B78&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D78" s="51" t="inlineStr">
@@ -42341,7 +42341,7 @@
         </is>
       </c>
       <c r="C79" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B79="","",IF(COUNTIF(lst_Jobs,B79&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D79" s="51" t="inlineStr">
@@ -42391,7 +42391,7 @@
         </is>
       </c>
       <c r="C80" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B80="","",IF(COUNTIF(lst_Jobs,B80&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D80" s="51" t="inlineStr">
@@ -42445,7 +42445,7 @@
         </is>
       </c>
       <c r="C81" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B81="","",IF(COUNTIF(lst_Jobs,B81&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D81" s="51" t="inlineStr">
@@ -42499,7 +42499,7 @@
         </is>
       </c>
       <c r="C82" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B82="","",IF(COUNTIF(lst_Jobs,B82&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D82" s="51" t="inlineStr">
@@ -42553,7 +42553,7 @@
         </is>
       </c>
       <c r="C83" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B83="","",IF(COUNTIF(lst_Jobs,B83&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D83" s="51" t="inlineStr">
@@ -42607,7 +42607,7 @@
         </is>
       </c>
       <c r="C84" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B84="","",IF(COUNTIF(lst_Jobs,B84&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D84" s="51" t="inlineStr">
@@ -42661,7 +42661,7 @@
         </is>
       </c>
       <c r="C85" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B85="","",IF(COUNTIF(lst_Jobs,B85&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D85" s="51" t="inlineStr">
@@ -42715,7 +42715,7 @@
         </is>
       </c>
       <c r="C86" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B86="","",IF(COUNTIF(lst_Jobs,B86&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D86" s="51" t="inlineStr">
@@ -42769,7 +42769,7 @@
         </is>
       </c>
       <c r="C87" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B87="","",IF(COUNTIF(lst_Jobs,B87&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D87" s="51" t="inlineStr">
@@ -42823,7 +42823,7 @@
         </is>
       </c>
       <c r="C88" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B88="","",IF(COUNTIF(lst_Jobs,B88&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D88" s="51" t="inlineStr">
@@ -42877,7 +42877,7 @@
         </is>
       </c>
       <c r="C89" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B89="","",IF(COUNTIF(lst_Jobs,B89&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D89" s="51" t="inlineStr">
@@ -42931,7 +42931,7 @@
         </is>
       </c>
       <c r="C90" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B90="","",IF(COUNTIF(lst_Jobs,B90&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D90" s="51" t="inlineStr">
@@ -42985,7 +42985,7 @@
         </is>
       </c>
       <c r="C91" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B91="","",IF(COUNTIF(lst_Jobs,B91&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D91" s="51" t="inlineStr">
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="C92" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B92="","",IF(COUNTIF(lst_Jobs,B92&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D92" s="51" t="inlineStr">
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="C93" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B93="","",IF(COUNTIF(lst_Jobs,B93&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D93" s="51" t="inlineStr">
@@ -43147,7 +43147,7 @@
         </is>
       </c>
       <c r="C94" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B94="","",IF(COUNTIF(lst_Jobs,B94&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D94" s="51" t="inlineStr">
@@ -43201,7 +43201,7 @@
         </is>
       </c>
       <c r="C95" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B95="","",IF(COUNTIF(lst_Jobs,B95&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D95" s="51" t="inlineStr">
@@ -43255,7 +43255,7 @@
         </is>
       </c>
       <c r="C96" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B96="","",IF(COUNTIF(lst_Jobs,B96&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D96" s="51" t="inlineStr">
@@ -43309,7 +43309,7 @@
         </is>
       </c>
       <c r="C97" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B97="","",IF(COUNTIF(lst_Jobs,B97&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D97" s="51" t="inlineStr">
@@ -43363,7 +43363,7 @@
         </is>
       </c>
       <c r="C98" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B98="","",IF(COUNTIF(lst_Jobs,B98&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D98" s="51" t="inlineStr">
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="C99" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B99="","",IF(COUNTIF(lst_Jobs,B99&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D99" s="51" t="inlineStr">
@@ -43471,7 +43471,7 @@
         </is>
       </c>
       <c r="C100" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B100="","",IF(COUNTIF(lst_Jobs,B100&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D100" s="51" t="inlineStr">
@@ -43525,7 +43525,7 @@
         </is>
       </c>
       <c r="C101" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B101="","",IF(COUNTIF(lst_Jobs,B101&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D101" s="51" t="inlineStr">
@@ -43579,7 +43579,7 @@
         </is>
       </c>
       <c r="C102" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B102="","",IF(COUNTIF(lst_Jobs,B102&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D102" s="51" t="inlineStr">
@@ -43633,7 +43633,7 @@
         </is>
       </c>
       <c r="C103" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B103="","",IF(COUNTIF(lst_Jobs,B103&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D103" s="51" t="inlineStr">
@@ -43687,7 +43687,7 @@
         </is>
       </c>
       <c r="C104" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B104="","",IF(COUNTIF(lst_Jobs,B104&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D104" s="51" t="inlineStr">
@@ -43741,7 +43741,7 @@
         </is>
       </c>
       <c r="C105" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B105="","",IF(COUNTIF(lst_Jobs,B105&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D105" s="51" t="inlineStr">
@@ -43795,7 +43795,7 @@
         </is>
       </c>
       <c r="C106" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B106="","",IF(COUNTIF(lst_Jobs,B106&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D106" s="51" t="inlineStr">
@@ -43849,7 +43849,7 @@
         </is>
       </c>
       <c r="C107" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B107="","",IF(COUNTIF(lst_Jobs,B107&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D107" s="51" t="inlineStr">
@@ -43903,7 +43903,7 @@
         </is>
       </c>
       <c r="C108" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B108="","",IF(COUNTIF(lst_Jobs,B108&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D108" s="51" t="inlineStr">
@@ -43957,7 +43957,7 @@
         </is>
       </c>
       <c r="C109" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B109="","",IF(COUNTIF(lst_Jobs,B109&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D109" s="51" t="inlineStr">
@@ -44011,7 +44011,7 @@
         </is>
       </c>
       <c r="C110" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B110="","",IF(COUNTIF(lst_Jobs,B110&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D110" s="51" t="inlineStr">
@@ -44065,7 +44065,7 @@
         </is>
       </c>
       <c r="C111" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B111="","",IF(COUNTIF(lst_Jobs,B111&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D111" s="51" t="inlineStr">
@@ -44119,7 +44119,7 @@
         </is>
       </c>
       <c r="C112" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B112="","",IF(COUNTIF(lst_Jobs,B112&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D112" s="51" t="inlineStr">
@@ -44173,7 +44173,7 @@
         </is>
       </c>
       <c r="C113" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B113="","",IF(COUNTIF(lst_Jobs,B113&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D113" s="51" t="inlineStr">
@@ -44227,7 +44227,7 @@
         </is>
       </c>
       <c r="C114" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B114="","",IF(COUNTIF(lst_Jobs,B114&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D114" s="51" t="inlineStr">
@@ -44281,7 +44281,7 @@
         </is>
       </c>
       <c r="C115" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B115="","",IF(COUNTIF(lst_Jobs,B115&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D115" s="51" t="inlineStr">
@@ -44335,7 +44335,7 @@
         </is>
       </c>
       <c r="C116" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B116="","",IF(COUNTIF(lst_Jobs,B116&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D116" s="51" t="inlineStr">
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="C117" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B117="","",IF(COUNTIF(lst_Jobs,B117&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D117" s="51" t="inlineStr">
@@ -44443,7 +44443,7 @@
         </is>
       </c>
       <c r="C118" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B118="","",IF(COUNTIF(lst_Jobs,B118&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D118" s="51" t="inlineStr">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="C119" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B119="","",IF(COUNTIF(lst_Jobs,B119&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D119" s="51" t="inlineStr">
@@ -44551,7 +44551,7 @@
         </is>
       </c>
       <c r="C120" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B120="","",IF(COUNTIF(lst_Jobs,B120&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D120" s="51" t="inlineStr">
@@ -44605,7 +44605,7 @@
         </is>
       </c>
       <c r="C121" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B121="","",IF(COUNTIF(lst_Jobs,B121&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D121" s="51" t="inlineStr">
@@ -44659,7 +44659,7 @@
         </is>
       </c>
       <c r="C122" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B122="","",IF(COUNTIF(lst_Jobs,B122&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D122" s="51" t="inlineStr">
@@ -44713,7 +44713,7 @@
         </is>
       </c>
       <c r="C123" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B123="","",IF(COUNTIF(lst_Jobs,B123&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D123" s="51" t="inlineStr">
@@ -44767,7 +44767,7 @@
         </is>
       </c>
       <c r="C124" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B124="","",IF(COUNTIF(lst_Jobs,B124&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D124" s="51" t="inlineStr">
@@ -44821,7 +44821,7 @@
         </is>
       </c>
       <c r="C125" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B125="","",IF(COUNTIF(lst_Jobs,B125&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D125" s="51" t="inlineStr">
@@ -44875,7 +44875,7 @@
         </is>
       </c>
       <c r="C126" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B126="","",IF(COUNTIF(lst_Jobs,B126&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D126" s="51" t="inlineStr">
@@ -44929,7 +44929,7 @@
         </is>
       </c>
       <c r="C127" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B127="","",IF(COUNTIF(lst_Jobs,B127&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D127" s="51" t="inlineStr">
@@ -44983,7 +44983,7 @@
         </is>
       </c>
       <c r="C128" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B128="","",IF(COUNTIF(lst_Jobs,B128&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D128" s="51" t="inlineStr">
@@ -45037,7 +45037,7 @@
         </is>
       </c>
       <c r="C129" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B129="","",IF(COUNTIF(lst_Jobs,B129&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D129" s="51" t="inlineStr">
@@ -45091,7 +45091,7 @@
         </is>
       </c>
       <c r="C130" s="50">
-        <f>IF([@[Job Number]]="","",IF(COUNTIF(lst_Jobs,[@[Job Number]]&amp;"")&gt;0,"OK","CHECK"))</f>
+        <f>IF(B130="","",IF(COUNTIF(lst_Jobs,B130&amp;"")&gt;0,"OK","CHECK"))</f>
         <v/>
       </c>
       <c r="D130" s="51" t="inlineStr">

--- a/reporting/FY27_Revenue_Tracker_v3.xlsx
+++ b/reporting/FY27_Revenue_Tracker_v3.xlsx
@@ -9678,13 +9678,13 @@
       <formula1>"All,Onsite,Production,Consulting,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>=lst_CostCentre</formula1>
+      <formula1>lst_CostCentre</formula1>
     </dataValidation>
     <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>=lst_Months</formula1>
+      <formula1>lst_Months</formula1>
     </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>=lst_Status</formula1>
+      <formula1>lst_Status</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10633,7 +10633,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="warning">
-      <formula1>=lst_Months</formula1>
+      <formula1>lst_Months</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24309,29 +24309,29 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_CostCentre</formula1>
+    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_CostCentre</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_InvoiceType</formula1>
+    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_InvoiceType</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_TaxCode</formula1>
+    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_TaxCode</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_RevGL</formula1>
+    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_RevGL</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_Status</formula1>
+    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_Status</formula1>
     </dataValidation>
-    <dataValidation sqref="U5:U20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Ariba Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_Ariba</formula1>
+    <dataValidation sqref="U5:U20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Ariba Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_Ariba</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33729,29 +33729,29 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_CostCentrePrd</formula1>
+    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_CostCentrePrd</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_InvoiceType</formula1>
+    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_InvoiceType</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_TaxCode</formula1>
+    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_TaxCode</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_RevGL</formula1>
+    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_RevGL</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_Status</formula1>
+    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_Status</formula1>
     </dataValidation>
-    <dataValidation sqref="AB5:AB20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Job Closed&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="AB5:AB20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Job Closed&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38019,26 +38019,26 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_CostCentre</formula1>
+    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_CostCentre</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_InvoiceType</formula1>
+    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_InvoiceType</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_TaxCode</formula1>
+    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_TaxCode</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_RevGL</formula1>
+    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_RevGL</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_Status</formula1>
+    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_Status</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -38239,26 +38239,26 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_CostCentre</formula1>
+    <dataValidation sqref="D5:D20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_CostCentre</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_InvoiceType</formula1>
+    <dataValidation sqref="I5:I20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Invoice Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_InvoiceType</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_TaxCode</formula1>
+    <dataValidation sqref="K5:K20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Tax Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_TaxCode</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_RevGL</formula1>
+    <dataValidation sqref="O5:O20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Revenue GL&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_RevGL</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="P5:P20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="Q5:Q20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;To WIP&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_Status</formula1>
+    <dataValidation sqref="R5:R20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Status&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_Status</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45147,17 +45147,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="E5:E20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_CostCentre</formula1>
+    <dataValidation sqref="E5:E20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Cost Centre&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_CostCentre</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_WIPType</formula1>
+    <dataValidation sqref="G5:G20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Type&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_WIPType</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;GL Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_WIPGL</formula1>
+    <dataValidation sqref="J5:J20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;GL Code&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_WIPGL</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L20000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
-      <formula1>=lst_YN</formula1>
+    <dataValidation sqref="L5:L20000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="&quot;Posted to Xero&quot; is not on the list in the Lists sheet. Add it there if it is genuinely new." type="list" errorStyle="warning">
+      <formula1>lst_YN</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reporting/FY27_Revenue_Tracker_v3.xlsx
+++ b/reporting/FY27_Revenue_Tracker_v3.xlsx
@@ -9552,7 +9552,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18">
-        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),keep,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,keep*fTeam*fCC*fMonth*fStat*fFind,cnt,SUM(k),tot,SUM(keep),ex,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,12)*1,0)),gs,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,13)*1,0)),ic,SUMPRODUCT(k,IFERROR(_xlfn.CHOOSECOLS(d,14)*1,0)),"Showing "&amp;TEXT(cnt,"#,##0")&amp;" of "&amp;TEXT(tot,"#,##0")&amp;" records"&amp;"      Ex GST "&amp;TEXT(ex,"$#,##0.00")&amp;"      GST "&amp;TEXT(gs,"$#,##0.00")&amp;"      Inc GST "&amp;TEXT(ic,"$#,##0.00"))</f>
+        <f>_xlfn.LET(_xlpm.dat,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),_xlpm.keep,--((_xlfn.CHOOSECOLS(_xlpm.dat,1)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,5)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,10)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,12))&lt;&gt;""),_xlpm.fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,3)=$A$5)),_xlpm.fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,4)=$C$5)),_xlpm.fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,2)=$E$5)),_xlpm.fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,18)=$G$5)),_xlpm.fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(_xlpm.dat,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,10)))),_xlpm.flag,_xlpm.keep*_xlpm.fTeam*_xlpm.fCC*_xlpm.fMonth*_xlpm.fStat*_xlpm.fFind,_xlpm.cnt,SUM(_xlpm.flag),_xlpm.tot,SUM(_xlpm.keep),_xlpm.exg,SUMPRODUCT(_xlpm.flag,IFERROR(_xlfn.CHOOSECOLS(_xlpm.dat,12)*1,0)),_xlpm.gst,SUMPRODUCT(_xlpm.flag,IFERROR(_xlfn.CHOOSECOLS(_xlpm.dat,13)*1,0)),_xlpm.inc,SUMPRODUCT(_xlpm.flag,IFERROR(_xlfn.CHOOSECOLS(_xlpm.dat,14)*1,0)),"Showing "&amp;TEXT(_xlpm.cnt,"#,##0")&amp;" of "&amp;TEXT(_xlpm.tot,"#,##0")&amp;" records"&amp;"      Ex GST "&amp;TEXT(_xlpm.exg,"$#,##0.00")&amp;"      GST "&amp;TEXT(_xlpm.gst,"$#,##0.00")&amp;"      Inc GST "&amp;TEXT(_xlpm.inc,"$#,##0.00"))</f>
         <v/>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>_xlfn.LET(d,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),keep,--((_xlfn.CHOOSECOLS(d,1)&amp;_xlfn.CHOOSECOLS(d,5)&amp;_xlfn.CHOOSECOLS(d,10)&amp;_xlfn.CHOOSECOLS(d,12))&lt;&gt;""),fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(d,3)=$A$5)),fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(d,4)=$C$5)),fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(d,2)=$E$5)),fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(d,18)=$G$5)),fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(d,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(d,10)))),k,keep*fTeam*fCC*fMonth*fStat*fFind,_xlfn._xlws.SORT(_xlfn._xlws.FILTER(d,k=1,"No records match these filters - widen them or check the department sheets"),1,-1))</f>
+        <f>_xlfn.LET(_xlpm.dat,_xlfn.VSTACK(_xlfn.CHOOSECOLS(tbl_Onsite[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Production[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Consulting[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19),_xlfn.CHOOSECOLS(tbl_Other[#Data],1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19)),_xlpm.keep,--((_xlfn.CHOOSECOLS(_xlpm.dat,1)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,5)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,10)&amp;_xlfn.CHOOSECOLS(_xlpm.dat,12))&lt;&gt;""),_xlpm.fTeam,IF($A$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,3)=$A$5)),_xlpm.fCC,IF($C$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,4)=$C$5)),_xlpm.fMonth,IF($E$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,2)=$E$5)),_xlpm.fStat,IF($G$5="All",1,--(_xlfn.CHOOSECOLS(_xlpm.dat,18)=$G$5)),_xlpm.fFind,IF($I$5="",1,--ISNUMBER(SEARCH($I$5,_xlfn.CHOOSECOLS(_xlpm.dat,5)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,6)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,8)&amp;"|"&amp;_xlfn.CHOOSECOLS(_xlpm.dat,10)))),_xlpm.flag,_xlpm.keep*_xlpm.fTeam*_xlpm.fCC*_xlpm.fMonth*_xlpm.fStat*_xlpm.fFind,_xlfn._xlws.SORT(_xlfn._xlws.FILTER(_xlpm.dat,_xlpm.flag=1,"No records match these filters - widen them or check the department sheets"),1,-1))</f>
         <v/>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="B43" s="38">
-        <f>IFERROR(_xlfn.LET(a,_xlfn.VSTACK(tbl_Onsite[Xero Invoice No],tbl_Production[Xero Invoice No],tbl_Consulting[Xero Invoice No],tbl_Other[Xero Invoice No]),v,_xlfn._xlws.FILTER(a,a&lt;&gt;""),ROWS(v)-ROWS(_xlfn.UNIQUE(v))),0)</f>
+        <f>IFERROR(_xlfn.LET(_xlpm.arr,_xlfn.VSTACK(tbl_Onsite[Xero Invoice No],tbl_Production[Xero Invoice No],tbl_Consulting[Xero Invoice No],tbl_Other[Xero Invoice No]),_xlpm.uni,_xlfn._xlws.FILTER(_xlpm.arr,_xlpm.arr&lt;&gt;""),ROWS(_xlpm.uni)-ROWS(_xlfn.UNIQUE(_xlpm.uni))),0)</f>
         <v/>
       </c>
       <c r="I43" s="37">
@@ -10768,7 +10768,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <f>_xlfn.LET(m,$C$4,j,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(tbl_WIP[Job Number],tbl_WIP[Job Number]&lt;&gt;"","No WIP rows"))),o,SUMIFS(tbl_WIP[Amount],tbl_WIP[Job Number],j,tbl_WIP[Month],"&lt;&gt;",tbl_WIP[Month],"&lt;"&amp;m),v,SUMIFS(tbl_WIP[Amount],tbl_WIP[Job Number],j,tbl_WIP[Month],m),_xlfn.HSTACK(j,_xlfn.XLOOKUP(j,tbl_WIP[Job Number],tbl_WIP[Client],""),_xlfn.XLOOKUP(j,tbl_WIP[Job Number],tbl_WIP[Cost Centre],""),o,v,o+v))</f>
+        <f>_xlfn.LET(_xlpm.mth,$C$4,_xlpm.job,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(tbl_WIP[Job Number],tbl_WIP[Job Number]&lt;&gt;"","No WIP rows"))),_xlpm.opn,SUMIFS(tbl_WIP[Amount],tbl_WIP[Job Number],_xlpm.job,tbl_WIP[Month],"&lt;&gt;",tbl_WIP[Month],"&lt;"&amp;_xlpm.mth),_xlpm.mvt,SUMIFS(tbl_WIP[Amount],tbl_WIP[Job Number],_xlpm.job,tbl_WIP[Month],_xlpm.mth),_xlfn.HSTACK(_xlpm.job,_xlfn.XLOOKUP(_xlpm.job,tbl_WIP[Job Number],tbl_WIP[Client],""),_xlfn.XLOOKUP(_xlpm.job,tbl_WIP[Job Number],tbl_WIP[Cost Centre],""),_xlpm.opn,_xlpm.mvt,_xlpm.opn+_xlpm.mvt))</f>
         <v/>
       </c>
       <c r="G11" s="26" t="n"/>
